--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
         <v>1.77</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1363,16 +1363,16 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
         <v>1.31</v>
@@ -1384,7 +1384,7 @@
         <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR5" t="n">
         <v>8.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>3.15</v>
       </c>
       <c r="G9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>28</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
         <v>19.5</v>
@@ -2214,10 +2214,10 @@
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO9" t="n">
         <v>21</v>
@@ -2232,7 +2232,7 @@
         <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
         <v>12</v>
@@ -2259,26 +2259,26 @@
         <v>30</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD9" t="n">
         <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG9" t="n">
         <v>15.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4661,16 +4661,16 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
         <v>1.32</v>
@@ -4679,10 +4679,10 @@
         <v>3.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U22" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
         <v>2.24</v>
@@ -4706,7 +4706,7 @@
         <v>16.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
         <v>10</v>
@@ -4763,7 +4763,7 @@
         <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
         <v>17.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.99</v>
       </c>
       <c r="G24" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H24" t="n">
         <v>4.3</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5419,13 +5419,13 @@
         <v>4.8</v>
       </c>
       <c r="H26" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="J26" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K26" t="n">
         <v>3.6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>1.69</v>
       </c>
       <c r="G27" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
         <v>5</v>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q27" t="n">
         <v>1.52</v>
@@ -5649,10 +5649,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U27" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG27" t="n">
         <v>12.5</v>
@@ -5709,7 +5709,7 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
@@ -5718,13 +5718,13 @@
         <v>20</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT27" t="n">
         <v>11.5</v>
@@ -5733,10 +5733,10 @@
         <v>9.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX27" t="n">
         <v>11.5</v>
@@ -5745,10 +5745,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB27" t="n">
         <v>16</v>
@@ -5757,20 +5757,20 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF27" t="n">
         <v>5.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G32" t="n">
         <v>2.6</v>
@@ -6586,7 +6586,7 @@
         <v>3.25</v>
       </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>3.15</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q32" t="n">
         <v>2.2</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7356,16 +7356,16 @@
         <v>3.15</v>
       </c>
       <c r="G36" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H36" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I36" t="n">
         <v>2.44</v>
       </c>
       <c r="J36" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K36" t="n">
         <v>3.9</v>
@@ -7383,7 +7383,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
         <v>1.83</v>
@@ -7416,7 +7416,7 @@
         <v>18</v>
       </c>
       <c r="AA36" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB36" t="n">
         <v>15</v>
@@ -7434,22 +7434,22 @@
         <v>26</v>
       </c>
       <c r="AG36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH36" t="n">
         <v>17</v>
       </c>
-      <c r="AH36" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AI36" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK36" t="n">
         <v>38</v>
       </c>
-      <c r="AJ36" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>40</v>
-      </c>
       <c r="AL36" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
@@ -7458,7 +7458,7 @@
         <v>34</v>
       </c>
       <c r="AO36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP36" t="n">
         <v>12</v>
@@ -7470,7 +7470,7 @@
         <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT36" t="n">
         <v>12</v>
@@ -7494,10 +7494,10 @@
         <v>13.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC36" t="n">
         <v>30</v>
@@ -7506,7 +7506,7 @@
         <v>36</v>
       </c>
       <c r="BE36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF36" t="n">
         <v>24</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
         <v>11</v>
       </c>
       <c r="J37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K37" t="n">
         <v>5.1</v>
@@ -7580,7 +7580,7 @@
         <v>1.96</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R37" t="n">
         <v>1.37</v>
@@ -7589,7 +7589,7 @@
         <v>3.55</v>
       </c>
       <c r="T37" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U37" t="n">
         <v>1.71</v>
@@ -7640,7 +7640,7 @@
         <v>11</v>
       </c>
       <c r="AK37" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL37" t="n">
         <v>50</v>
@@ -7673,7 +7673,7 @@
         <v>10</v>
       </c>
       <c r="AV37" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AW37" t="n">
         <v>46</v>
@@ -7685,7 +7685,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ37" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BA37" t="n">
         <v>46</v>
@@ -7700,7 +7700,7 @@
         <v>42</v>
       </c>
       <c r="BE37" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="BF37" t="n">
         <v>6.8</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7771,10 +7771,10 @@
         <v>1.36</v>
       </c>
       <c r="P38" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R38" t="n">
         <v>1.3</v>
@@ -7855,34 +7855,34 @@
         <v>11</v>
       </c>
       <c r="AR38" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
         <v>15</v>
       </c>
       <c r="AW38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
         <v>16.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
         <v>20</v>
@@ -7891,20 +7891,20 @@
         <v>17</v>
       </c>
       <c r="BD38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
         <v>12.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
@@ -7968,7 +7968,7 @@
         <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R39" t="n">
         <v>1.09</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -8905,25 +8905,25 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="G44" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="H44" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I44" t="n">
         <v>3.05</v>
       </c>
       <c r="J44" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L44" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
         <v>1.01</v>
@@ -8935,10 +8935,10 @@
         <v>1.24</v>
       </c>
       <c r="P44" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="R44" t="n">
         <v>1.34</v>
@@ -8950,13 +8950,13 @@
         <v>1.56</v>
       </c>
       <c r="U44" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V44" t="n">
         <v>1.49</v>
       </c>
       <c r="W44" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X44" t="n">
         <v>24</v>
@@ -8986,7 +8986,7 @@
         <v>25</v>
       </c>
       <c r="AG44" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH44" t="n">
         <v>21</v>
@@ -9007,7 +9007,7 @@
         <v>95</v>
       </c>
       <c r="AN44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO44" t="n">
         <v>29</v>
@@ -9022,34 +9022,34 @@
         <v>15</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AT44" t="n">
         <v>9.6</v>
       </c>
       <c r="AU44" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AW44" t="n">
         <v>21</v>
       </c>
       <c r="AX44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AY44" t="n">
         <v>2.84</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BA44" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BB44" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BC44" t="n">
         <v>19.5</v>
@@ -9058,7 +9058,7 @@
         <v>3.2</v>
       </c>
       <c r="BE44" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BF44" t="n">
         <v>13</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         <v>5.1</v>
       </c>
       <c r="J45" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="K45" t="n">
         <v>4.1</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
         <v>2.64</v>
       </c>
       <c r="H46" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
         <v>4.4</v>
@@ -9308,7 +9308,7 @@
         <v>3.3</v>
       </c>
       <c r="K46" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9487,16 +9487,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G47" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H47" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I47" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>3.55</v>
@@ -9520,7 +9520,7 @@
         <v>1.98</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G48" t="n">
         <v>2.66</v>
@@ -9711,7 +9711,7 @@
         <v>1.47</v>
       </c>
       <c r="P48" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q48" t="n">
         <v>2.42</v>
@@ -9723,7 +9723,7 @@
         <v>4.7</v>
       </c>
       <c r="T48" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U48" t="n">
         <v>1.96</v>
@@ -9741,7 +9741,7 @@
         <v>10.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA48" t="n">
         <v>65</v>
@@ -9759,7 +9759,7 @@
         <v>48</v>
       </c>
       <c r="AF48" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG48" t="n">
         <v>12.5</v>
@@ -9768,7 +9768,7 @@
         <v>19.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ48" t="n">
         <v>42</v>
@@ -9777,13 +9777,13 @@
         <v>38</v>
       </c>
       <c r="AL48" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM48" t="n">
         <v>150</v>
       </c>
       <c r="AN48" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO48" t="n">
         <v>55</v>
@@ -9822,7 +9822,7 @@
         <v>17.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB48" t="n">
         <v>34</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -9875,19 +9875,19 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="G49" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="H49" t="n">
         <v>1.25</v>
       </c>
       <c r="I49" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="J49" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="K49" t="n">
         <v>7.2</v>
@@ -9899,19 +9899,19 @@
         <v>1.03</v>
       </c>
       <c r="N49" t="n">
-        <v>4.9</v>
+        <v>2.54</v>
       </c>
       <c r="O49" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P49" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="Q49" t="n">
         <v>1.58</v>
       </c>
       <c r="R49" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S49" t="n">
         <v>2.4</v>
@@ -9920,13 +9920,13 @@
         <v>2.2</v>
       </c>
       <c r="U49" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V49" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
         <v>28</v>
@@ -9947,7 +9947,7 @@
         <v>16</v>
       </c>
       <c r="AD49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE49" t="n">
         <v>16.5</v>
@@ -9983,7 +9983,7 @@
         <v>4.7</v>
       </c>
       <c r="AP49" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ49" t="n">
         <v>8.199999999999999</v>
@@ -9995,7 +9995,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU49" t="n">
         <v>12</v>
@@ -10004,41 +10004,41 @@
         <v>11</v>
       </c>
       <c r="AW49" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX49" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY49" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA49" t="n">
         <v>5.2</v>
       </c>
-      <c r="AZ49" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BB49" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC49" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC49" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD49" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG49" t="n">
         <v>3.45</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G50" t="n">
         <v>3.15</v>
@@ -10081,10 +10081,10 @@
         <v>2.78</v>
       </c>
       <c r="J50" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K50" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>1.58</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -10111,7 +10111,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U50" t="n">
         <v>1.84</v>
@@ -10138,7 +10138,7 @@
         <v>10.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD50" t="n">
         <v>970</v>
@@ -10180,28 +10180,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AR50" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AU50" t="n">
         <v>6.2</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW50" t="n">
         <v>4.8</v>
       </c>
       <c r="AX50" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY50" t="n">
         <v>4</v>
@@ -10213,16 +10213,16 @@
         <v>5</v>
       </c>
       <c r="BB50" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC50" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC50" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD50" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE50" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF50" t="n">
         <v>4.9</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="G51" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H51" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="I51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K51" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10287,10 +10287,10 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O51" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P51" t="n">
         <v>1.52</v>
@@ -10311,10 +10311,10 @@
         <v>1.51</v>
       </c>
       <c r="V51" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W51" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X51" t="n">
         <v>11</v>
@@ -10383,7 +10383,7 @@
         <v>12.5</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU51" t="n">
         <v>8.4</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-04 01:23:04</t>
+          <t>2026-04-04 03:54:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
         <v>1.47</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
         <v>3.9</v>
@@ -966,7 +966,7 @@
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
         <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>1.31</v>
@@ -1399,10 +1399,10 @@
         <v>7.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
         <v>17.5</v>
@@ -1420,7 +1420,7 @@
         <v>46</v>
       </c>
       <c r="AG5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH5" t="n">
         <v>24</v>
@@ -1441,22 +1441,22 @@
         <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AO5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
         <v>8.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
@@ -1465,7 +1465,7 @@
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>17.5</v>
@@ -1480,29 +1480,29 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
         <v>11</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="G6" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
         <v>3.4</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
         <v>2.24</v>
@@ -2169,16 +2169,16 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
         <v>14</v>
@@ -2187,52 +2187,52 @@
         <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>12</v>
@@ -2250,35 +2250,35 @@
         <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
         <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>38</v>
+        <v>9.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BG9" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G10" t="n">
         <v>3.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
         <v>1.76</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G12" t="n">
         <v>2.38</v>
@@ -2709,10 +2709,10 @@
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -2897,16 +2897,16 @@
         <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G14" t="n">
         <v>2.22</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="I14" t="n">
         <v>5.4</v>
@@ -3100,7 +3100,7 @@
         <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H20" t="n">
         <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
         <v>6.2</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="G21" t="n">
         <v>4.6</v>
@@ -4452,13 +4452,13 @@
         <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -4661,10 +4661,10 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
         <v>1.86</v>
@@ -4694,7 +4694,7 @@
         <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z22" t="n">
         <v>10</v>
@@ -4730,7 +4730,7 @@
         <v>170</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AL22" t="n">
         <v>100</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G23" t="n">
         <v>3.7</v>
       </c>
       <c r="H23" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G25" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="H25" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
         <v>14</v>
@@ -5234,7 +5234,7 @@
         <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
         <v>4.8</v>
       </c>
       <c r="H26" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="I26" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>1.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="G27" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="I27" t="n">
         <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5649,10 +5649,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5664,34 +5664,34 @@
         <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC27" t="n">
         <v>11.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5700,55 +5700,55 @@
         <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
         <v>11.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX27" t="n">
         <v>11.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
         <v>16</v>
@@ -5757,20 +5757,20 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>2.86</v>
+        <v>1.02</v>
       </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="G29" t="n">
         <v>2.3</v>
       </c>
       <c r="H29" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I29" t="n">
         <v>5.9</v>
@@ -6010,7 +6010,7 @@
         <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G30" t="n">
         <v>4.1</v>
       </c>
       <c r="H30" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="I30" t="n">
         <v>3.2</v>
       </c>
       <c r="J30" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="K30" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="G31" t="n">
         <v>3.4</v>
       </c>
       <c r="H31" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I31" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K31" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>2.4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H32" t="n">
         <v>3.25</v>
@@ -6589,10 +6589,10 @@
         <v>3.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="G35" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H35" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I35" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J35" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K35" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
         <v>2.26</v>
       </c>
       <c r="I36" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>3.5</v>
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U36" t="n">
         <v>2.22</v>
@@ -7407,76 +7407,76 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z36" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y36" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>18</v>
-      </c>
       <c r="AA36" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB36" t="n">
         <v>15</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD36" t="n">
         <v>13</v>
       </c>
       <c r="AE36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AF36" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG36" t="n">
         <v>15</v>
       </c>
       <c r="AH36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
         <v>36</v>
       </c>
-      <c r="AJ36" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>34</v>
-      </c>
       <c r="AO36" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT36" t="n">
         <v>12</v>
       </c>
       <c r="AU36" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV36" t="n">
         <v>9.800000000000001</v>
@@ -7494,29 +7494,29 @@
         <v>13.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="BD36" t="n">
-        <v>36</v>
+        <v>5.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>24</v>
+        <v>5.2</v>
       </c>
       <c r="BG36" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -7550,16 +7550,16 @@
         <v>1.4</v>
       </c>
       <c r="G37" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I37" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K37" t="n">
         <v>5.1</v>
@@ -7613,7 +7613,7 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC37" t="n">
         <v>11.5</v>
@@ -7622,7 +7622,7 @@
         <v>42</v>
       </c>
       <c r="AE37" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AF37" t="n">
         <v>7.2</v>
@@ -7631,7 +7631,7 @@
         <v>11</v>
       </c>
       <c r="AH37" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -7640,13 +7640,13 @@
         <v>11</v>
       </c>
       <c r="AK37" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL37" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM37" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AN37" t="n">
         <v>7.4</v>
@@ -7658,13 +7658,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AR37" t="n">
         <v>36</v>
       </c>
       <c r="AS37" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AT37" t="n">
         <v>6.6</v>
@@ -7673,7 +7673,7 @@
         <v>10</v>
       </c>
       <c r="AV37" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AW37" t="n">
         <v>46</v>
@@ -7685,19 +7685,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ37" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BA37" t="n">
         <v>46</v>
       </c>
       <c r="BB37" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC37" t="n">
         <v>15</v>
       </c>
       <c r="BD37" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BE37" t="n">
         <v>95</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G38" t="n">
         <v>2.12</v>
@@ -7750,22 +7750,22 @@
         <v>4.1</v>
       </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
         <v>4.2</v>
       </c>
       <c r="L38" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O38" t="n">
         <v>1.36</v>
@@ -7777,16 +7777,16 @@
         <v>2.06</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S38" t="n">
         <v>3.75</v>
       </c>
       <c r="T38" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="U38" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="V38" t="n">
         <v>1.25</v>
@@ -7798,58 +7798,58 @@
         <v>14.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA38" t="n">
         <v>120</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE38" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG38" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI38" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AK38" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL38" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM38" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN38" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO38" t="n">
         <v>80</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>11</v>
@@ -7861,34 +7861,34 @@
         <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>15</v>
       </c>
-      <c r="AW38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA38" t="n">
         <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC38" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD38" t="n">
         <v>1.01</v>
@@ -7897,14 +7897,14 @@
         <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG38" t="n">
         <v>1.01</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G39" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H39" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I39" t="n">
         <v>3.3</v>
@@ -7950,7 +7950,7 @@
         <v>2.92</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,16 +7959,16 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
       </c>
       <c r="P39" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
         <v>1.09</v>
@@ -7986,7 +7986,7 @@
         <v>1.44</v>
       </c>
       <c r="W39" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="G40" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H40" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I40" t="n">
         <v>6</v>
       </c>
       <c r="J40" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -8159,10 +8159,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="G41" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H41" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="I41" t="n">
         <v>3.95</v>
       </c>
       <c r="J41" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
         <v>1.5</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="H42" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
         <v>3.25</v>
@@ -8547,7 +8547,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q42" t="n">
         <v>2.06</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G43" t="n">
         <v>3.3</v>
       </c>
       <c r="H43" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="I43" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="J43" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K43" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8741,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q43" t="n">
         <v>1.65</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -8908,25 +8908,25 @@
         <v>2.6</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="I44" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K44" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N44" t="n">
         <v>4</v>
@@ -8935,140 +8935,140 @@
         <v>1.24</v>
       </c>
       <c r="P44" t="n">
-        <v>1.91</v>
+        <v>1.26</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="R44" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="T44" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W44" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X44" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G45" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H45" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="K45" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -9132,7 +9132,7 @@
         <v>1.29</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G46" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I46" t="n">
         <v>4.4</v>
       </c>
       <c r="J46" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K46" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="H47" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K47" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G48" t="n">
         <v>2.66</v>
@@ -9708,7 +9708,7 @@
         <v>3.05</v>
       </c>
       <c r="O48" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P48" t="n">
         <v>1.67</v>
@@ -9723,10 +9723,10 @@
         <v>4.7</v>
       </c>
       <c r="T48" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U48" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
@@ -9741,25 +9741,25 @@
         <v>10.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA48" t="n">
         <v>65</v>
       </c>
       <c r="AB48" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC48" t="n">
         <v>6.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF48" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG48" t="n">
         <v>12.5</v>
@@ -9771,10 +9771,10 @@
         <v>65</v>
       </c>
       <c r="AJ48" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK48" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL48" t="n">
         <v>55</v>
@@ -9783,7 +9783,7 @@
         <v>150</v>
       </c>
       <c r="AN48" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO48" t="n">
         <v>55</v>
@@ -9798,7 +9798,7 @@
         <v>19</v>
       </c>
       <c r="AS48" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AT48" t="n">
         <v>8.199999999999999</v>
@@ -9813,25 +9813,25 @@
         <v>38</v>
       </c>
       <c r="AX48" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ48" t="n">
         <v>17.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB48" t="n">
         <v>34</v>
       </c>
       <c r="BC48" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BD48" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BE48" t="n">
         <v>42</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="G49" t="n">
         <v>17.5</v>
@@ -9902,7 +9902,7 @@
         <v>2.54</v>
       </c>
       <c r="O49" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P49" t="n">
         <v>2.54</v>
@@ -9911,7 +9911,7 @@
         <v>1.58</v>
       </c>
       <c r="R49" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S49" t="n">
         <v>2.4</v>
@@ -9929,13 +9929,13 @@
         <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y49" t="n">
         <v>12</v>
       </c>
       <c r="Z49" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA49" t="n">
         <v>11</v>
@@ -9944,22 +9944,22 @@
         <v>55</v>
       </c>
       <c r="AC49" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AD49" t="n">
         <v>14</v>
       </c>
       <c r="AE49" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AF49" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AG49" t="n">
         <v>65</v>
       </c>
       <c r="AH49" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI49" t="n">
         <v>55</v>
@@ -9968,37 +9968,37 @@
         <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AL49" t="n">
         <v>230</v>
       </c>
       <c r="AM49" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AN49" t="n">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="AO49" t="n">
         <v>4.7</v>
       </c>
       <c r="AP49" t="n">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR49" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT49" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AU49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV49" t="n">
         <v>11</v>
@@ -10007,38 +10007,38 @@
         <v>12.5</v>
       </c>
       <c r="AX49" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AY49" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB49" t="n">
         <v>5.3</v>
       </c>
-      <c r="AZ49" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA49" t="n">
+      <c r="BC49" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD49" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB49" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE49" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG49" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -10069,19 +10069,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="G50" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="H50" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="I50" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J50" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K50" t="n">
         <v>3.4</v>
@@ -10102,7 +10102,7 @@
         <v>1.58</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U50" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -10123,46 +10123,46 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y50" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA50" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AB50" t="n">
         <v>10.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE50" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AF50" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG50" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH50" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI50" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ50" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AK50" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL50" t="n">
         <v>75</v>
@@ -10171,68 +10171,68 @@
         <v>180</v>
       </c>
       <c r="AN50" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO50" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AP50" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="AR50" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AS50" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU50" t="n">
         <v>6.2</v>
       </c>
       <c r="AV50" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX50" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="AY50" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="BA50" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BD50" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BE50" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BG50" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -10263,13 +10263,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G51" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="H51" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I51" t="n">
         <v>12</v>
@@ -10278,7 +10278,7 @@
         <v>3.85</v>
       </c>
       <c r="K51" t="n">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10287,7 +10287,7 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O51" t="n">
         <v>1.02</v>
@@ -10296,137 +10296,137 @@
         <v>1.52</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R51" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T51" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U51" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="V51" t="n">
         <v>1.09</v>
       </c>
       <c r="W51" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="X51" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y51" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z51" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA51" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE51" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI51" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK51" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL51" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM51" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO51" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR51" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS51" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU51" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV51" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW51" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY51" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA51" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC51" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD51" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -10490,13 +10490,13 @@
         <v>1.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R52" t="n">
         <v>1.08</v>
       </c>
       <c r="S52" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-04 03:54:58</t>
+          <t>2026-04-04 06:26:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
@@ -757,28 +757,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G2" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H2" t="n">
         <v>6.8</v>
       </c>
       <c r="I2" t="n">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="J2" t="n">
         <v>4.7</v>
       </c>
       <c r="K2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
         <v>5.2</v>
@@ -796,19 +796,19 @@
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
         <v>3.9</v>
@@ -1002,7 +1002,7 @@
         <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -1154,10 +1154,10 @@
         <v>2.02</v>
       </c>
       <c r="I4" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
         <v>4.9</v>
@@ -1169,31 +1169,31 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="W4" t="n">
         <v>1.32</v>
@@ -1253,7 +1253,7 @@
         <v>12.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>10.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
-        <v>2.38</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>85</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G6" t="n">
         <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I6" t="n">
         <v>1.73</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
@@ -1581,7 +1581,7 @@
         <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1593,7 +1593,7 @@
         <v>7.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" t="n">
         <v>18</v>
@@ -1677,16 +1677,16 @@
         <v>36</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="BD6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BE6" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H7" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
         <v>3.8</v>
@@ -1748,37 +1748,37 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1793,7 +1793,7 @@
         <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -1838,16 +1838,16 @@
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
         <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>6.6</v>
@@ -1856,41 +1856,41 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
         <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF7" t="n">
         <v>19</v>
       </c>
       <c r="BG7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -1936,19 +1936,19 @@
         <v>2.72</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
         <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="P8" t="n">
         <v>1.58</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>1.91</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
         <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
@@ -2351,16 +2351,16 @@
         <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
         <v>24</v>
@@ -2414,10 +2414,10 @@
         <v>13.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ10" t="n">
         <v>13</v>
@@ -2429,16 +2429,16 @@
         <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
         <v>1.13</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
         <v>1.13</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -2700,25 +2700,25 @@
         <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I12" t="n">
         <v>2.56</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
         <v>4</v>
@@ -2727,22 +2727,22 @@
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V12" t="n">
         <v>1.64</v>
@@ -2751,116 +2751,116 @@
         <v>1.45</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H13" t="n">
         <v>2.06</v>
       </c>
       <c r="I13" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2921,7 +2921,7 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
         <v>1.67</v>
@@ -2939,7 +2939,7 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="W13" t="n">
         <v>1.29</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>110</v>
       </c>
       <c r="H14" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="I14" t="n">
         <v>2.86</v>
@@ -3136,7 +3136,7 @@
         <v>1.54</v>
       </c>
       <c r="W14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>5.6</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>4.6</v>
@@ -3297,7 +3297,7 @@
         <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
@@ -3315,7 +3315,7 @@
         <v>1.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
         <v>2.34</v>
@@ -3324,10 +3324,10 @@
         <v>1.66</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
         <v>2.58</v>
@@ -3396,10 +3396,10 @@
         <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
         <v>8.800000000000001</v>
@@ -3420,7 +3420,7 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3438,11 +3438,11 @@
         <v>4.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -3506,13 +3506,13 @@
         <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.7</v>
@@ -3542,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
         <v>13</v>
@@ -3572,7 +3572,7 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="n">
         <v>36</v>
@@ -3587,13 +3587,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
         <v>5</v>
       </c>
       <c r="AT16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>7.4</v>
@@ -3602,25 +3602,25 @@
         <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX16" t="n">
         <v>17.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
         <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="BB16" t="n">
         <v>5.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="BD16" t="n">
         <v>5.2</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -4079,13 +4079,13 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O19" t="n">
         <v>1.19</v>
       </c>
       <c r="P19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q19" t="n">
         <v>1.19</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
@@ -4273,13 +4273,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
         <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
         <v>1.02</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -4837,16 +4837,16 @@
         <v>4.3</v>
       </c>
       <c r="H23" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4867,7 +4867,7 @@
         <v>1.85</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="S23" t="n">
         <v>3.05</v>
@@ -4879,7 +4879,7 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W23" t="n">
         <v>1.31</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -5243,13 +5243,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
         <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
         <v>1.19</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -5715,52 +5715,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H28" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I28" t="n">
         <v>2.34</v>
@@ -5846,13 +5846,13 @@
         <v>1.53</v>
       </c>
       <c r="U28" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V28" t="n">
         <v>1.74</v>
       </c>
       <c r="W28" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X28" t="n">
         <v>30</v>
@@ -5867,7 +5867,7 @@
         <v>34</v>
       </c>
       <c r="AB28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC28" t="n">
         <v>12</v>
@@ -5909,7 +5909,7 @@
         <v>12.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ28" t="n">
         <v>11.5</v>
@@ -5918,7 +5918,7 @@
         <v>13.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT28" t="n">
         <v>14.5</v>
@@ -5930,7 +5930,7 @@
         <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
         <v>20</v>
@@ -5951,10 +5951,10 @@
         <v>4.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF28" t="n">
         <v>14.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -6189,118 +6189,118 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H30" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="I30" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>2.38</v>
+        <v>3.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
         <v>1.58</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S30" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP30" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>1.03</v>
@@ -6309,25 +6309,25 @@
         <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW30" t="n">
         <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA30" t="n">
         <v>1.03</v>
@@ -6345,14 +6345,14 @@
         <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>2.74</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>2.72</v>
       </c>
       <c r="K33" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.43</v>
@@ -6795,16 +6795,16 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O33" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="P33" t="n">
         <v>1.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="G35" t="n">
         <v>4.4</v>
@@ -7180,7 +7180,7 @@
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N35" t="n">
         <v>2.78</v>
@@ -7189,7 +7189,7 @@
         <v>1.35</v>
       </c>
       <c r="P35" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Q35" t="n">
         <v>1.91</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="G36" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="H36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="J36" t="n">
         <v>4.3</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7389,7 +7389,7 @@
         <v>1.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S36" t="n">
         <v>1.79</v>
@@ -7401,10 +7401,10 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7461,52 +7461,52 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.02</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H38" t="n">
         <v>3.4</v>
@@ -7768,7 +7768,7 @@
         <v>4.1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P38" t="n">
         <v>2.06</v>
@@ -7780,10 +7780,10 @@
         <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T38" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U38" t="n">
         <v>2.06</v>
@@ -7792,7 +7792,7 @@
         <v>1.31</v>
       </c>
       <c r="W38" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="X38" t="n">
         <v>22</v>
@@ -7849,7 +7849,7 @@
         <v>44</v>
       </c>
       <c r="AP38" t="n">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>11.5</v>
@@ -7867,7 +7867,7 @@
         <v>3.05</v>
       </c>
       <c r="AV38" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AW38" t="n">
         <v>3.95</v>
@@ -7876,10 +7876,10 @@
         <v>10.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AZ38" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="BA38" t="n">
         <v>3.95</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -8043,52 +8043,52 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
         <v>1.01</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>2.42</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H40" t="n">
         <v>3.25</v>
@@ -8150,7 +8150,7 @@
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N40" t="n">
         <v>3.15</v>
@@ -8180,7 +8180,7 @@
         <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X40" t="n">
         <v>14.5</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
         <v>1.18</v>
       </c>
       <c r="P41" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q41" t="n">
         <v>1.18</v>
@@ -8431,52 +8431,52 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF41" t="n">
         <v>1.01</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -8523,10 +8523,10 @@
         <v>4.8</v>
       </c>
       <c r="H42" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I42" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>3.45</v>
@@ -8547,7 +8547,7 @@
         <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q42" t="n">
         <v>2.06</v>
@@ -8559,13 +8559,13 @@
         <v>3.6</v>
       </c>
       <c r="T42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.85</v>
       </c>
-      <c r="U42" t="n">
-        <v>1.95</v>
-      </c>
       <c r="V42" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
         <v>1.26</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -8926,25 +8926,25 @@
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="O44" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P44" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="R44" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
         <v>1.71</v>
@@ -8959,7 +8959,7 @@
         <v>1.92</v>
       </c>
       <c r="X44" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y44" t="n">
         <v>17.5</v>
@@ -9022,7 +9022,7 @@
         <v>4.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT44" t="n">
         <v>7.6</v>
@@ -9046,7 +9046,7 @@
         <v>17</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB44" t="n">
         <v>21</v>
@@ -9055,20 +9055,20 @@
         <v>20</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF44" t="n">
         <v>14.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -9099,16 +9099,16 @@
         </is>
       </c>
       <c r="F45" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G45" t="n">
         <v>5.4</v>
       </c>
-      <c r="G45" t="n">
-        <v>5.6</v>
-      </c>
       <c r="H45" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="I45" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J45" t="n">
         <v>3.8</v>
@@ -9132,7 +9132,7 @@
         <v>1.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R45" t="n">
         <v>1.32</v>
@@ -9147,10 +9147,10 @@
         <v>1.95</v>
       </c>
       <c r="V45" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W45" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X45" t="n">
         <v>13</v>
@@ -9159,10 +9159,10 @@
         <v>7.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA45" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AB45" t="n">
         <v>16.5</v>
@@ -9189,7 +9189,7 @@
         <v>40</v>
       </c>
       <c r="AJ45" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="n">
         <v>80</v>
@@ -9204,10 +9204,10 @@
         <v>110</v>
       </c>
       <c r="AO45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP45" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ45" t="n">
         <v>7.4</v>
@@ -9240,7 +9240,7 @@
         <v>19.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB45" t="n">
         <v>42</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -9302,10 +9302,10 @@
         <v>5.3</v>
       </c>
       <c r="I46" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="K46" t="n">
         <v>5.3</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -9496,13 +9496,13 @@
         <v>2.6</v>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J47" t="n">
         <v>3.4</v>
       </c>
       <c r="K47" t="n">
-        <v>5.3</v>
+        <v>110</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9535,7 +9535,7 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W47" t="n">
         <v>1.57</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -9875,13 +9875,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G49" t="n">
         <v>3.15</v>
       </c>
       <c r="H49" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I49" t="n">
         <v>2.7</v>
@@ -9923,7 +9923,7 @@
         <v>2.22</v>
       </c>
       <c r="V49" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W49" t="n">
         <v>1.46</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -10072,25 +10072,25 @@
         <v>3.2</v>
       </c>
       <c r="G50" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H50" t="n">
         <v>1.86</v>
       </c>
       <c r="I50" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>3.45</v>
       </c>
       <c r="K50" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N50" t="n">
         <v>1.01</v>
@@ -10108,7 +10108,7 @@
         <v>1.64</v>
       </c>
       <c r="S50" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -10117,7 +10117,7 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W50" t="n">
         <v>1.33</v>
@@ -10177,52 +10177,52 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF50" t="n">
         <v>1.01</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>3.65</v>
       </c>
       <c r="G51" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="H51" t="n">
         <v>1.86</v>
@@ -10275,7 +10275,7 @@
         <v>2.02</v>
       </c>
       <c r="J51" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K51" t="n">
         <v>4.7</v>
@@ -10284,7 +10284,7 @@
         <v>1.24</v>
       </c>
       <c r="M51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N51" t="n">
         <v>5.6</v>
@@ -10299,10 +10299,10 @@
         <v>1.53</v>
       </c>
       <c r="R51" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S51" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="T51" t="n">
         <v>1.54</v>
@@ -10314,7 +10314,7 @@
         <v>1.98</v>
       </c>
       <c r="W51" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="X51" t="n">
         <v>32</v>
@@ -10392,10 +10392,10 @@
         <v>8.6</v>
       </c>
       <c r="AW51" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX51" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AY51" t="n">
         <v>12.5</v>
@@ -10407,16 +10407,16 @@
         <v>19.5</v>
       </c>
       <c r="BB51" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="BC51" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BD51" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE51" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF51" t="n">
         <v>20</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="G52" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="H52" t="n">
         <v>11</v>
@@ -10472,7 +10472,7 @@
         <v>6.8</v>
       </c>
       <c r="K52" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10481,34 +10481,34 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="P52" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="R52" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="S52" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T52" t="n">
         <v>1.68</v>
       </c>
       <c r="U52" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V52" t="n">
         <v>1.05</v>
       </c>
       <c r="W52" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="X52" t="n">
         <v>65</v>
@@ -10565,28 +10565,28 @@
         <v>190</v>
       </c>
       <c r="AP52" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AQ52" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="AR52" t="n">
-        <v>100</v>
+        <v>1.03</v>
       </c>
       <c r="AS52" t="n">
-        <v>85</v>
+        <v>1.03</v>
       </c>
       <c r="AT52" t="n">
         <v>12</v>
       </c>
       <c r="AU52" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AV52" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AW52" t="n">
-        <v>120</v>
+        <v>1.03</v>
       </c>
       <c r="AX52" t="n">
         <v>8.6</v>
@@ -10595,10 +10595,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ52" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BA52" t="n">
-        <v>85</v>
+        <v>1.03</v>
       </c>
       <c r="BB52" t="n">
         <v>8</v>
@@ -10607,10 +10607,10 @@
         <v>10</v>
       </c>
       <c r="BD52" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BE52" t="n">
-        <v>75</v>
+        <v>1.03</v>
       </c>
       <c r="BF52" t="n">
         <v>2.32</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10660,7 @@
         <v>1.9</v>
       </c>
       <c r="I53" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J53" t="n">
         <v>4</v>
@@ -10699,7 +10699,7 @@
         <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W53" t="n">
         <v>1.28</v>
@@ -10759,52 +10759,52 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF53" t="n">
         <v>1.01</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -10869,19 +10869,19 @@
         <v>1.03</v>
       </c>
       <c r="N54" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
       </c>
       <c r="P54" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R54" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
         <v>2.36</v>
@@ -10953,52 +10953,52 @@
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF54" t="n">
         <v>1.01</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -11039,28 +11039,28 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="G55" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="H55" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="I55" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J55" t="n">
         <v>3.35</v>
       </c>
       <c r="K55" t="n">
-        <v>110</v>
+        <v>3.95</v>
       </c>
       <c r="L55" t="n">
         <v>1.29</v>
       </c>
       <c r="M55" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N55" t="n">
         <v>2.9</v>
@@ -11069,16 +11069,16 @@
         <v>1.28</v>
       </c>
       <c r="P55" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R55" t="n">
         <v>1.31</v>
       </c>
       <c r="S55" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T55" t="n">
         <v>1.01</v>
@@ -11087,122 +11087,122 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W55" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
       </c>
       <c r="Y55" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z55" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA55" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB55" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC55" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD55" t="n">
         <v>1000</v>
       </c>
       <c r="AE55" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF55" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG55" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI55" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK55" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL55" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM55" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN55" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO55" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -11269,16 +11269,16 @@
         <v>1.66</v>
       </c>
       <c r="R56" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S56" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T56" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="U56" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="V56" t="n">
         <v>2.04</v>
@@ -11365,7 +11365,7 @@
         <v>13</v>
       </c>
       <c r="AX56" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AY56" t="n">
         <v>13</v>
@@ -11377,16 +11377,16 @@
         <v>21</v>
       </c>
       <c r="BB56" t="n">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="BC56" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BD56" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE56" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF56" t="n">
         <v>27</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -11427,22 +11427,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G57" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="H57" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>2.44</v>
+        <v>3.85</v>
       </c>
       <c r="K57" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="L57" t="n">
         <v>1.01</v>
@@ -11451,13 +11451,13 @@
         <v>1.02</v>
       </c>
       <c r="N57" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="O57" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P57" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q57" t="n">
         <v>1.43</v>
@@ -11466,67 +11466,67 @@
         <v>1.58</v>
       </c>
       <c r="S57" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T57" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U57" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V57" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
       </c>
       <c r="Y57" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z57" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA57" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB57" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC57" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD57" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE57" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF57" t="n">
         <v>1000</v>
       </c>
       <c r="AG57" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI57" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK57" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL57" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM57" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN57" t="n">
         <v>1000</v>
@@ -11535,62 +11535,62 @@
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -11651,7 +11651,7 @@
         <v>1.31</v>
       </c>
       <c r="P58" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q58" t="n">
         <v>1.78</v>
@@ -11729,52 +11729,52 @@
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
         <v>1.01</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -11818,13 +11818,13 @@
         <v>3.65</v>
       </c>
       <c r="G59" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H59" t="n">
         <v>1.99</v>
       </c>
       <c r="I59" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="J59" t="n">
         <v>3.6</v>
@@ -11845,28 +11845,28 @@
         <v>1.26</v>
       </c>
       <c r="P59" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q59" t="n">
         <v>1.78</v>
       </c>
       <c r="R59" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S59" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="T59" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="U59" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V59" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="W59" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X59" t="n">
         <v>20</v>
@@ -11947,7 +11947,7 @@
         <v>16</v>
       </c>
       <c r="AX59" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AY59" t="n">
         <v>12</v>
@@ -11956,19 +11956,19 @@
         <v>13</v>
       </c>
       <c r="BA59" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BB59" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BC59" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BD59" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BE59" t="n">
-        <v>60</v>
+        <v>1.03</v>
       </c>
       <c r="BF59" t="n">
         <v>30</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -12009,22 +12009,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G60" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="H60" t="n">
         <v>3.35</v>
       </c>
       <c r="I60" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="K60" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -12039,10 +12039,10 @@
         <v>1.22</v>
       </c>
       <c r="P60" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R60" t="n">
         <v>1.36</v>
@@ -12057,10 +12057,10 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W60" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12117,16 +12117,16 @@
         <v>48</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ60" t="n">
         <v>10.5</v>
       </c>
       <c r="AR60" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS60" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="AT60" t="n">
         <v>7.6</v>
@@ -12138,7 +12138,7 @@
         <v>10</v>
       </c>
       <c r="AW60" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AX60" t="n">
         <v>9.6</v>
@@ -12150,19 +12150,19 @@
         <v>11</v>
       </c>
       <c r="BA60" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BB60" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC60" t="n">
         <v>14</v>
       </c>
       <c r="BD60" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE60" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BF60" t="n">
         <v>9.199999999999999</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12218,7 @@
         <v>3.5</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12278,19 +12278,19 @@
         <v>12.5</v>
       </c>
       <c r="AE61" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF61" t="n">
         <v>42</v>
       </c>
       <c r="AG61" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH61" t="n">
         <v>22</v>
       </c>
-      <c r="AH61" t="n">
-        <v>23</v>
-      </c>
       <c r="AI61" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ61" t="n">
         <v>120</v>
@@ -12326,7 +12326,7 @@
         <v>11.5</v>
       </c>
       <c r="AU61" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV61" t="n">
         <v>7.6</v>
@@ -12335,38 +12335,38 @@
         <v>14.5</v>
       </c>
       <c r="AX61" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AY61" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ61" t="n">
         <v>13.5</v>
       </c>
       <c r="BA61" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BB61" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BC61" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BD61" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BE61" t="n">
-        <v>70</v>
+        <v>1.03</v>
       </c>
       <c r="BF61" t="n">
         <v>42</v>
       </c>
       <c r="BG61" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
         <v>17</v>
       </c>
       <c r="AW62" t="n">
-        <v>38</v>
+        <v>5.1</v>
       </c>
       <c r="AX62" t="n">
         <v>11.5</v>
@@ -12556,11 +12556,11 @@
         <v>5.4</v>
       </c>
       <c r="BG62" t="n">
-        <v>29</v>
+        <v>4.9</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
         <v>2.62</v>
       </c>
       <c r="J63" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="K63" t="n">
         <v>3.45</v>
@@ -12699,52 +12699,52 @@
         <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ63" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR63" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS63" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AT63" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU63" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV63" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW63" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX63" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY63" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ63" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA63" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB63" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC63" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BD63" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE63" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF63" t="n">
         <v>1.01</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -12833,7 +12833,7 @@
         <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W64" t="n">
         <v>1.83</v>
@@ -12893,52 +12893,52 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ64" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR64" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS64" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT64" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU64" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV64" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW64" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX64" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY64" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ64" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA64" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB64" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC64" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD64" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE64" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF64" t="n">
         <v>1.01</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -13367,25 +13367,25 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G67" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="H67" t="n">
         <v>3.05</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K67" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L67" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M67" t="n">
         <v>1.02</v>
@@ -13397,106 +13397,106 @@
         <v>1.17</v>
       </c>
       <c r="P67" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="R67" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="S67" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="T67" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U67" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V67" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W67" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="X67" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y67" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z67" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA67" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB67" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC67" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD67" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE67" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF67" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG67" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI67" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK67" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL67" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM67" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN67" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO67" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP67" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ67" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AR67" t="n">
         <v>20</v>
       </c>
       <c r="AS67" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="AT67" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV67" t="n">
         <v>11</v>
       </c>
-      <c r="AU67" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>10</v>
-      </c>
       <c r="AW67" t="n">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="AX67" t="n">
         <v>13.5</v>
@@ -13505,32 +13505,32 @@
         <v>9</v>
       </c>
       <c r="AZ67" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BA67" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="BB67" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC67" t="n">
         <v>15.5</v>
       </c>
       <c r="BD67" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BE67" t="n">
-        <v>30</v>
+        <v>4.5</v>
       </c>
       <c r="BF67" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG67" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -13594,13 +13594,13 @@
         <v>3.6</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="R68" t="n">
         <v>2.06</v>
       </c>
       <c r="S68" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="T68" t="n">
         <v>1.42</v>
@@ -13609,7 +13609,7 @@
         <v>2.68</v>
       </c>
       <c r="V68" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W68" t="n">
         <v>2.24</v>
@@ -13687,7 +13687,7 @@
         <v>10.5</v>
       </c>
       <c r="AV68" t="n">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="AW68" t="n">
         <v>4</v>
@@ -13696,7 +13696,7 @@
         <v>13.5</v>
       </c>
       <c r="AY68" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ68" t="n">
         <v>11.5</v>
@@ -13705,7 +13705,7 @@
         <v>3.95</v>
       </c>
       <c r="BB68" t="n">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="BC68" t="n">
         <v>11.5</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -13767,7 +13767,7 @@
         <v>1000</v>
       </c>
       <c r="J69" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K69" t="n">
         <v>1000</v>
@@ -13794,7 +13794,7 @@
         <v>1.68</v>
       </c>
       <c r="S69" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T69" t="n">
         <v>1.01</v>
@@ -13806,7 +13806,7 @@
         <v>1.07</v>
       </c>
       <c r="W69" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="X69" t="n">
         <v>1000</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G71" t="n">
         <v>2.58</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -14337,22 +14337,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="G72" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H72" t="n">
         <v>5.1</v>
       </c>
       <c r="I72" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="K72" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -14388,7 +14388,7 @@
         <v>1.14</v>
       </c>
       <c r="W72" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="X72" t="n">
         <v>55</v>
@@ -14475,7 +14475,7 @@
         <v>2.26</v>
       </c>
       <c r="AZ72" t="n">
-        <v>2.4</v>
+        <v>12</v>
       </c>
       <c r="BA72" t="n">
         <v>2.56</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -14579,10 +14579,10 @@
         <v>2.18</v>
       </c>
       <c r="V73" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W73" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X73" t="n">
         <v>32</v>
@@ -14639,7 +14639,7 @@
         <v>44</v>
       </c>
       <c r="AP73" t="n">
-        <v>3.8</v>
+        <v>19</v>
       </c>
       <c r="AQ73" t="n">
         <v>3.75</v>
@@ -14666,16 +14666,16 @@
         <v>10</v>
       </c>
       <c r="AY73" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AZ73" t="n">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="BA73" t="n">
         <v>4</v>
       </c>
       <c r="BB73" t="n">
-        <v>3.65</v>
+        <v>14</v>
       </c>
       <c r="BC73" t="n">
         <v>12</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
         <v>12.5</v>
       </c>
       <c r="AH74" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI74" t="n">
         <v>55</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -15218,10 +15218,10 @@
         <v>80</v>
       </c>
       <c r="AO76" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AP76" t="n">
-        <v>40</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ76" t="n">
         <v>14.5</v>
@@ -15233,7 +15233,7 @@
         <v>11</v>
       </c>
       <c r="AT76" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU76" t="n">
         <v>14.5</v>
@@ -15245,10 +15245,10 @@
         <v>11.5</v>
       </c>
       <c r="AX76" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY76" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ76" t="n">
         <v>19</v>
@@ -15257,26 +15257,26 @@
         <v>21</v>
       </c>
       <c r="BB76" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC76" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC76" t="n">
+      <c r="BD76" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD76" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BE76" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF76" t="n">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG76" t="n">
         <v>2.96</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15316,7 @@
         <v>4.4</v>
       </c>
       <c r="I77" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J77" t="n">
         <v>4</v>
@@ -15361,7 +15361,7 @@
         <v>2.2</v>
       </c>
       <c r="X77" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y77" t="n">
         <v>26</v>
@@ -15373,13 +15373,13 @@
         <v>120</v>
       </c>
       <c r="AB77" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC77" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE77" t="n">
         <v>65</v>
@@ -15388,22 +15388,22 @@
         <v>15</v>
       </c>
       <c r="AG77" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH77" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI77" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ77" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK77" t="n">
         <v>19.5</v>
       </c>
       <c r="AL77" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM77" t="n">
         <v>85</v>
@@ -15418,13 +15418,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AR77" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS77" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT77" t="n">
         <v>9.199999999999999</v>
@@ -15436,7 +15436,7 @@
         <v>14.5</v>
       </c>
       <c r="AW77" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AX77" t="n">
         <v>9.800000000000001</v>
@@ -15448,7 +15448,7 @@
         <v>13</v>
       </c>
       <c r="BA77" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BB77" t="n">
         <v>15.5</v>
@@ -15460,17 +15460,17 @@
         <v>21</v>
       </c>
       <c r="BE77" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF77" t="n">
         <v>6.6</v>
       </c>
       <c r="BG77" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -15504,16 +15504,16 @@
         <v>2.54</v>
       </c>
       <c r="G78" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H78" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K78" t="n">
         <v>4.4</v>
@@ -15525,146 +15525,146 @@
         <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O78" t="n">
         <v>1.32</v>
       </c>
       <c r="P78" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="R78" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T78" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U78" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V78" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W78" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X78" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y78" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z78" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA78" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB78" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC78" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD78" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE78" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF78" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG78" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH78" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI78" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ78" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK78" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL78" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM78" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN78" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO78" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU78" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV78" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW78" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX78" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY78" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ78" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA78" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB78" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BC78" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BD78" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE78" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BF78" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG78" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
         <v>1.72</v>
       </c>
       <c r="S79" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T79" t="n">
         <v>1.4</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15892,7 @@
         <v>2.8</v>
       </c>
       <c r="G80" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H80" t="n">
         <v>2.46</v>
@@ -15901,10 +15901,10 @@
         <v>3.2</v>
       </c>
       <c r="J80" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="K80" t="n">
-        <v>85</v>
+        <v>4.3</v>
       </c>
       <c r="L80" t="n">
         <v>1.01</v>
@@ -15937,10 +15937,10 @@
         <v>1.01</v>
       </c>
       <c r="V80" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W80" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="X80" t="n">
         <v>1000</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16086,7 @@
         <v>1.39</v>
       </c>
       <c r="G81" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="H81" t="n">
         <v>5.6</v>
@@ -16134,7 +16134,7 @@
         <v>1.06</v>
       </c>
       <c r="W81" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="X81" t="n">
         <v>1000</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
         <v>18</v>
       </c>
       <c r="AA82" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB82" t="n">
         <v>16.5</v>
@@ -16406,10 +16406,10 @@
         <v>9.6</v>
       </c>
       <c r="AW82" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX82" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="AY82" t="n">
         <v>12</v>
@@ -16418,29 +16418,29 @@
         <v>13.5</v>
       </c>
       <c r="BA82" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB82" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC82" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF82" t="n">
         <v>6.8</v>
       </c>
-      <c r="BD82" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE82" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF82" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG82" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G83" t="n">
         <v>2.62</v>
@@ -16480,13 +16480,13 @@
         <v>3.15</v>
       </c>
       <c r="I83" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>3.2</v>
       </c>
       <c r="K83" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L83" t="n">
         <v>1.01</v>
@@ -16522,7 +16522,7 @@
         <v>1.4</v>
       </c>
       <c r="W83" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X83" t="n">
         <v>14</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -16665,58 +16665,58 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="G84" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H84" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="I84" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J84" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K84" t="n">
-        <v>110</v>
+        <v>4.2</v>
       </c>
       <c r="L84" t="n">
         <v>1.35</v>
       </c>
       <c r="M84" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N84" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O84" t="n">
         <v>1.34</v>
       </c>
       <c r="P84" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q84" t="n">
         <v>1.94</v>
       </c>
       <c r="R84" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S84" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T84" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U84" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V84" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W84" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X84" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -16859,13 +16859,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G85" t="n">
         <v>2.8</v>
       </c>
       <c r="H85" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="I85" t="n">
         <v>4.5</v>
@@ -16874,7 +16874,7 @@
         <v>2.86</v>
       </c>
       <c r="K85" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L85" t="n">
         <v>1.01</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
         <v>2.72</v>
       </c>
       <c r="G86" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H86" t="n">
         <v>2.52</v>
@@ -17101,10 +17101,10 @@
         <v>2.28</v>
       </c>
       <c r="V86" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W86" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X86" t="n">
         <v>18</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
         <v>1.4</v>
       </c>
       <c r="G89" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H89" t="n">
         <v>10.5</v>
@@ -17677,7 +17677,7 @@
         <v>3.65</v>
       </c>
       <c r="T89" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U89" t="n">
         <v>1.7</v>
@@ -17734,7 +17734,7 @@
         <v>48</v>
       </c>
       <c r="AM89" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN89" t="n">
         <v>7.4</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -17832,13 +17832,13 @@
         <v>1.31</v>
       </c>
       <c r="G90" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H90" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I90" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="J90" t="n">
         <v>5.2</v>
@@ -17850,149 +17850,149 @@
         <v>1.01</v>
       </c>
       <c r="M90" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N90" t="n">
         <v>5.3</v>
       </c>
       <c r="O90" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P90" t="n">
         <v>2.44</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R90" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="S90" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="T90" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U90" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V90" t="n">
         <v>1.06</v>
       </c>
       <c r="W90" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="X90" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL90" t="n">
         <v>34</v>
       </c>
-      <c r="Y90" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>85</v>
-      </c>
-      <c r="AE90" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI90" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ90" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK90" t="n">
+      <c r="AM90" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>330</v>
+      </c>
+      <c r="AP90" t="n">
         <v>20</v>
       </c>
-      <c r="AL90" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM90" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN90" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO90" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP90" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AQ90" t="n">
-        <v>2.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR90" t="n">
-        <v>2.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS90" t="n">
-        <v>2.34</v>
+        <v>10</v>
       </c>
       <c r="AT90" t="n">
-        <v>1.99</v>
+        <v>8.4</v>
       </c>
       <c r="AU90" t="n">
-        <v>2.06</v>
+        <v>10.5</v>
       </c>
       <c r="AV90" t="n">
-        <v>2.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW90" t="n">
-        <v>2.34</v>
+        <v>10</v>
       </c>
       <c r="AX90" t="n">
-        <v>1.97</v>
+        <v>7.6</v>
       </c>
       <c r="AY90" t="n">
-        <v>2.02</v>
+        <v>9</v>
       </c>
       <c r="AZ90" t="n">
-        <v>2.2</v>
+        <v>21</v>
       </c>
       <c r="BA90" t="n">
-        <v>2.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB90" t="n">
-        <v>2.34</v>
+        <v>9.6</v>
       </c>
       <c r="BC90" t="n">
-        <v>2.08</v>
+        <v>12</v>
       </c>
       <c r="BD90" t="n">
-        <v>2.22</v>
+        <v>8</v>
       </c>
       <c r="BE90" t="n">
-        <v>2.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF90" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG90" t="n">
-        <v>2.34</v>
+        <v>10</v>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
         <v>1.83</v>
       </c>
       <c r="V91" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W91" t="n">
         <v>1.23</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -18217,13 +18217,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G92" t="n">
         <v>3.2</v>
       </c>
       <c r="H92" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I92" t="n">
         <v>3.65</v>
@@ -18232,7 +18232,7 @@
         <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
@@ -18247,7 +18247,7 @@
         <v>1.34</v>
       </c>
       <c r="P92" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q92" t="n">
         <v>1.89</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -18414,16 +18414,16 @@
         <v>2.14</v>
       </c>
       <c r="G93" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H93" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I93" t="n">
         <v>3.8</v>
       </c>
       <c r="J93" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K93" t="n">
         <v>4.3</v>
@@ -18435,7 +18435,7 @@
         <v>1.06</v>
       </c>
       <c r="N93" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O93" t="n">
         <v>1.29</v>
@@ -18444,13 +18444,13 @@
         <v>1.93</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="R93" t="n">
         <v>1.36</v>
       </c>
       <c r="S93" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="T93" t="n">
         <v>1.7</v>
@@ -18462,7 +18462,7 @@
         <v>1.35</v>
       </c>
       <c r="W93" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X93" t="n">
         <v>18</v>
@@ -18528,7 +18528,7 @@
         <v>19</v>
       </c>
       <c r="AS93" t="n">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="AT93" t="n">
         <v>8.199999999999999</v>
@@ -18540,7 +18540,7 @@
         <v>11</v>
       </c>
       <c r="AW93" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AX93" t="n">
         <v>11.5</v>
@@ -18552,29 +18552,29 @@
         <v>13</v>
       </c>
       <c r="BA93" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BB93" t="n">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="BC93" t="n">
         <v>18</v>
       </c>
       <c r="BD93" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BE93" t="n">
-        <v>8.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="BF93" t="n">
         <v>13</v>
       </c>
       <c r="BG93" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -18608,7 +18608,7 @@
         <v>1.9</v>
       </c>
       <c r="G94" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H94" t="n">
         <v>3.2</v>
@@ -18656,7 +18656,7 @@
         <v>1.24</v>
       </c>
       <c r="W94" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X94" t="n">
         <v>1000</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -19029,16 +19029,16 @@
         <v>1.83</v>
       </c>
       <c r="R96" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S96" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T96" t="n">
         <v>1.67</v>
       </c>
       <c r="U96" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V96" t="n">
         <v>1.7</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -19211,28 +19211,28 @@
         <v>1.01</v>
       </c>
       <c r="N97" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="O97" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P97" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="R97" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S97" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="T97" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="U97" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="V97" t="n">
         <v>1.7</v>
@@ -19256,7 +19256,7 @@
         <v>15</v>
       </c>
       <c r="AC97" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD97" t="n">
         <v>14</v>
@@ -19295,25 +19295,25 @@
         <v>29</v>
       </c>
       <c r="AP97" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ97" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR97" t="n">
         <v>10.5</v>
       </c>
       <c r="AS97" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AT97" t="n">
         <v>9</v>
       </c>
       <c r="AU97" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV97" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW97" t="n">
         <v>19.5</v>
@@ -19325,32 +19325,32 @@
         <v>11</v>
       </c>
       <c r="AZ97" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA97" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB97" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC97" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BD97" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE97" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF97" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BG97" t="n">
         <v>17</v>
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -19438,7 +19438,7 @@
         <v>14.5</v>
       </c>
       <c r="Y98" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z98" t="n">
         <v>38</v>
@@ -19450,34 +19450,34 @@
         <v>9.4</v>
       </c>
       <c r="AC98" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD98" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH98" t="n">
         <v>21</v>
       </c>
-      <c r="AE98" t="n">
+      <c r="AI98" t="n">
         <v>75</v>
       </c>
-      <c r="AF98" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG98" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH98" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI98" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ98" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK98" t="n">
         <v>27</v>
       </c>
       <c r="AL98" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM98" t="n">
         <v>150</v>
@@ -19501,31 +19501,31 @@
         <v>1.01</v>
       </c>
       <c r="AT98" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU98" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV98" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW98" t="n">
         <v>1.01</v>
       </c>
       <c r="AX98" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY98" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ98" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA98" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB98" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC98" t="n">
         <v>17.5</v>
@@ -19540,11 +19540,11 @@
         <v>13</v>
       </c>
       <c r="BG98" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -19575,13 +19575,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G99" t="n">
         <v>3.65</v>
       </c>
       <c r="H99" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="I99" t="n">
         <v>3.2</v>
@@ -19590,13 +19590,13 @@
         <v>2.96</v>
       </c>
       <c r="K99" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L99" t="n">
         <v>1.38</v>
       </c>
       <c r="M99" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N99" t="n">
         <v>2.96</v>
@@ -19605,16 +19605,16 @@
         <v>1.43</v>
       </c>
       <c r="P99" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="R99" t="n">
         <v>1.22</v>
       </c>
       <c r="S99" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T99" t="n">
         <v>1.01</v>
@@ -19632,46 +19632,46 @@
         <v>1000</v>
       </c>
       <c r="Y99" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z99" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA99" t="n">
         <v>1000</v>
       </c>
       <c r="AB99" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC99" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD99" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE99" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF99" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG99" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH99" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI99" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ99" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK99" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL99" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM99" t="n">
         <v>1000</v>
@@ -19680,65 +19680,65 @@
         <v>1000</v>
       </c>
       <c r="AO99" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP99" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU99" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV99" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW99" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AX99" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY99" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ99" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA99" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB99" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BC99" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD99" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE99" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BF99" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BG99" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -19996,7 +19996,7 @@
         <v>1.83</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R101" t="n">
         <v>1.25</v>
@@ -20071,52 +20071,52 @@
         <v>1000</v>
       </c>
       <c r="AP101" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ101" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR101" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS101" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT101" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU101" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV101" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW101" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX101" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY101" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ101" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA101" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB101" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC101" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD101" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE101" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BF101" t="n">
         <v>1.01</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -20211,10 +20211,10 @@
         <v>2.58</v>
       </c>
       <c r="X102" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y102" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z102" t="n">
         <v>65</v>
@@ -20238,16 +20238,16 @@
         <v>11.5</v>
       </c>
       <c r="AG102" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI102" t="n">
         <v>85</v>
       </c>
       <c r="AJ102" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK102" t="n">
         <v>19</v>
@@ -20274,7 +20274,7 @@
         <v>40</v>
       </c>
       <c r="AS102" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT102" t="n">
         <v>8</v>
@@ -20286,7 +20286,7 @@
         <v>18.5</v>
       </c>
       <c r="AW102" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX102" t="n">
         <v>8.800000000000001</v>
@@ -20298,7 +20298,7 @@
         <v>18.5</v>
       </c>
       <c r="BA102" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB102" t="n">
         <v>11.5</v>
@@ -20307,20 +20307,20 @@
         <v>12.5</v>
       </c>
       <c r="BD102" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE102" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF102" t="n">
         <v>6.4</v>
       </c>
       <c r="BG102" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -20366,7 +20366,7 @@
         <v>3.85</v>
       </c>
       <c r="K103" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -20545,22 +20545,22 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="G104" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="H104" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I104" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J104" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K104" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="L104" t="n">
         <v>1.01</v>
@@ -20569,16 +20569,16 @@
         <v>1.01</v>
       </c>
       <c r="N104" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O104" t="n">
         <v>1.37</v>
       </c>
       <c r="P104" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="R104" t="n">
         <v>1.2</v>
@@ -20596,7 +20596,7 @@
         <v>1.2</v>
       </c>
       <c r="W104" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="X104" t="n">
         <v>1000</v>
@@ -20653,52 +20653,52 @@
         <v>1000</v>
       </c>
       <c r="AP104" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ104" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR104" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS104" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT104" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU104" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV104" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW104" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX104" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY104" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ104" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA104" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB104" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC104" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD104" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE104" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF104" t="n">
         <v>1.01</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -20966,7 +20966,7 @@
         <v>1.78</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R106" t="n">
         <v>1.3</v>
@@ -20978,13 +20978,13 @@
         <v>1.86</v>
       </c>
       <c r="U106" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V106" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W106" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X106" t="n">
         <v>14.5</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -21169,7 +21169,7 @@
         <v>2.92</v>
       </c>
       <c r="T107" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U107" t="n">
         <v>2.36</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -21321,10 +21321,10 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G108" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H108" t="n">
         <v>2.66</v>
@@ -21333,7 +21333,7 @@
         <v>3.35</v>
       </c>
       <c r="J108" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="K108" t="n">
         <v>5.7</v>
@@ -21345,22 +21345,22 @@
         <v>1.01</v>
       </c>
       <c r="N108" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P108" t="n">
         <v>2.96</v>
-      </c>
-      <c r="O108" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P108" t="n">
-        <v>1.54</v>
       </c>
       <c r="Q108" t="n">
         <v>1.29</v>
       </c>
       <c r="R108" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="S108" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="T108" t="n">
         <v>1.01</v>
@@ -21369,25 +21369,25 @@
         <v>1.01</v>
       </c>
       <c r="V108" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W108" t="n">
         <v>1.62</v>
       </c>
       <c r="X108" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y108" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z108" t="n">
         <v>1000</v>
       </c>
       <c r="AA108" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB108" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC108" t="n">
         <v>1000</v>
@@ -21396,95 +21396,95 @@
         <v>1000</v>
       </c>
       <c r="AE108" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF108" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG108" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH108" t="n">
         <v>1000</v>
       </c>
       <c r="AI108" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ108" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK108" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL108" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM108" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN108" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO108" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP108" t="n">
-        <v>38</v>
+        <v>1.87</v>
       </c>
       <c r="AQ108" t="n">
-        <v>20</v>
+        <v>1.83</v>
       </c>
       <c r="AR108" t="n">
-        <v>24</v>
+        <v>1.93</v>
       </c>
       <c r="AS108" t="n">
-        <v>36</v>
+        <v>1.87</v>
       </c>
       <c r="AT108" t="n">
-        <v>19</v>
+        <v>1.82</v>
       </c>
       <c r="AU108" t="n">
-        <v>9.6</v>
+        <v>1.93</v>
       </c>
       <c r="AV108" t="n">
-        <v>10.5</v>
+        <v>1.93</v>
       </c>
       <c r="AW108" t="n">
-        <v>18.5</v>
+        <v>1.83</v>
       </c>
       <c r="AX108" t="n">
-        <v>19</v>
+        <v>1.83</v>
       </c>
       <c r="AY108" t="n">
-        <v>9.6</v>
+        <v>1.75</v>
       </c>
       <c r="AZ108" t="n">
-        <v>9.800000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="BA108" t="n">
-        <v>16.5</v>
+        <v>1.83</v>
       </c>
       <c r="BB108" t="n">
-        <v>27</v>
+        <v>1.86</v>
       </c>
       <c r="BC108" t="n">
-        <v>15.5</v>
+        <v>1.81</v>
       </c>
       <c r="BD108" t="n">
-        <v>15</v>
+        <v>1.82</v>
       </c>
       <c r="BE108" t="n">
-        <v>21</v>
+        <v>1.86</v>
       </c>
       <c r="BF108" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BG108" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -21539,28 +21539,28 @@
         <v>1.01</v>
       </c>
       <c r="N109" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="O109" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P109" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="R109" t="n">
         <v>1.12</v>
       </c>
       <c r="S109" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T109" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U109" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V109" t="n">
         <v>1.32</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
         <v>2.06</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R111" t="n">
         <v>1.42</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -22503,13 +22503,13 @@
         <v>3.75</v>
       </c>
       <c r="L114" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M114" t="n">
         <v>1.05</v>
       </c>
       <c r="N114" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O114" t="n">
         <v>1.24</v>
@@ -22524,7 +22524,7 @@
         <v>1.51</v>
       </c>
       <c r="S114" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T114" t="n">
         <v>1.63</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
         <v>14.5</v>
       </c>
       <c r="G115" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="H115" t="n">
         <v>1.25</v>
@@ -22703,7 +22703,7 @@
         <v>1.03</v>
       </c>
       <c r="N115" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O115" t="n">
         <v>1.19</v>
@@ -22724,7 +22724,7 @@
         <v>2.2</v>
       </c>
       <c r="U115" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V115" t="n">
         <v>4.4</v>
@@ -22733,7 +22733,7 @@
         <v>1.06</v>
       </c>
       <c r="X115" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y115" t="n">
         <v>10.5</v>
@@ -22787,10 +22787,10 @@
         <v>4.7</v>
       </c>
       <c r="AP115" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ115" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR115" t="n">
         <v>7</v>
@@ -22799,10 +22799,10 @@
         <v>8.4</v>
       </c>
       <c r="AT115" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU115" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV115" t="n">
         <v>11</v>
@@ -22814,16 +22814,16 @@
         <v>6.6</v>
       </c>
       <c r="AY115" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AZ115" t="n">
-        <v>29</v>
+        <v>5.8</v>
       </c>
       <c r="BA115" t="n">
         <v>6</v>
       </c>
       <c r="BB115" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC115" t="n">
         <v>6.6</v>
@@ -22835,14 +22835,14 @@
         <v>6.6</v>
       </c>
       <c r="BF115" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG115" t="n">
         <v>3.4</v>
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -22897,10 +22897,10 @@
         <v>1.11</v>
       </c>
       <c r="N116" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="O116" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P116" t="n">
         <v>1.58</v>
@@ -22909,7 +22909,7 @@
         <v>2.42</v>
       </c>
       <c r="R116" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S116" t="n">
         <v>4.7</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -23076,7 +23076,7 @@
         <v>8.6</v>
       </c>
       <c r="I117" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J117" t="n">
         <v>4</v>
@@ -23127,7 +23127,7 @@
         <v>26</v>
       </c>
       <c r="Z117" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA117" t="n">
         <v>390</v>
@@ -23172,7 +23172,7 @@
         <v>15</v>
       </c>
       <c r="AO117" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AP117" t="n">
         <v>9.800000000000001</v>
@@ -23184,7 +23184,7 @@
         <v>4.3</v>
       </c>
       <c r="AS117" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT117" t="n">
         <v>5.4</v>
@@ -23208,7 +23208,7 @@
         <v>4.1</v>
       </c>
       <c r="BA117" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB117" t="n">
         <v>12</v>
@@ -23217,20 +23217,20 @@
         <v>17.5</v>
       </c>
       <c r="BD117" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE117" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF117" t="n">
         <v>9</v>
       </c>
       <c r="BG117" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -23279,10 +23279,10 @@
         <v>3.6</v>
       </c>
       <c r="L118" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M118" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N118" t="n">
         <v>2.44</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>
@@ -23473,152 +23473,152 @@
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P119" t="n">
         <v>1.24</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO119" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP119" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR119" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS119" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU119" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW119" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY119" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA119" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB119" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC119" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD119" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE119" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG119" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-04-04 19:06:14</t>
+          <t>2026-04-04 21:37:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
@@ -763,10 +763,10 @@
         <v>1.49</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
         <v>4.7</v>
@@ -790,31 +790,31 @@
         <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
         <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
         <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,43 +823,43 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -877,10 +877,10 @@
         <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
         <v>1.03</v>
@@ -889,22 +889,22 @@
         <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD2" t="n">
         <v>1.03</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>7</v>
@@ -1002,7 +1002,7 @@
         <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="U4" t="n">
         <v>2.48</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>85</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.33</v>
@@ -1363,16 +1363,16 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
         <v>1.38</v>
@@ -1426,7 +1426,7 @@
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ5" t="n">
         <v>55</v>
@@ -1438,25 +1438,25 @@
         <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
         <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT5" t="n">
         <v>11.5</v>
@@ -1468,41 +1468,41 @@
         <v>10</v>
       </c>
       <c r="AW5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX5" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
         <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD5" t="n">
         <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG5" t="n">
         <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>1.72</v>
       </c>
       <c r="I6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="J6" t="n">
         <v>3.9</v>
@@ -1581,7 +1581,7 @@
         <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1680,7 +1680,7 @@
         <v>18.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
         <v>17</v>
@@ -1689,14 +1689,14 @@
         <v>18.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG6" t="n">
         <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
         <v>3.6</v>
@@ -1751,10 +1751,10 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
         <v>1.78</v>
@@ -1763,10 +1763,10 @@
         <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
         <v>1.89</v>
@@ -1778,7 +1778,7 @@
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>2.44</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
         <v>3.8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2348,13 +2348,13 @@
         <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
         <v>1.3</v>
@@ -2417,7 +2417,7 @@
         <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>13</v>
@@ -2429,10 +2429,10 @@
         <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
@@ -2444,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
@@ -2453,7 +2453,7 @@
         <v>3.95</v>
       </c>
       <c r="BB10" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC10" t="n">
         <v>14</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
@@ -3321,7 +3321,7 @@
         <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="U15" t="n">
         <v>2.12</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>1.93</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
         <v>2.88</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H24" t="n">
         <v>2.56</v>
       </c>
-      <c r="G24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.28</v>
-      </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,22 +5049,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P24" t="n">
         <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R24" t="n">
         <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5073,10 +5073,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5610,19 @@
         <v>2.72</v>
       </c>
       <c r="G27" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H27" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I27" t="n">
         <v>3.15</v>
       </c>
       <c r="J27" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.28</v>
@@ -5631,7 +5631,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O27" t="n">
         <v>1.26</v>
@@ -5646,7 +5646,7 @@
         <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5658,7 +5658,7 @@
         <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G28" t="n">
         <v>3.3</v>
@@ -5825,28 +5825,28 @@
         <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P28" t="n">
         <v>2.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R28" t="n">
         <v>1.63</v>
       </c>
       <c r="S28" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U28" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V28" t="n">
         <v>1.74</v>
@@ -5867,10 +5867,10 @@
         <v>34</v>
       </c>
       <c r="AB28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD28" t="n">
         <v>13.5</v>
@@ -5882,7 +5882,7 @@
         <v>32</v>
       </c>
       <c r="AG28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH28" t="n">
         <v>17.5</v>
@@ -5894,7 +5894,7 @@
         <v>60</v>
       </c>
       <c r="AK28" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL28" t="n">
         <v>40</v>
@@ -5906,10 +5906,10 @@
         <v>23</v>
       </c>
       <c r="AO28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ28" t="n">
         <v>11.5</v>
@@ -5921,16 +5921,16 @@
         <v>4.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
         <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AX28" t="n">
         <v>20</v>
@@ -5945,7 +5945,7 @@
         <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC28" t="n">
         <v>4.4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.14</v>
       </c>
       <c r="G30" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H30" t="n">
         <v>3.2</v>
@@ -6219,28 +6219,28 @@
         <v>1.23</v>
       </c>
       <c r="P30" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V30" t="n">
         <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="K31" t="n">
-        <v>6.4</v>
+        <v>110</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6407,22 +6407,22 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
         <v>1.19</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
-        <v>2.24</v>
+        <v>1.19</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6431,10 +6431,10 @@
         <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -6604,19 +6604,19 @@
         <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
         <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -6771,46 +6771,46 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H33" t="n">
         <v>2.4</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="K33" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P33" t="n">
         <v>1.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G34" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>1.09</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="K34" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>1.34</v>
@@ -6998,10 +6998,10 @@
         <v>1.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
         <v>2.78</v>
@@ -7016,7 +7016,7 @@
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -7159,25 +7159,25 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G35" t="n">
         <v>4.4</v>
       </c>
       <c r="H35" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="I35" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>2.8</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M35" t="n">
         <v>1.05</v>
@@ -7192,13 +7192,13 @@
         <v>1.62</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R35" t="n">
         <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7207,13 +7207,13 @@
         <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W35" t="n">
         <v>1.29</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y35" t="n">
         <v>1000</v>
@@ -7267,7 +7267,7 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.03</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
         <v>1.79</v>
       </c>
       <c r="S36" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -7744,16 +7744,16 @@
         <v>2.02</v>
       </c>
       <c r="G38" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H38" t="n">
         <v>3.4</v>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K38" t="n">
         <v>4.1</v>
@@ -7768,7 +7768,7 @@
         <v>4.1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P38" t="n">
         <v>2.06</v>
@@ -7780,7 +7780,7 @@
         <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T38" t="n">
         <v>1.57</v>
@@ -7789,10 +7789,10 @@
         <v>2.06</v>
       </c>
       <c r="V38" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="X38" t="n">
         <v>22</v>
@@ -7849,7 +7849,7 @@
         <v>44</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ38" t="n">
         <v>11.5</v>
@@ -7861,10 +7861,10 @@
         <v>4</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.25</v>
+        <v>9.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="AV38" t="n">
         <v>3.45</v>
@@ -7876,7 +7876,7 @@
         <v>10.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ38" t="n">
         <v>3.5</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -7938,25 +7938,25 @@
         <v>1.95</v>
       </c>
       <c r="G39" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H39" t="n">
         <v>3.65</v>
       </c>
       <c r="I39" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K39" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N39" t="n">
         <v>4</v>
@@ -7965,7 +7965,7 @@
         <v>1.24</v>
       </c>
       <c r="P39" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q39" t="n">
         <v>1.65</v>
@@ -7974,7 +7974,7 @@
         <v>1.37</v>
       </c>
       <c r="S39" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -7983,10 +7983,10 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W39" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>2.42</v>
       </c>
       <c r="G40" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H40" t="n">
         <v>3.25</v>
@@ -8144,7 +8144,7 @@
         <v>3.15</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8156,7 +8156,7 @@
         <v>3.15</v>
       </c>
       <c r="O40" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P40" t="n">
         <v>1.72</v>
@@ -8177,13 +8177,13 @@
         <v>1.98</v>
       </c>
       <c r="V40" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
         <v>1.64</v>
       </c>
       <c r="X40" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y40" t="n">
         <v>12.5</v>
@@ -8201,7 +8201,7 @@
         <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE40" t="n">
         <v>50</v>
@@ -8237,7 +8237,7 @@
         <v>48</v>
       </c>
       <c r="AP40" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ40" t="n">
         <v>9.4</v>
@@ -8246,7 +8246,7 @@
         <v>18.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT40" t="n">
         <v>8</v>
@@ -8258,7 +8258,7 @@
         <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX40" t="n">
         <v>13</v>
@@ -8270,29 +8270,29 @@
         <v>16</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC40" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC40" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD40" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF40" t="n">
         <v>20</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -8347,13 +8347,13 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O41" t="n">
         <v>1.18</v>
       </c>
       <c r="P41" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q41" t="n">
         <v>1.18</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -8526,10 +8526,10 @@
         <v>1.94</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J42" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
         <v>3.8</v>
@@ -8541,28 +8541,28 @@
         <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O42" t="n">
         <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q42" t="n">
         <v>2.06</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T42" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="U42" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V42" t="n">
         <v>2</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -8714,13 +8714,13 @@
         <v>1.44</v>
       </c>
       <c r="G43" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H43" t="n">
         <v>8.4</v>
       </c>
       <c r="I43" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="J43" t="n">
         <v>4.5</v>
@@ -8735,34 +8735,34 @@
         <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
         <v>1.28</v>
       </c>
       <c r="P43" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S43" t="n">
         <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U43" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V43" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W43" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X43" t="n">
         <v>21</v>
@@ -8867,14 +8867,14 @@
         <v>6</v>
       </c>
       <c r="BF43" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG43" t="n">
         <v>6</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>1.99</v>
       </c>
       <c r="G44" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H44" t="n">
         <v>4.2</v>
@@ -8926,25 +8926,25 @@
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N44" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="O44" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P44" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T44" t="n">
         <v>1.71</v>
@@ -8959,7 +8959,7 @@
         <v>1.92</v>
       </c>
       <c r="X44" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y44" t="n">
         <v>17.5</v>
@@ -8995,7 +8995,7 @@
         <v>85</v>
       </c>
       <c r="AJ44" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK44" t="n">
         <v>28</v>
@@ -9022,7 +9022,7 @@
         <v>4.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT44" t="n">
         <v>7.6</v>
@@ -9046,7 +9046,7 @@
         <v>17</v>
       </c>
       <c r="BA44" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB44" t="n">
         <v>21</v>
@@ -9055,20 +9055,20 @@
         <v>20</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF44" t="n">
         <v>14.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -9204,7 +9204,7 @@
         <v>110</v>
       </c>
       <c r="AO45" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP45" t="n">
         <v>11.5</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
         <v>1.22</v>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q46" t="n">
         <v>1.61</v>
@@ -9332,7 +9332,7 @@
         <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G49" t="n">
         <v>3.15</v>
@@ -9884,7 +9884,7 @@
         <v>2.52</v>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J49" t="n">
         <v>3.45</v>
@@ -9917,13 +9917,13 @@
         <v>3.15</v>
       </c>
       <c r="T49" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="U49" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W49" t="n">
         <v>1.46</v>
@@ -9980,7 +9980,7 @@
         <v>34</v>
       </c>
       <c r="AO49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP49" t="n">
         <v>11.5</v>
@@ -10022,13 +10022,13 @@
         <v>4.3</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF49" t="n">
         <v>4.1</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -10072,10 +10072,10 @@
         <v>3.2</v>
       </c>
       <c r="G50" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H50" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="I50" t="n">
         <v>2.4</v>
@@ -10084,7 +10084,7 @@
         <v>3.45</v>
       </c>
       <c r="K50" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -10263,19 +10263,19 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G51" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="H51" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="I51" t="n">
         <v>2.02</v>
       </c>
       <c r="J51" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K51" t="n">
         <v>4.7</v>
@@ -10287,10 +10287,10 @@
         <v>1.02</v>
       </c>
       <c r="N51" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O51" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P51" t="n">
         <v>2.58</v>
@@ -10302,19 +10302,19 @@
         <v>1.64</v>
       </c>
       <c r="S51" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="T51" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U51" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V51" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W51" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="X51" t="n">
         <v>32</v>
@@ -10374,7 +10374,7 @@
         <v>20</v>
       </c>
       <c r="AQ51" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR51" t="n">
         <v>11.5</v>
@@ -10422,11 +10422,11 @@
         <v>20</v>
       </c>
       <c r="BG51" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -10457,22 +10457,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="G52" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="H52" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I52" t="n">
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10481,37 +10481,37 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="O52" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P52" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="R52" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="S52" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="T52" t="n">
         <v>1.68</v>
       </c>
       <c r="U52" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="V52" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W52" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="X52" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Y52" t="n">
         <v>85</v>
@@ -10526,7 +10526,7 @@
         <v>20</v>
       </c>
       <c r="AC52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD52" t="n">
         <v>65</v>
@@ -10559,7 +10559,7 @@
         <v>140</v>
       </c>
       <c r="AN52" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AO52" t="n">
         <v>190</v>
@@ -10580,7 +10580,7 @@
         <v>12</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AV52" t="n">
         <v>1.03</v>
@@ -10604,7 +10604,7 @@
         <v>8</v>
       </c>
       <c r="BC52" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD52" t="n">
         <v>1.03</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
         <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -10684,7 +10684,7 @@
         <v>2.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R53" t="n">
         <v>1.57</v>
@@ -10693,7 +10693,7 @@
         <v>2.04</v>
       </c>
       <c r="T53" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U53" t="n">
         <v>1.01</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -11045,10 +11045,10 @@
         <v>3.4</v>
       </c>
       <c r="H55" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I55" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J55" t="n">
         <v>3.35</v>
@@ -11060,10 +11060,10 @@
         <v>1.29</v>
       </c>
       <c r="M55" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N55" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="O55" t="n">
         <v>1.28</v>
@@ -11072,137 +11072,137 @@
         <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="R55" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="T55" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U55" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V55" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W55" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X55" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AA55" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL55" t="n">
         <v>46</v>
       </c>
-      <c r="AB55" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC55" t="n">
+      <c r="AM55" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT55" t="n">
         <v>11</v>
       </c>
-      <c r="AD55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG55" t="n">
+      <c r="AU55" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX55" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH55" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>15</v>
-      </c>
       <c r="AY55" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ55" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF55" t="n">
         <v>24</v>
       </c>
-      <c r="BB55" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>19</v>
-      </c>
       <c r="BG55" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11248,7 @@
         <v>3.9</v>
       </c>
       <c r="K56" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -11263,7 +11263,7 @@
         <v>1.22</v>
       </c>
       <c r="P56" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
         <v>1.66</v>
@@ -11275,7 +11275,7 @@
         <v>2.62</v>
       </c>
       <c r="T56" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U56" t="n">
         <v>2.08</v>
@@ -11371,7 +11371,7 @@
         <v>13</v>
       </c>
       <c r="AZ56" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA56" t="n">
         <v>21</v>
@@ -11389,14 +11389,14 @@
         <v>1.03</v>
       </c>
       <c r="BF56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG56" t="n">
         <v>7</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G57" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="H57" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="I57" t="n">
         <v>3</v>
@@ -11442,7 +11442,7 @@
         <v>3.85</v>
       </c>
       <c r="K57" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L57" t="n">
         <v>1.01</v>
@@ -11457,19 +11457,19 @@
         <v>1.16</v>
       </c>
       <c r="P57" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="R57" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="S57" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="T57" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U57" t="n">
         <v>2.5</v>
@@ -11478,119 +11478,119 @@
         <v>1.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="X57" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y57" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="Z57" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI57" t="n">
         <v>32</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AJ57" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM57" t="n">
         <v>55</v>
       </c>
-      <c r="AB57" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC57" t="n">
+      <c r="AN57" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AO57" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC57" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE57" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ57" t="n">
+      <c r="BD57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG57" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR57" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>10</v>
-      </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -11815,19 +11815,19 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G59" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H59" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
         <v>2.08</v>
       </c>
       <c r="J59" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K59" t="n">
         <v>4.1</v>
@@ -11842,7 +11842,7 @@
         <v>4.1</v>
       </c>
       <c r="O59" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P59" t="n">
         <v>2.08</v>
@@ -11866,7 +11866,7 @@
         <v>1.92</v>
       </c>
       <c r="W59" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X59" t="n">
         <v>20</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
         <v>4.8</v>
       </c>
       <c r="J60" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K60" t="n">
         <v>5.1</v>
@@ -12036,10 +12036,10 @@
         <v>2.22</v>
       </c>
       <c r="O60" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P60" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q60" t="n">
         <v>1.66</v>
@@ -12048,7 +12048,7 @@
         <v>1.36</v>
       </c>
       <c r="S60" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T60" t="n">
         <v>1.01</v>
@@ -12066,7 +12066,7 @@
         <v>1000</v>
       </c>
       <c r="Y60" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z60" t="n">
         <v>36</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
         <v>2.02</v>
       </c>
       <c r="J61" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K61" t="n">
         <v>4.2</v>
@@ -12233,10 +12233,10 @@
         <v>1.29</v>
       </c>
       <c r="P61" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R61" t="n">
         <v>1.36</v>
@@ -12248,7 +12248,7 @@
         <v>1.76</v>
       </c>
       <c r="U61" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V61" t="n">
         <v>1.98</v>
@@ -12281,7 +12281,7 @@
         <v>22</v>
       </c>
       <c r="AF61" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG61" t="n">
         <v>21</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
         <v>29</v>
       </c>
       <c r="Z62" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA62" t="n">
         <v>120</v>
@@ -12466,7 +12466,7 @@
         <v>15.5</v>
       </c>
       <c r="AC62" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD62" t="n">
         <v>23</v>
@@ -12475,10 +12475,10 @@
         <v>60</v>
       </c>
       <c r="AF62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG62" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH62" t="n">
         <v>19.5</v>
@@ -12511,10 +12511,10 @@
         <v>21</v>
       </c>
       <c r="AR62" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT62" t="n">
         <v>11.5</v>
@@ -12526,7 +12526,7 @@
         <v>17</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AX62" t="n">
         <v>11.5</v>
@@ -12538,7 +12538,7 @@
         <v>14.5</v>
       </c>
       <c r="BA62" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB62" t="n">
         <v>16</v>
@@ -12547,20 +12547,20 @@
         <v>14</v>
       </c>
       <c r="BD62" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE62" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF62" t="n">
         <v>5.4</v>
       </c>
       <c r="BG62" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
         <v>3.8</v>
       </c>
       <c r="H63" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I63" t="n">
         <v>2.62</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.72</v>
+        <v>1.09</v>
       </c>
       <c r="G64" t="n">
         <v>2.2</v>
@@ -12794,7 +12794,7 @@
         <v>3.95</v>
       </c>
       <c r="I64" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J64" t="n">
         <v>3.35</v>
@@ -12815,7 +12815,7 @@
         <v>1.38</v>
       </c>
       <c r="P64" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q64" t="n">
         <v>2.06</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -13012,7 +13012,7 @@
         <v>2.06</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R65" t="n">
         <v>1.41</v>
@@ -13036,7 +13036,7 @@
         <v>20</v>
       </c>
       <c r="Y65" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z65" t="n">
         <v>24</v>
@@ -13096,7 +13096,7 @@
         <v>20</v>
       </c>
       <c r="AS65" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT65" t="n">
         <v>10</v>
@@ -13108,7 +13108,7 @@
         <v>12</v>
       </c>
       <c r="AW65" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX65" t="n">
         <v>14</v>
@@ -13120,16 +13120,16 @@
         <v>14</v>
       </c>
       <c r="BA65" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB65" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC65" t="n">
         <v>21</v>
       </c>
       <c r="BD65" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE65" t="n">
         <v>10</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -13182,13 +13182,13 @@
         <v>5.9</v>
       </c>
       <c r="I66" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J66" t="n">
         <v>4.9</v>
       </c>
       <c r="K66" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L66" t="n">
         <v>1.21</v>
@@ -13203,7 +13203,7 @@
         <v>1.14</v>
       </c>
       <c r="P66" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q66" t="n">
         <v>1.46</v>
@@ -13236,19 +13236,19 @@
         <v>70</v>
       </c>
       <c r="AA66" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB66" t="n">
         <v>16.5</v>
       </c>
       <c r="AC66" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD66" t="n">
         <v>28</v>
       </c>
       <c r="AE66" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF66" t="n">
         <v>15</v>
@@ -13281,16 +13281,16 @@
         <v>60</v>
       </c>
       <c r="AP66" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ66" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR66" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS66" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT66" t="n">
         <v>10.5</v>
@@ -13314,7 +13314,7 @@
         <v>14</v>
       </c>
       <c r="BA66" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB66" t="n">
         <v>13.5</v>
@@ -13326,17 +13326,17 @@
         <v>19</v>
       </c>
       <c r="BE66" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF66" t="n">
         <v>4.1</v>
       </c>
       <c r="BG66" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
         <v>3.05</v>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J67" t="n">
         <v>3.95</v>
@@ -13403,10 +13403,10 @@
         <v>1.54</v>
       </c>
       <c r="R67" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S67" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="T67" t="n">
         <v>1.53</v>
@@ -13415,10 +13415,10 @@
         <v>2.42</v>
       </c>
       <c r="V67" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W67" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X67" t="n">
         <v>32</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -13600,16 +13600,16 @@
         <v>2.06</v>
       </c>
       <c r="S68" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="T68" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="U68" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="V68" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W68" t="n">
         <v>2.24</v>
@@ -13624,7 +13624,7 @@
         <v>60</v>
       </c>
       <c r="AA68" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB68" t="n">
         <v>25</v>
@@ -13669,25 +13669,25 @@
         <v>25</v>
       </c>
       <c r="AP68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS68" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ68" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AT68" t="n">
-        <v>3.75</v>
+        <v>15</v>
       </c>
       <c r="AU68" t="n">
         <v>10.5</v>
       </c>
       <c r="AV68" t="n">
-        <v>14.5</v>
+        <v>3.7</v>
       </c>
       <c r="AW68" t="n">
         <v>4</v>
@@ -13696,16 +13696,16 @@
         <v>13.5</v>
       </c>
       <c r="AY68" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ68" t="n">
         <v>11.5</v>
       </c>
       <c r="BA68" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB68" t="n">
-        <v>15.5</v>
+        <v>3.75</v>
       </c>
       <c r="BC68" t="n">
         <v>11.5</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
         <v>1.33</v>
       </c>
       <c r="G69" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H69" t="n">
         <v>1.09</v>
@@ -13767,7 +13767,7 @@
         <v>1000</v>
       </c>
       <c r="J69" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K69" t="n">
         <v>1000</v>
@@ -13806,7 +13806,7 @@
         <v>1.07</v>
       </c>
       <c r="W69" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X69" t="n">
         <v>1000</v>
@@ -13863,52 +13863,52 @@
         <v>1000</v>
       </c>
       <c r="AP69" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AQ69" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AR69" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS69" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT69" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU69" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV69" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AW69" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX69" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY69" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ69" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA69" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB69" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC69" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD69" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BE69" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF69" t="n">
         <v>1.01</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -13949,16 +13949,16 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G70" t="n">
         <v>3.05</v>
       </c>
       <c r="H70" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J70" t="n">
         <v>3.85</v>
@@ -13967,13 +13967,13 @@
         <v>4.5</v>
       </c>
       <c r="L70" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M70" t="n">
         <v>1.02</v>
       </c>
       <c r="N70" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O70" t="n">
         <v>1.18</v>
@@ -13982,13 +13982,13 @@
         <v>2.5</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R70" t="n">
         <v>1.61</v>
       </c>
       <c r="S70" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T70" t="n">
         <v>1.51</v>
@@ -13997,7 +13997,7 @@
         <v>2.58</v>
       </c>
       <c r="V70" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W70" t="n">
         <v>1.48</v>
@@ -14012,7 +14012,7 @@
         <v>21</v>
       </c>
       <c r="AA70" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB70" t="n">
         <v>20</v>
@@ -14048,13 +14048,13 @@
         <v>34</v>
       </c>
       <c r="AM70" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN70" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP70" t="n">
         <v>21</v>
@@ -14066,7 +14066,7 @@
         <v>16.5</v>
       </c>
       <c r="AS70" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT70" t="n">
         <v>15</v>
@@ -14093,13 +14093,13 @@
         <v>21</v>
       </c>
       <c r="BB70" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC70" t="n">
         <v>20</v>
       </c>
       <c r="BD70" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE70" t="n">
         <v>40</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
         <v>3</v>
       </c>
       <c r="J71" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K71" t="n">
         <v>4.5</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -14361,13 +14361,13 @@
         <v>1.01</v>
       </c>
       <c r="N72" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="O72" t="n">
         <v>1.1</v>
       </c>
       <c r="P72" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q72" t="n">
         <v>1.32</v>
@@ -14445,28 +14445,28 @@
         <v>50</v>
       </c>
       <c r="AP72" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ72" t="n">
         <v>2.52</v>
       </c>
-      <c r="AQ72" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AR72" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AS72" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AU72" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AV72" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AW72" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AX72" t="n">
         <v>10</v>
@@ -14481,7 +14481,7 @@
         <v>2.56</v>
       </c>
       <c r="BB72" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BC72" t="n">
         <v>10</v>
@@ -14490,7 +14490,7 @@
         <v>16</v>
       </c>
       <c r="BE72" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BF72" t="n">
         <v>3.35</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -14531,19 +14531,19 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G73" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H73" t="n">
         <v>4.3</v>
       </c>
       <c r="I73" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J73" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
         <v>4.8</v>
@@ -14576,10 +14576,10 @@
         <v>1.5</v>
       </c>
       <c r="U73" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V73" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W73" t="n">
         <v>2.12</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -14767,10 +14767,10 @@
         <v>2.1</v>
       </c>
       <c r="T74" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U74" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="V74" t="n">
         <v>1.19</v>
@@ -14851,7 +14851,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV74" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW74" t="n">
         <v>4.7</v>
@@ -14869,7 +14869,7 @@
         <v>4.7</v>
       </c>
       <c r="BB74" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BC74" t="n">
         <v>11.5</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -15116,19 +15116,19 @@
         <v>9</v>
       </c>
       <c r="G76" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H76" t="n">
         <v>1.32</v>
       </c>
       <c r="I76" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J76" t="n">
         <v>6.4</v>
       </c>
       <c r="K76" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L76" t="n">
         <v>1.01</v>
@@ -15146,10 +15146,10 @@
         <v>3.55</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="R76" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S76" t="n">
         <v>1.81</v>
@@ -15161,10 +15161,10 @@
         <v>2.32</v>
       </c>
       <c r="V76" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="W76" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X76" t="n">
         <v>55</v>
@@ -15218,10 +15218,10 @@
         <v>80</v>
       </c>
       <c r="AO76" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AP76" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ76" t="n">
         <v>14.5</v>
@@ -15233,7 +15233,7 @@
         <v>11</v>
       </c>
       <c r="AT76" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU76" t="n">
         <v>14.5</v>
@@ -15245,10 +15245,10 @@
         <v>11.5</v>
       </c>
       <c r="AX76" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY76" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AZ76" t="n">
         <v>19</v>
@@ -15257,26 +15257,26 @@
         <v>21</v>
       </c>
       <c r="BB76" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC76" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD76" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE76" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF76" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG76" t="n">
         <v>2.96</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -15501,34 +15501,34 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G78" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H78" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I78" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J78" t="n">
         <v>3.2</v>
       </c>
-      <c r="J78" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K78" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L78" t="n">
         <v>1.01</v>
       </c>
       <c r="M78" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N78" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="O78" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P78" t="n">
         <v>1.8</v>
@@ -15537,10 +15537,10 @@
         <v>1.99</v>
       </c>
       <c r="R78" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S78" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="T78" t="n">
         <v>1.65</v>
@@ -15552,7 +15552,7 @@
         <v>1.47</v>
       </c>
       <c r="W78" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X78" t="n">
         <v>16</v>
@@ -15618,7 +15618,7 @@
         <v>14</v>
       </c>
       <c r="AS78" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AT78" t="n">
         <v>8</v>
@@ -15630,7 +15630,7 @@
         <v>9.4</v>
       </c>
       <c r="AW78" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX78" t="n">
         <v>13</v>
@@ -15642,19 +15642,19 @@
         <v>12.5</v>
       </c>
       <c r="BA78" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB78" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BC78" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD78" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE78" t="n">
-        <v>70</v>
+        <v>1.03</v>
       </c>
       <c r="BF78" t="n">
         <v>20</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -15892,16 +15892,16 @@
         <v>2.8</v>
       </c>
       <c r="G80" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H80" t="n">
         <v>2.46</v>
       </c>
       <c r="I80" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J80" t="n">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="K80" t="n">
         <v>4.3</v>
@@ -15937,10 +15937,10 @@
         <v>1.01</v>
       </c>
       <c r="V80" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W80" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="X80" t="n">
         <v>1000</v>
@@ -15997,52 +15997,52 @@
         <v>1000</v>
       </c>
       <c r="AP80" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ80" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR80" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS80" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT80" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU80" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV80" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW80" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX80" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY80" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ80" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA80" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB80" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC80" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD80" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE80" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF80" t="n">
         <v>1.01</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -16191,52 +16191,52 @@
         <v>1000</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF81" t="n">
         <v>1.01</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -16474,16 +16474,16 @@
         <v>2.44</v>
       </c>
       <c r="G83" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="H83" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J83" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I83" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J83" t="n">
-        <v>3.2</v>
       </c>
       <c r="K83" t="n">
         <v>3.45</v>
@@ -16504,7 +16504,7 @@
         <v>1.73</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R83" t="n">
         <v>1.27</v>
@@ -16519,16 +16519,16 @@
         <v>1.99</v>
       </c>
       <c r="V83" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W83" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="X83" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y83" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z83" t="n">
         <v>27</v>
@@ -16537,34 +16537,34 @@
         <v>65</v>
       </c>
       <c r="AB83" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC83" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD83" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE83" t="n">
         <v>55</v>
       </c>
       <c r="AF83" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG83" t="n">
         <v>14.5</v>
       </c>
       <c r="AH83" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI83" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ83" t="n">
         <v>46</v>
       </c>
       <c r="AK83" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL83" t="n">
         <v>60</v>
@@ -16585,25 +16585,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR83" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="AS83" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT83" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU83" t="n">
         <v>6.6</v>
       </c>
       <c r="AV83" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW83" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="AX83" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY83" t="n">
         <v>10.5</v>
@@ -16612,29 +16612,29 @@
         <v>16.5</v>
       </c>
       <c r="BA83" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB83" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BC83" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BD83" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BE83" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF83" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BG83" t="n">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -16665,10 +16665,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G84" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H84" t="n">
         <v>2.2</v>
@@ -16695,7 +16695,7 @@
         <v>1.34</v>
       </c>
       <c r="P84" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q84" t="n">
         <v>1.94</v>
@@ -16713,7 +16713,7 @@
         <v>1.84</v>
       </c>
       <c r="V84" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W84" t="n">
         <v>1.31</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -17447,7 +17447,7 @@
         <v>2.84</v>
       </c>
       <c r="H88" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I88" t="n">
         <v>3.25</v>
@@ -17489,7 +17489,7 @@
         <v>1.9</v>
       </c>
       <c r="V88" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W88" t="n">
         <v>1.54</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -18220,19 +18220,19 @@
         <v>2.48</v>
       </c>
       <c r="G92" t="n">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="H92" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="I92" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J92" t="n">
         <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
@@ -18241,16 +18241,16 @@
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O92" t="n">
         <v>1.34</v>
       </c>
       <c r="P92" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R92" t="n">
         <v>1.24</v>
@@ -18265,10 +18265,10 @@
         <v>1.01</v>
       </c>
       <c r="V92" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W92" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="X92" t="n">
         <v>1000</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
         <v>3.2</v>
       </c>
       <c r="I93" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>3.35</v>
@@ -18462,7 +18462,7 @@
         <v>1.35</v>
       </c>
       <c r="W93" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X93" t="n">
         <v>18</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -18826,7 +18826,7 @@
         <v>2.78</v>
       </c>
       <c r="O95" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P95" t="n">
         <v>1.75</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -19211,16 +19211,16 @@
         <v>1.01</v>
       </c>
       <c r="N97" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O97" t="n">
         <v>1.38</v>
       </c>
       <c r="P97" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="R97" t="n">
         <v>1.22</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19384,7 @@
         <v>1.91</v>
       </c>
       <c r="G98" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H98" t="n">
         <v>4.1</v>
@@ -19432,7 +19432,7 @@
         <v>1.25</v>
       </c>
       <c r="W98" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X98" t="n">
         <v>14.5</v>
@@ -19528,23 +19528,23 @@
         <v>20</v>
       </c>
       <c r="BC98" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD98" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE98" t="n">
         <v>1.01</v>
       </c>
       <c r="BF98" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG98" t="n">
         <v>55</v>
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -20157,7 +20157,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G102" t="n">
         <v>1.64</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -20354,10 +20354,10 @@
         <v>2.24</v>
       </c>
       <c r="G103" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H103" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I103" t="n">
         <v>3.45</v>
@@ -20366,7 +20366,7 @@
         <v>3.85</v>
       </c>
       <c r="K103" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
         <v>1.01</v>
       </c>
       <c r="N104" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O104" t="n">
         <v>1.37</v>
@@ -20578,7 +20578,7 @@
         <v>1.71</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="R104" t="n">
         <v>1.2</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -20948,7 +20948,7 @@
         <v>3.15</v>
       </c>
       <c r="K106" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L106" t="n">
         <v>1.01</v>
@@ -20984,7 +20984,7 @@
         <v>1.27</v>
       </c>
       <c r="W106" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X106" t="n">
         <v>14.5</v>
@@ -21032,7 +21032,7 @@
         <v>42</v>
       </c>
       <c r="AM106" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN106" t="n">
         <v>19</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -21321,22 +21321,22 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G108" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="H108" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I108" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="J108" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="K108" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="L108" t="n">
         <v>1.01</v>
@@ -21345,146 +21345,146 @@
         <v>1.01</v>
       </c>
       <c r="N108" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="O108" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P108" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="R108" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="S108" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="T108" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="U108" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="V108" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W108" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X108" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Y108" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ108" t="n">
         <v>36</v>
       </c>
-      <c r="Z108" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA108" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB108" t="n">
+      <c r="AK108" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE108" t="n">
         <v>32</v>
       </c>
-      <c r="AC108" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD108" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE108" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF108" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG108" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH108" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI108" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ108" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK108" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL108" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM108" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN108" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO108" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP108" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AQ108" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR108" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS108" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AT108" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AU108" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AV108" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AW108" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX108" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY108" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AZ108" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BA108" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BB108" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BC108" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BD108" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BE108" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BF108" t="n">
-        <v>1.66</v>
+        <v>7.6</v>
       </c>
       <c r="BG108" t="n">
-        <v>1.72</v>
+        <v>9.6</v>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -21557,10 +21557,10 @@
         <v>5.9</v>
       </c>
       <c r="T109" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U109" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="V109" t="n">
         <v>1.32</v>
@@ -21623,62 +21623,62 @@
         <v>1000</v>
       </c>
       <c r="AP109" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AU109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AV109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AW109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AX109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AY109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AZ109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BA109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BB109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BC109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BD109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BE109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BF109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG109" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -21745,7 +21745,7 @@
         <v>1.75</v>
       </c>
       <c r="R110" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S110" t="n">
         <v>2.92</v>
@@ -21763,7 +21763,7 @@
         <v>1.73</v>
       </c>
       <c r="X110" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y110" t="n">
         <v>15.5</v>
@@ -21823,10 +21823,10 @@
         <v>13</v>
       </c>
       <c r="AR110" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS110" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT110" t="n">
         <v>10</v>
@@ -21838,7 +21838,7 @@
         <v>12.5</v>
       </c>
       <c r="AW110" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AX110" t="n">
         <v>13</v>
@@ -21850,29 +21850,29 @@
         <v>14</v>
       </c>
       <c r="BA110" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB110" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC110" t="n">
         <v>19</v>
       </c>
       <c r="BD110" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE110" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF110" t="n">
         <v>12.5</v>
       </c>
       <c r="BG110" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -22300,7 +22300,7 @@
         <v>3.3</v>
       </c>
       <c r="I113" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J113" t="n">
         <v>3.1</v>
@@ -22447,14 +22447,14 @@
         <v>42</v>
       </c>
       <c r="BF113" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BG113" t="n">
         <v>44</v>
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -22688,10 +22688,10 @@
         <v>1.25</v>
       </c>
       <c r="I115" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="J115" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K115" t="n">
         <v>7.2</v>
@@ -22703,7 +22703,7 @@
         <v>1.03</v>
       </c>
       <c r="N115" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O115" t="n">
         <v>1.19</v>
@@ -22724,25 +22724,25 @@
         <v>2.2</v>
       </c>
       <c r="U115" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V115" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="W115" t="n">
         <v>1.06</v>
       </c>
       <c r="X115" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y115" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA115" t="n">
         <v>10.5</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>11</v>
       </c>
       <c r="AB115" t="n">
         <v>55</v>
@@ -22751,40 +22751,40 @@
         <v>15.5</v>
       </c>
       <c r="AD115" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE115" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF115" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AG115" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AH115" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI115" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ115" t="n">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AK115" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AL115" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AM115" t="n">
         <v>220</v>
       </c>
       <c r="AN115" t="n">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="AO115" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AP115" t="n">
         <v>21</v>
@@ -22799,10 +22799,10 @@
         <v>8.4</v>
       </c>
       <c r="AT115" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="AU115" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV115" t="n">
         <v>11</v>
@@ -22811,38 +22811,38 @@
         <v>13</v>
       </c>
       <c r="AX115" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AY115" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ115" t="n">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="BA115" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB115" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC115" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BD115" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BE115" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BF115" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG115" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -22873,16 +22873,16 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G116" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="H116" t="n">
         <v>2.38</v>
       </c>
       <c r="I116" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="J116" t="n">
         <v>3.05</v>
@@ -22921,10 +22921,10 @@
         <v>1.84</v>
       </c>
       <c r="V116" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W116" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X116" t="n">
         <v>11</v>
@@ -22933,10 +22933,10 @@
         <v>8.6</v>
       </c>
       <c r="Z116" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA116" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB116" t="n">
         <v>12</v>
@@ -22945,10 +22945,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD116" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE116" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF116" t="n">
         <v>26</v>
@@ -22960,7 +22960,7 @@
         <v>25</v>
       </c>
       <c r="AI116" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ116" t="n">
         <v>80</v>
@@ -22978,10 +22978,10 @@
         <v>70</v>
       </c>
       <c r="AO116" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP116" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ116" t="n">
         <v>6.4</v>
@@ -22990,7 +22990,7 @@
         <v>11.5</v>
       </c>
       <c r="AS116" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT116" t="n">
         <v>8.800000000000001</v>
@@ -23002,7 +23002,7 @@
         <v>9.4</v>
       </c>
       <c r="AW116" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX116" t="n">
         <v>17</v>
@@ -23014,29 +23014,29 @@
         <v>18</v>
       </c>
       <c r="BA116" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB116" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG116" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC116" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD116" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE116" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF116" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG116" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -23193,10 +23193,10 @@
         <v>8.6</v>
       </c>
       <c r="AV117" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW117" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX117" t="n">
         <v>6.8</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -23318,7 +23318,7 @@
         <v>11.5</v>
       </c>
       <c r="Y118" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z118" t="n">
         <v>42</v>
@@ -23339,10 +23339,10 @@
         <v>100</v>
       </c>
       <c r="AF118" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG118" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH118" t="n">
         <v>29</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>
@@ -23563,52 +23563,52 @@
         <v>1000</v>
       </c>
       <c r="AP119" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ119" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR119" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS119" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT119" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU119" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV119" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW119" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX119" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY119" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ119" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA119" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB119" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC119" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD119" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE119" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF119" t="n">
         <v>1.01</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-04-04 21:37:35</t>
+          <t>2026-04-05 00:06:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
@@ -787,7 +787,7 @@
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
         <v>1.58</v>
@@ -796,13 +796,13 @@
         <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
@@ -868,13 +868,13 @@
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AT2" t="n">
         <v>6.6</v>
@@ -883,10 +883,10 @@
         <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AX2" t="n">
         <v>6.2</v>
@@ -898,7 +898,7 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="BB2" t="n">
         <v>7.6</v>
@@ -907,20 +907,20 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="BF2" t="n">
         <v>3.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>85</v>
+        <v>2.86</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="G3" t="n">
         <v>2.32</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>3.85</v>
@@ -1369,13 +1369,13 @@
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
         <v>3.25</v>
@@ -1387,7 +1387,7 @@
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
         <v>1.42</v>
@@ -1399,7 +1399,7 @@
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
         <v>34</v>
@@ -1423,7 +1423,7 @@
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="H6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="I6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="J6" t="n">
         <v>3.95</v>
@@ -1575,16 +1575,16 @@
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
         <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -1593,7 +1593,7 @@
         <v>7.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" t="n">
         <v>18</v>
@@ -1605,13 +1605,13 @@
         <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE6" t="n">
         <v>19.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG6" t="n">
         <v>23</v>
@@ -1662,7 +1662,7 @@
         <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
         <v>40</v>
@@ -1677,26 +1677,26 @@
         <v>36</v>
       </c>
       <c r="BB6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC6" t="n">
         <v>80</v>
       </c>
       <c r="BD6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BE6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BF6" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BG6" t="n">
         <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
         <v>3.6</v>
@@ -1739,7 +1739,7 @@
         <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>3.4</v>
@@ -1763,7 +1763,7 @@
         <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
         <v>4.1</v>
@@ -1778,7 +1778,7 @@
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -1936,19 +1936,19 @@
         <v>2.72</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
         <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="P8" t="n">
         <v>1.58</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
         <v>5.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J9" t="n">
         <v>2.92</v>
@@ -2154,7 +2154,7 @@
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,7 +2163,7 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
         <v>1.23</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -2351,10 +2351,10 @@
         <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
         <v>1.3</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
         <v>1.13</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q11" t="n">
         <v>1.13</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
         <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
         <v>2.06</v>
@@ -2739,10 +2739,10 @@
         <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
         <v>1.62</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>2.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
@@ -2918,7 +2918,7 @@
         <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
         <v>2.06</v>
@@ -2927,10 +2927,10 @@
         <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
         <v>1.65</v>
@@ -2942,7 +2942,7 @@
         <v>1.83</v>
       </c>
       <c r="W13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3032,29 +3032,29 @@
         <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>23</v>
+        <v>3.85</v>
       </c>
       <c r="BG13" t="n">
         <v>10.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
         <v>1.54</v>
       </c>
       <c r="W14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
         <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
         <v>2.58</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
         <v>42</v>
@@ -3590,7 +3590,7 @@
         <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
@@ -3617,7 +3617,7 @@
         <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.3</v>
+        <v>42</v>
       </c>
       <c r="BC16" t="n">
         <v>27</v>
@@ -3626,7 +3626,7 @@
         <v>38</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF16" t="n">
         <v>27</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -3885,13 +3885,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q18" t="n">
         <v>1.02</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O19" t="n">
         <v>1.19</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -4449,13 +4449,13 @@
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -4467,13 +4467,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="O21" t="n">
         <v>1.01</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q21" t="n">
         <v>1.29</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="H22" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4664,19 +4664,19 @@
         <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P22" t="n">
         <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>4.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I23" t="n">
         <v>2.4</v>
@@ -4846,7 +4846,7 @@
         <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4948,53 +4948,53 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="BF23" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="BG23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G24" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="H24" t="n">
         <v>2.56</v>
@@ -5040,13 +5040,13 @@
         <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
         <v>4.3</v>
@@ -5076,7 +5076,7 @@
         <v>1.55</v>
       </c>
       <c r="W24" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="X24" t="n">
         <v>21</v>
@@ -5142,7 +5142,7 @@
         <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -5166,19 +5166,19 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BC24" t="n">
         <v>21</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BF24" t="n">
         <v>15.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -5243,22 +5243,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="O25" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H26" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K26" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,22 +5437,22 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>5.8</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R26" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="S26" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -5461,10 +5461,10 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>2.72</v>
       </c>
       <c r="G27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H27" t="n">
         <v>2.44</v>
@@ -5646,7 +5646,7 @@
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
         <v>1.55</v>
@@ -5748,19 +5748,19 @@
         <v>11.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
         <v>1.03</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>17.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
         <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L28" t="n">
         <v>1.25</v>
@@ -5834,7 +5834,7 @@
         <v>2.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R28" t="n">
         <v>1.63</v>
@@ -5846,13 +5846,13 @@
         <v>1.54</v>
       </c>
       <c r="U28" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V28" t="n">
         <v>1.74</v>
       </c>
       <c r="W28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X28" t="n">
         <v>28</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.14</v>
       </c>
       <c r="G30" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="H30" t="n">
         <v>3.2</v>
@@ -6228,7 +6228,7 @@
         <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
         <v>1.53</v>
@@ -6237,10 +6237,10 @@
         <v>2.16</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W30" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -6255,25 +6255,25 @@
         <v>70</v>
       </c>
       <c r="AB30" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC30" t="n">
         <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE30" t="n">
         <v>44</v>
       </c>
       <c r="AF30" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI30" t="n">
         <v>48</v>
@@ -6291,7 +6291,7 @@
         <v>85</v>
       </c>
       <c r="AN30" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AO30" t="n">
         <v>34</v>
@@ -6306,7 +6306,7 @@
         <v>18.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT30" t="n">
         <v>9.199999999999999</v>
@@ -6318,7 +6318,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX30" t="n">
         <v>11.5</v>
@@ -6330,7 +6330,7 @@
         <v>11.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB30" t="n">
         <v>20</v>
@@ -6339,20 +6339,20 @@
         <v>15.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF30" t="n">
         <v>9.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>19.5</v>
+        <v>3.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         <v>1.03</v>
       </c>
       <c r="K31" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
         <v>1.03</v>
       </c>
       <c r="K32" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>2.92</v>
       </c>
       <c r="G33" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H33" t="n">
         <v>2.4</v>
@@ -6789,13 +6789,13 @@
         <v>4.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O33" t="n">
         <v>1.47</v>
@@ -6804,13 +6804,13 @@
         <v>1.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W33" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -6968,10 +6968,10 @@
         <v>1.25</v>
       </c>
       <c r="G34" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="H34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -7162,22 +7162,22 @@
         <v>3.25</v>
       </c>
       <c r="G35" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="H35" t="n">
         <v>2.28</v>
       </c>
       <c r="I35" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J35" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="K35" t="n">
         <v>3.95</v>
       </c>
       <c r="L35" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
         <v>1.08</v>
@@ -7201,13 +7201,13 @@
         <v>3.75</v>
       </c>
       <c r="T35" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U35" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V35" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W35" t="n">
         <v>1.37</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
         <v>4.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J36" t="n">
         <v>4.6</v>
@@ -7377,10 +7377,10 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="O36" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P36" t="n">
         <v>3.25</v>
@@ -7398,10 +7398,10 @@
         <v>1.48</v>
       </c>
       <c r="U36" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
         <v>2.26</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -7568,25 +7568,25 @@
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P37" t="n">
         <v>1.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R37" t="n">
         <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -7744,13 +7744,13 @@
         <v>2.02</v>
       </c>
       <c r="G38" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H38" t="n">
         <v>3.4</v>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
         <v>3.6</v>
@@ -7759,46 +7759,46 @@
         <v>4.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
         <v>1.76</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S38" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="T38" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="U38" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="V38" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
         <v>1.8</v>
       </c>
       <c r="X38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y38" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z38" t="n">
         <v>34</v>
@@ -7810,7 +7810,7 @@
         <v>13.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD38" t="n">
         <v>18.5</v>
@@ -7819,13 +7819,13 @@
         <v>50</v>
       </c>
       <c r="AF38" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG38" t="n">
         <v>13.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI38" t="n">
         <v>60</v>
@@ -7834,7 +7834,7 @@
         <v>32</v>
       </c>
       <c r="AK38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL38" t="n">
         <v>40</v>
@@ -7843,19 +7843,19 @@
         <v>95</v>
       </c>
       <c r="AN38" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO38" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP38" t="n">
         <v>3.55</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS38" t="n">
         <v>4</v>
@@ -7864,25 +7864,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU38" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX38" t="n">
         <v>10.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ38" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB38" t="n">
         <v>19</v>
@@ -7891,20 +7891,20 @@
         <v>15.5</v>
       </c>
       <c r="BD38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG38" t="n">
         <v>3.85</v>
       </c>
-      <c r="BE38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -7965,22 +7965,22 @@
         <v>1.24</v>
       </c>
       <c r="P39" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R39" t="n">
         <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="T39" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U39" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V39" t="n">
         <v>1.31</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -8132,13 +8132,13 @@
         <v>2.38</v>
       </c>
       <c r="G40" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H40" t="n">
         <v>3.35</v>
       </c>
       <c r="I40" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>3.15</v>
@@ -8174,10 +8174,10 @@
         <v>1.85</v>
       </c>
       <c r="U40" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
         <v>1.64</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -8347,13 +8347,13 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="O41" t="n">
         <v>1.18</v>
       </c>
       <c r="P41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q41" t="n">
         <v>1.18</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
         <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q42" t="n">
         <v>2.08</v>
@@ -8556,7 +8556,7 @@
         <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T42" t="n">
         <v>1.91</v>
@@ -8622,7 +8622,7 @@
         <v>80</v>
       </c>
       <c r="AO42" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP42" t="n">
         <v>11.5</v>
@@ -8670,17 +8670,17 @@
         <v>8</v>
       </c>
       <c r="BE42" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF42" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG42" t="n">
         <v>13</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -8741,22 +8741,22 @@
         <v>1.28</v>
       </c>
       <c r="P43" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R43" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S43" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T43" t="n">
         <v>2.06</v>
       </c>
       <c r="U43" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V43" t="n">
         <v>1.12</v>
@@ -8813,7 +8813,7 @@
         <v>200</v>
       </c>
       <c r="AN43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO43" t="n">
         <v>250</v>
@@ -8822,13 +8822,13 @@
         <v>15</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT43" t="n">
         <v>7</v>
@@ -8837,7 +8837,7 @@
         <v>9.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW43" t="n">
         <v>6</v>
@@ -8849,10 +8849,10 @@
         <v>9</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB43" t="n">
         <v>11</v>
@@ -8861,7 +8861,7 @@
         <v>14</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE43" t="n">
         <v>6</v>
@@ -8870,11 +8870,11 @@
         <v>6.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G44" t="n">
         <v>2.06</v>
@@ -8914,7 +8914,7 @@
         <v>4.3</v>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J44" t="n">
         <v>3.45</v>
@@ -8935,7 +8935,7 @@
         <v>1.37</v>
       </c>
       <c r="P44" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q44" t="n">
         <v>2.08</v>
@@ -8953,7 +8953,7 @@
         <v>2.02</v>
       </c>
       <c r="V44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W44" t="n">
         <v>1.94</v>
@@ -8974,7 +8974,7 @@
         <v>10</v>
       </c>
       <c r="AC44" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD44" t="n">
         <v>21</v>
@@ -8983,7 +8983,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG44" t="n">
         <v>11</v>
@@ -9019,10 +9019,10 @@
         <v>12.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT44" t="n">
         <v>7.6</v>
@@ -9034,7 +9034,7 @@
         <v>15.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX44" t="n">
         <v>10.5</v>
@@ -9046,7 +9046,7 @@
         <v>17</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB44" t="n">
         <v>21</v>
@@ -9055,20 +9055,20 @@
         <v>20</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF44" t="n">
         <v>14.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
         <v>5.4</v>
       </c>
       <c r="H45" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I45" t="n">
         <v>1.83</v>
@@ -9144,7 +9144,7 @@
         <v>1.99</v>
       </c>
       <c r="U45" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V45" t="n">
         <v>2.2</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9305,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K46" t="n">
         <v>5.3</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -9490,19 +9490,19 @@
         <v>2.06</v>
       </c>
       <c r="G47" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H47" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I47" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="K47" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9520,7 +9520,7 @@
         <v>2.74</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="R47" t="n">
         <v>1.88</v>
@@ -9535,10 +9535,10 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W47" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -9875,16 +9875,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="G49" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H49" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I49" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J49" t="n">
         <v>3.45</v>
@@ -9908,7 +9908,7 @@
         <v>2.04</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R49" t="n">
         <v>1.4</v>
@@ -9917,28 +9917,28 @@
         <v>3.15</v>
       </c>
       <c r="T49" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U49" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V49" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W49" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X49" t="n">
         <v>19</v>
       </c>
       <c r="Y49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z49" t="n">
         <v>21</v>
       </c>
       <c r="AA49" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB49" t="n">
         <v>15.5</v>
@@ -9947,7 +9947,7 @@
         <v>8.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE49" t="n">
         <v>34</v>
@@ -9992,7 +9992,7 @@
         <v>12.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT49" t="n">
         <v>11</v>
@@ -10004,7 +10004,7 @@
         <v>10.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX49" t="n">
         <v>18</v>
@@ -10016,29 +10016,29 @@
         <v>14.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BB49" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG49" t="n">
         <v>15</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -10072,16 +10072,16 @@
         <v>3.2</v>
       </c>
       <c r="G50" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H50" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J50" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K50" t="n">
         <v>6.2</v>
@@ -10108,7 +10108,7 @@
         <v>1.64</v>
       </c>
       <c r="S50" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -10117,7 +10117,7 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W50" t="n">
         <v>1.33</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -10296,19 +10296,19 @@
         <v>3.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R51" t="n">
         <v>2.08</v>
       </c>
       <c r="S51" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="T51" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="U51" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="V51" t="n">
         <v>1.06</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
         <v>1.02</v>
       </c>
       <c r="N52" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="O52" t="n">
         <v>1.14</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -10687,10 +10687,10 @@
         <v>1.66</v>
       </c>
       <c r="R53" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S53" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="T53" t="n">
         <v>1.54</v>
@@ -10798,7 +10798,7 @@
         <v>1.01</v>
       </c>
       <c r="BC53" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BD53" t="n">
         <v>1.01</v>
@@ -10807,14 +10807,14 @@
         <v>1.01</v>
       </c>
       <c r="BF53" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BG53" t="n">
         <v>7</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="G54" t="n">
         <v>5.6</v>
@@ -10854,13 +10854,13 @@
         <v>1.67</v>
       </c>
       <c r="I54" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>4.1</v>
       </c>
       <c r="K54" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="L54" t="n">
         <v>1.27</v>
@@ -10869,19 +10869,19 @@
         <v>1.04</v>
       </c>
       <c r="N54" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
       </c>
       <c r="P54" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q54" t="n">
         <v>1.64</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S54" t="n">
         <v>2.38</v>
@@ -10893,7 +10893,7 @@
         <v>1.01</v>
       </c>
       <c r="V54" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="W54" t="n">
         <v>1.22</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -11386,17 +11386,17 @@
         <v>4.6</v>
       </c>
       <c r="BE56" t="n">
-        <v>42</v>
+        <v>4.7</v>
       </c>
       <c r="BF56" t="n">
         <v>20</v>
       </c>
       <c r="BG56" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G57" t="n">
         <v>2.48</v>
@@ -11478,7 +11478,7 @@
         <v>1.48</v>
       </c>
       <c r="W57" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="X57" t="n">
         <v>32</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
         <v>1.79</v>
       </c>
       <c r="H61" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I61" t="n">
         <v>5</v>
@@ -12242,10 +12242,10 @@
         <v>1.66</v>
       </c>
       <c r="S61" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T61" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U61" t="n">
         <v>2.46</v>
@@ -12260,7 +12260,7 @@
         <v>32</v>
       </c>
       <c r="Y61" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z61" t="n">
         <v>48</v>
@@ -12269,7 +12269,7 @@
         <v>110</v>
       </c>
       <c r="AB61" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC61" t="n">
         <v>11.5</v>
@@ -12278,7 +12278,7 @@
         <v>23</v>
       </c>
       <c r="AE61" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF61" t="n">
         <v>14</v>
@@ -12287,7 +12287,7 @@
         <v>11</v>
       </c>
       <c r="AH61" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI61" t="n">
         <v>50</v>
@@ -12296,19 +12296,19 @@
         <v>21</v>
       </c>
       <c r="AK61" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL61" t="n">
         <v>30</v>
       </c>
       <c r="AM61" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN61" t="n">
         <v>8</v>
       </c>
       <c r="AO61" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP61" t="n">
         <v>21</v>
@@ -12317,10 +12317,10 @@
         <v>21</v>
       </c>
       <c r="AR61" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS61" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT61" t="n">
         <v>11.5</v>
@@ -12332,7 +12332,7 @@
         <v>17</v>
       </c>
       <c r="AW61" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AX61" t="n">
         <v>11.5</v>
@@ -12344,7 +12344,7 @@
         <v>14.5</v>
       </c>
       <c r="BA61" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB61" t="n">
         <v>16</v>
@@ -12353,20 +12353,20 @@
         <v>14</v>
       </c>
       <c r="BD61" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE61" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF61" t="n">
         <v>5.6</v>
       </c>
       <c r="BG61" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -12457,10 +12457,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA62" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB62" t="n">
         <v>12.5</v>
@@ -12514,7 +12514,7 @@
         <v>12.5</v>
       </c>
       <c r="AS62" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT62" t="n">
         <v>9</v>
@@ -12526,7 +12526,7 @@
         <v>10</v>
       </c>
       <c r="AW62" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX62" t="n">
         <v>19.5</v>
@@ -12538,7 +12538,7 @@
         <v>17.5</v>
       </c>
       <c r="BA62" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB62" t="n">
         <v>5.1</v>
@@ -12550,17 +12550,17 @@
         <v>5.1</v>
       </c>
       <c r="BE62" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF62" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG62" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
         <v>2.24</v>
       </c>
       <c r="BB63" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BC63" t="n">
         <v>14</v>
@@ -12744,7 +12744,7 @@
         <v>2.2</v>
       </c>
       <c r="BE63" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BF63" t="n">
         <v>9.199999999999999</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -12785,16 +12785,16 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G64" t="n">
         <v>2.1</v>
       </c>
       <c r="H64" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I64" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>3.35</v>
@@ -12806,13 +12806,13 @@
         <v>1.4</v>
       </c>
       <c r="M64" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N64" t="n">
         <v>2.66</v>
       </c>
       <c r="O64" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P64" t="n">
         <v>1.63</v>
@@ -12824,7 +12824,7 @@
         <v>1.25</v>
       </c>
       <c r="S64" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T64" t="n">
         <v>1.82</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
         <v>1.42</v>
       </c>
       <c r="S65" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T65" t="n">
         <v>1.7</v>
@@ -13108,7 +13108,7 @@
         <v>12</v>
       </c>
       <c r="AW65" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX65" t="n">
         <v>14</v>
@@ -13120,7 +13120,7 @@
         <v>14</v>
       </c>
       <c r="BA65" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB65" t="n">
         <v>7.8</v>
@@ -13129,7 +13129,7 @@
         <v>21</v>
       </c>
       <c r="BD65" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE65" t="n">
         <v>8.800000000000001</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G66" t="n">
         <v>1.58</v>
@@ -13206,7 +13206,7 @@
         <v>2.96</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R66" t="n">
         <v>1.77</v>
@@ -13218,7 +13218,7 @@
         <v>1.59</v>
       </c>
       <c r="U66" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V66" t="n">
         <v>1.17</v>
@@ -13251,7 +13251,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG66" t="n">
         <v>12.5</v>
@@ -13281,16 +13281,16 @@
         <v>60</v>
       </c>
       <c r="AP66" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ66" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR66" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS66" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT66" t="n">
         <v>10.5</v>
@@ -13302,7 +13302,7 @@
         <v>18.5</v>
       </c>
       <c r="AW66" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX66" t="n">
         <v>9.800000000000001</v>
@@ -13314,7 +13314,7 @@
         <v>14</v>
       </c>
       <c r="BA66" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB66" t="n">
         <v>13.5</v>
@@ -13326,17 +13326,17 @@
         <v>19</v>
       </c>
       <c r="BE66" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF66" t="n">
         <v>4.1</v>
       </c>
       <c r="BG66" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -13367,13 +13367,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G67" t="n">
         <v>2.32</v>
       </c>
       <c r="H67" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I67" t="n">
         <v>3.35</v>
@@ -13382,7 +13382,7 @@
         <v>3.95</v>
       </c>
       <c r="K67" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L67" t="n">
         <v>1.24</v>
@@ -13403,16 +13403,16 @@
         <v>1.54</v>
       </c>
       <c r="R67" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S67" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T67" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="U67" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="V67" t="n">
         <v>1.43</v>
@@ -13490,7 +13490,7 @@
         <v>11.5</v>
       </c>
       <c r="AU67" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV67" t="n">
         <v>11</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -13600,7 +13600,7 @@
         <v>2.06</v>
       </c>
       <c r="S68" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="T68" t="n">
         <v>1.42</v>
@@ -13609,7 +13609,7 @@
         <v>2.68</v>
       </c>
       <c r="V68" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W68" t="n">
         <v>2.26</v>
@@ -13630,16 +13630,16 @@
         <v>25</v>
       </c>
       <c r="AC68" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AD68" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE68" t="n">
         <v>50</v>
       </c>
       <c r="AF68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG68" t="n">
         <v>14.5</v>
@@ -13657,7 +13657,7 @@
         <v>19</v>
       </c>
       <c r="AL68" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM68" t="n">
         <v>55</v>
@@ -13672,7 +13672,7 @@
         <v>4.1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="AR68" t="n">
         <v>4.1</v>
@@ -13681,22 +13681,22 @@
         <v>4.2</v>
       </c>
       <c r="AT68" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV68" t="n">
         <v>14.5</v>
       </c>
-      <c r="AU68" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AW68" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX68" t="n">
         <v>13</v>
       </c>
       <c r="AY68" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ68" t="n">
         <v>11.5</v>
@@ -13705,7 +13705,7 @@
         <v>4</v>
       </c>
       <c r="BB68" t="n">
-        <v>3.85</v>
+        <v>15.5</v>
       </c>
       <c r="BC68" t="n">
         <v>11.5</v>
@@ -13720,11 +13720,11 @@
         <v>3.95</v>
       </c>
       <c r="BG68" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -14337,13 +14337,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="G72" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H72" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I72" t="n">
         <v>7.6</v>
@@ -14352,7 +14352,7 @@
         <v>4.7</v>
       </c>
       <c r="K72" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L72" t="n">
         <v>1.18</v>
@@ -14379,10 +14379,10 @@
         <v>1.83</v>
       </c>
       <c r="T72" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="U72" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V72" t="n">
         <v>1.15</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -14534,22 +14534,22 @@
         <v>1.74</v>
       </c>
       <c r="G73" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H73" t="n">
         <v>4.3</v>
       </c>
       <c r="I73" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J73" t="n">
         <v>4.2</v>
       </c>
       <c r="K73" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L73" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M73" t="n">
         <v>1.02</v>
@@ -14642,7 +14642,7 @@
         <v>3.75</v>
       </c>
       <c r="AQ73" t="n">
-        <v>3.75</v>
+        <v>17</v>
       </c>
       <c r="AR73" t="n">
         <v>3.95</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -14770,7 +14770,7 @@
         <v>1.5</v>
       </c>
       <c r="U74" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="V74" t="n">
         <v>1.19</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15036,7 @@
         <v>14</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT75" t="n">
         <v>8</v>
@@ -15060,29 +15060,29 @@
         <v>12.5</v>
       </c>
       <c r="BA75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC75" t="n">
         <v>1.03</v>
       </c>
       <c r="BD75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF75" t="n">
         <v>20</v>
       </c>
       <c r="BG75" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -15155,7 +15155,7 @@
         <v>1.84</v>
       </c>
       <c r="T76" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U76" t="n">
         <v>2.32</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
         <v>1.62</v>
       </c>
       <c r="U77" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="V77" t="n">
         <v>1.23</v>
@@ -15397,7 +15397,7 @@
         <v>55</v>
       </c>
       <c r="AJ77" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AK77" t="n">
         <v>19</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -15501,13 +15501,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G78" t="n">
         <v>2.28</v>
       </c>
       <c r="H78" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I78" t="n">
         <v>4.6</v>
@@ -15531,7 +15531,7 @@
         <v>1.31</v>
       </c>
       <c r="P78" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q78" t="n">
         <v>1.93</v>
@@ -15552,7 +15552,7 @@
         <v>1.27</v>
       </c>
       <c r="W78" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -15710,7 +15710,7 @@
         <v>3.95</v>
       </c>
       <c r="K79" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
@@ -15734,16 +15734,16 @@
         <v>1.72</v>
       </c>
       <c r="S79" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T79" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="U79" t="n">
         <v>2.74</v>
       </c>
       <c r="V79" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W79" t="n">
         <v>1.79</v>
@@ -15797,22 +15797,22 @@
         <v>60</v>
       </c>
       <c r="AN79" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO79" t="n">
         <v>19</v>
       </c>
       <c r="AP79" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ79" t="n">
         <v>17.5</v>
       </c>
       <c r="AR79" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS79" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT79" t="n">
         <v>14</v>
@@ -15824,7 +15824,7 @@
         <v>12.5</v>
       </c>
       <c r="AW79" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX79" t="n">
         <v>15.5</v>
@@ -15836,10 +15836,10 @@
         <v>12.5</v>
       </c>
       <c r="BA79" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB79" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC79" t="n">
         <v>16.5</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -15928,7 +15928,7 @@
         <v>1.21</v>
       </c>
       <c r="S80" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T80" t="n">
         <v>1.6</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -16086,16 +16086,16 @@
         <v>1.43</v>
       </c>
       <c r="G81" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="H81" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="I81" t="n">
         <v>11</v>
       </c>
       <c r="J81" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="K81" t="n">
         <v>5.7</v>
@@ -16113,7 +16113,7 @@
         <v>1.21</v>
       </c>
       <c r="P81" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q81" t="n">
         <v>1.63</v>
@@ -16134,7 +16134,7 @@
         <v>1.1</v>
       </c>
       <c r="W81" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="X81" t="n">
         <v>1000</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -16289,10 +16289,10 @@
         <v>2.28</v>
       </c>
       <c r="J82" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K82" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
@@ -16307,25 +16307,25 @@
         <v>1.26</v>
       </c>
       <c r="P82" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R82" t="n">
         <v>1.46</v>
       </c>
       <c r="S82" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="T82" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U82" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V82" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W82" t="n">
         <v>1.39</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -16471,22 +16471,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G83" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H83" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I83" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J83" t="n">
         <v>3.15</v>
       </c>
       <c r="K83" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L83" t="n">
         <v>1.01</v>
@@ -16495,10 +16495,10 @@
         <v>1.09</v>
       </c>
       <c r="N83" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O83" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P83" t="n">
         <v>1.73</v>
@@ -16507,13 +16507,13 @@
         <v>2.24</v>
       </c>
       <c r="R83" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S83" t="n">
         <v>4.2</v>
       </c>
       <c r="T83" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U83" t="n">
         <v>2</v>
@@ -16522,7 +16522,7 @@
         <v>1.41</v>
       </c>
       <c r="W83" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X83" t="n">
         <v>13.5</v>
@@ -16585,10 +16585,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR83" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS83" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT83" t="n">
         <v>8.4</v>
@@ -16600,7 +16600,7 @@
         <v>12.5</v>
       </c>
       <c r="AW83" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX83" t="n">
         <v>14</v>
@@ -16612,29 +16612,29 @@
         <v>16.5</v>
       </c>
       <c r="BA83" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB83" t="n">
         <v>32</v>
       </c>
       <c r="BC83" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD83" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE83" t="n">
         <v>5.1</v>
       </c>
       <c r="BF83" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG83" t="n">
         <v>4.9</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -16665,16 +16665,16 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G84" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H84" t="n">
         <v>2.2</v>
       </c>
       <c r="I84" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="J84" t="n">
         <v>2.86</v>
@@ -16713,10 +16713,10 @@
         <v>1.84</v>
       </c>
       <c r="V84" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W84" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X84" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
         <v>1.01</v>
       </c>
       <c r="N85" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="O85" t="n">
         <v>1.47</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -17107,13 +17107,13 @@
         <v>1.5</v>
       </c>
       <c r="X86" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y86" t="n">
         <v>13</v>
       </c>
       <c r="Z86" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AA86" t="n">
         <v>40</v>
@@ -17137,7 +17137,7 @@
         <v>13.5</v>
       </c>
       <c r="AH86" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI86" t="n">
         <v>38</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -17256,7 +17256,7 @@
         <v>10.5</v>
       </c>
       <c r="I87" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J87" t="n">
         <v>5.1</v>
@@ -17271,7 +17271,7 @@
         <v>1.07</v>
       </c>
       <c r="N87" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O87" t="n">
         <v>1.33</v>
@@ -17295,10 +17295,10 @@
         <v>1.7</v>
       </c>
       <c r="V87" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W87" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="X87" t="n">
         <v>15</v>
@@ -17361,7 +17361,7 @@
         <v>24</v>
       </c>
       <c r="AR87" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AS87" t="n">
         <v>55</v>
@@ -17373,10 +17373,10 @@
         <v>10.5</v>
       </c>
       <c r="AV87" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AW87" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX87" t="n">
         <v>6.6</v>
@@ -17388,7 +17388,7 @@
         <v>30</v>
       </c>
       <c r="BA87" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB87" t="n">
         <v>10</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
         <v>3.35</v>
       </c>
       <c r="L88" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M88" t="n">
         <v>1.1</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18056,7 @@
         <v>1.84</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R91" t="n">
         <v>1.32</v>
@@ -18152,7 +18152,7 @@
         <v>8</v>
       </c>
       <c r="AW91" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AX91" t="n">
         <v>4.8</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18435,7 @@
         <v>1.01</v>
       </c>
       <c r="N93" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="O93" t="n">
         <v>1.29</v>
@@ -18444,7 +18444,7 @@
         <v>1.73</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R93" t="n">
         <v>1.21</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -18799,7 +18799,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G95" t="n">
         <v>1.36</v>
@@ -18811,19 +18811,19 @@
         <v>1000</v>
       </c>
       <c r="J95" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K95" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="L95" t="n">
         <v>1.01</v>
       </c>
       <c r="M95" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N95" t="n">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="O95" t="n">
         <v>1.25</v>
@@ -18832,13 +18832,13 @@
         <v>1.86</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R95" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S95" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="T95" t="n">
         <v>1.01</v>
@@ -18850,7 +18850,7 @@
         <v>1.01</v>
       </c>
       <c r="W95" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X95" t="n">
         <v>1000</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -18996,7 +18996,7 @@
         <v>2.5</v>
       </c>
       <c r="G96" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H96" t="n">
         <v>2.82</v>
@@ -19020,7 +19020,7 @@
         <v>3.3</v>
       </c>
       <c r="O96" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P96" t="n">
         <v>1.8</v>
@@ -19044,7 +19044,7 @@
         <v>1.47</v>
       </c>
       <c r="W96" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X96" t="n">
         <v>15</v>
@@ -19107,10 +19107,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT96" t="n">
         <v>8</v>
@@ -19122,7 +19122,7 @@
         <v>10</v>
       </c>
       <c r="AW96" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX96" t="n">
         <v>13</v>
@@ -19134,29 +19134,29 @@
         <v>13.5</v>
       </c>
       <c r="BA96" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB96" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC96" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD96" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE96" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF96" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG96" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G97" t="n">
         <v>3.45</v>
@@ -19199,7 +19199,7 @@
         <v>2.4</v>
       </c>
       <c r="J97" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K97" t="n">
         <v>3.8</v>
@@ -19211,13 +19211,13 @@
         <v>1.06</v>
       </c>
       <c r="N97" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O97" t="n">
         <v>1.27</v>
       </c>
       <c r="P97" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q97" t="n">
         <v>1.83</v>
@@ -19226,7 +19226,7 @@
         <v>1.43</v>
       </c>
       <c r="S97" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="T97" t="n">
         <v>1.67</v>
@@ -19250,7 +19250,7 @@
         <v>16.5</v>
       </c>
       <c r="AA97" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB97" t="n">
         <v>15</v>
@@ -19262,7 +19262,7 @@
         <v>13.5</v>
       </c>
       <c r="AE97" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF97" t="n">
         <v>25</v>
@@ -19277,7 +19277,7 @@
         <v>36</v>
       </c>
       <c r="AJ97" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK97" t="n">
         <v>40</v>
@@ -19304,7 +19304,7 @@
         <v>13.5</v>
       </c>
       <c r="AS97" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT97" t="n">
         <v>12</v>
@@ -19328,29 +19328,29 @@
         <v>13.5</v>
       </c>
       <c r="BA97" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB97" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC97" t="n">
         <v>7</v>
       </c>
-      <c r="BC97" t="n">
+      <c r="BD97" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF97" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BD97" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE97" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF97" t="n">
-        <v>6.4</v>
       </c>
       <c r="BG97" t="n">
         <v>12.5</v>
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -19390,10 +19390,10 @@
         <v>3.2</v>
       </c>
       <c r="I98" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J98" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K98" t="n">
         <v>4.3</v>
@@ -19423,7 +19423,7 @@
         <v>3.15</v>
       </c>
       <c r="T98" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="U98" t="n">
         <v>2.14</v>
@@ -19432,7 +19432,7 @@
         <v>1.32</v>
       </c>
       <c r="W98" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X98" t="n">
         <v>18</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -19590,7 +19590,7 @@
         <v>3.3</v>
       </c>
       <c r="K99" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L99" t="n">
         <v>1.44</v>
@@ -19623,7 +19623,7 @@
         <v>1.94</v>
       </c>
       <c r="V99" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W99" t="n">
         <v>1.9</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
         <v>10.5</v>
       </c>
       <c r="Z100" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AA100" t="n">
         <v>1000</v>
@@ -19886,7 +19886,7 @@
         <v>14</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT100" t="n">
         <v>8.800000000000001</v>
@@ -19898,7 +19898,7 @@
         <v>10.5</v>
       </c>
       <c r="AW100" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX100" t="n">
         <v>17</v>
@@ -19907,32 +19907,32 @@
         <v>12</v>
       </c>
       <c r="AZ100" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BA100" t="n">
         <v>36</v>
       </c>
       <c r="BB100" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC100" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BD100" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE100" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF100" t="n">
         <v>30</v>
       </c>
       <c r="BG100" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G101" t="n">
         <v>1.75</v>
@@ -19972,7 +19972,7 @@
         <v>5.5</v>
       </c>
       <c r="I101" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J101" t="n">
         <v>3.95</v>
@@ -19996,7 +19996,7 @@
         <v>2.04</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R101" t="n">
         <v>1.4</v>
@@ -20005,13 +20005,13 @@
         <v>3.15</v>
       </c>
       <c r="T101" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U101" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V101" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W101" t="n">
         <v>2.32</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -20157,22 +20157,22 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G102" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H102" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="I102" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="J102" t="n">
         <v>3.25</v>
       </c>
       <c r="K102" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L102" t="n">
         <v>1.01</v>
@@ -20181,16 +20181,16 @@
         <v>1.01</v>
       </c>
       <c r="N102" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O102" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P102" t="n">
         <v>1.78</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R102" t="n">
         <v>1.25</v>
@@ -20205,10 +20205,10 @@
         <v>1.01</v>
       </c>
       <c r="V102" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W102" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X102" t="n">
         <v>1000</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G103" t="n">
         <v>1.64</v>
@@ -20363,10 +20363,10 @@
         <v>7</v>
       </c>
       <c r="J103" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K103" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L103" t="n">
         <v>1.01</v>
@@ -20396,7 +20396,7 @@
         <v>1.86</v>
       </c>
       <c r="U103" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V103" t="n">
         <v>1.17</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -20578,7 +20578,7 @@
         <v>2.08</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R104" t="n">
         <v>1.35</v>
@@ -20587,7 +20587,7 @@
         <v>2.32</v>
       </c>
       <c r="T104" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U104" t="n">
         <v>1.01</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -20739,19 +20739,19 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G105" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H105" t="n">
         <v>4.1</v>
       </c>
       <c r="I105" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K105" t="n">
         <v>3.5</v>
@@ -20763,34 +20763,34 @@
         <v>1.08</v>
       </c>
       <c r="N105" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O105" t="n">
         <v>1.37</v>
       </c>
       <c r="P105" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q105" t="n">
         <v>2.08</v>
       </c>
       <c r="R105" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S105" t="n">
         <v>3.8</v>
       </c>
       <c r="T105" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U105" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V105" t="n">
         <v>1.28</v>
       </c>
       <c r="W105" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X105" t="n">
         <v>14.5</v>
@@ -20805,7 +20805,7 @@
         <v>110</v>
       </c>
       <c r="AB105" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC105" t="n">
         <v>7.8</v>
@@ -20853,10 +20853,10 @@
         <v>12</v>
       </c>
       <c r="AR105" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS105" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT105" t="n">
         <v>7.6</v>
@@ -20868,7 +20868,7 @@
         <v>15</v>
       </c>
       <c r="AW105" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX105" t="n">
         <v>10.5</v>
@@ -20880,7 +20880,7 @@
         <v>15.5</v>
       </c>
       <c r="BA105" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB105" t="n">
         <v>21</v>
@@ -20889,20 +20889,20 @@
         <v>19.5</v>
       </c>
       <c r="BD105" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE105" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF105" t="n">
         <v>15</v>
       </c>
       <c r="BG105" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -21127,64 +21127,64 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G107" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H107" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I107" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J107" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K107" t="n">
         <v>3.75</v>
       </c>
       <c r="L107" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M107" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N107" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="O107" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P107" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R107" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S107" t="n">
         <v>4.1</v>
       </c>
       <c r="T107" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U107" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V107" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W107" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="X107" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y107" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z107" t="n">
         <v>1000</v>
@@ -21193,10 +21193,10 @@
         <v>1000</v>
       </c>
       <c r="AB107" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC107" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD107" t="n">
         <v>1000</v>
@@ -21205,10 +21205,10 @@
         <v>1000</v>
       </c>
       <c r="AF107" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG107" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH107" t="n">
         <v>1000</v>
@@ -21229,68 +21229,68 @@
         <v>1000</v>
       </c>
       <c r="AN107" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO107" t="n">
         <v>1000</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.46</v>
+        <v>5.4</v>
       </c>
       <c r="AQ107" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AR107" t="n">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="AS107" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.26</v>
+        <v>4.1</v>
       </c>
       <c r="AU107" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="AV107" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="AW107" t="n">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="AX107" t="n">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="AY107" t="n">
-        <v>2.44</v>
+        <v>4.8</v>
       </c>
       <c r="AZ107" t="n">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="BA107" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB107" t="n">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="BC107" t="n">
-        <v>2.66</v>
+        <v>6.4</v>
       </c>
       <c r="BD107" t="n">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="BE107" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF107" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG107" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -21321,16 +21321,16 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G108" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H108" t="n">
         <v>2.76</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J108" t="n">
         <v>3.6</v>
@@ -21345,7 +21345,7 @@
         <v>1.05</v>
       </c>
       <c r="N108" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O108" t="n">
         <v>1.26</v>
@@ -21354,13 +21354,13 @@
         <v>2.14</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R108" t="n">
         <v>1.45</v>
       </c>
       <c r="S108" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T108" t="n">
         <v>1.56</v>
@@ -21369,10 +21369,10 @@
         <v>2.36</v>
       </c>
       <c r="V108" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W108" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X108" t="n">
         <v>21</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -21515,19 +21515,19 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G109" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H109" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I109" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J109" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="K109" t="n">
         <v>3.05</v>
@@ -21539,40 +21539,40 @@
         <v>1.15</v>
       </c>
       <c r="N109" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O109" t="n">
         <v>1.69</v>
       </c>
       <c r="P109" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="R109" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S109" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T109" t="n">
         <v>2.34</v>
       </c>
       <c r="U109" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V109" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W109" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="X109" t="n">
         <v>1000</v>
       </c>
       <c r="Y109" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z109" t="n">
         <v>1000</v>
@@ -21584,7 +21584,7 @@
         <v>8.6</v>
       </c>
       <c r="AC109" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD109" t="n">
         <v>1000</v>
@@ -21623,28 +21623,28 @@
         <v>1000</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="AQ109" t="n">
-        <v>7</v>
+        <v>2.02</v>
       </c>
       <c r="AR109" t="n">
         <v>17.5</v>
       </c>
       <c r="AS109" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AU109" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AV109" t="n">
-        <v>14</v>
+        <v>2.22</v>
       </c>
       <c r="AW109" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AX109" t="n">
         <v>9.6</v>
@@ -21653,32 +21653,32 @@
         <v>10</v>
       </c>
       <c r="AZ109" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BA109" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB109" t="n">
         <v>2.36</v>
       </c>
-      <c r="BB109" t="n">
-        <v>2.26</v>
-      </c>
       <c r="BC109" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="BD109" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BE109" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BF109" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="BG109" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -21718,13 +21718,13 @@
         <v>2.64</v>
       </c>
       <c r="I110" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J110" t="n">
         <v>3.8</v>
       </c>
       <c r="K110" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L110" t="n">
         <v>1.01</v>
@@ -21745,13 +21745,13 @@
         <v>1.37</v>
       </c>
       <c r="R110" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S110" t="n">
         <v>1.92</v>
       </c>
       <c r="T110" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U110" t="n">
         <v>2.74</v>
@@ -21862,7 +21862,7 @@
         <v>20</v>
       </c>
       <c r="BE110" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BF110" t="n">
         <v>4</v>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -21912,7 +21912,7 @@
         <v>3.2</v>
       </c>
       <c r="I111" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J111" t="n">
         <v>3.6</v>
@@ -22011,7 +22011,7 @@
         <v>32</v>
       </c>
       <c r="AP111" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ111" t="n">
         <v>13</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
         <v>2.08</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R112" t="n">
         <v>1.42</v>
@@ -22151,7 +22151,7 @@
         <v>2.22</v>
       </c>
       <c r="X112" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y112" t="n">
         <v>23</v>
@@ -22214,7 +22214,7 @@
         <v>4.1</v>
       </c>
       <c r="AS112" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT112" t="n">
         <v>8.4</v>
@@ -22226,7 +22226,7 @@
         <v>16.5</v>
       </c>
       <c r="AW112" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX112" t="n">
         <v>9.800000000000001</v>
@@ -22247,10 +22247,10 @@
         <v>15.5</v>
       </c>
       <c r="BD112" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE112" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF112" t="n">
         <v>8</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -22291,7 +22291,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G113" t="n">
         <v>2.12</v>
@@ -22315,7 +22315,7 @@
         <v>1.06</v>
       </c>
       <c r="N113" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O113" t="n">
         <v>1.29</v>
@@ -22327,13 +22327,13 @@
         <v>1.84</v>
       </c>
       <c r="R113" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S113" t="n">
         <v>3.1</v>
       </c>
       <c r="T113" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="U113" t="n">
         <v>2.12</v>
@@ -22342,7 +22342,7 @@
         <v>1.29</v>
       </c>
       <c r="W113" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X113" t="n">
         <v>16.5</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -22515,7 +22515,7 @@
         <v>1.45</v>
       </c>
       <c r="P114" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q114" t="n">
         <v>2.4</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
         <v>28</v>
       </c>
       <c r="BB115" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BC115" t="n">
         <v>29</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -22873,13 +22873,13 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="G116" t="n">
         <v>17</v>
       </c>
       <c r="H116" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I116" t="n">
         <v>1.27</v>
@@ -22888,37 +22888,37 @@
         <v>6.8</v>
       </c>
       <c r="K116" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L116" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M116" t="n">
         <v>1.03</v>
       </c>
       <c r="N116" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O116" t="n">
         <v>1.19</v>
       </c>
       <c r="P116" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R116" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S116" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="T116" t="n">
         <v>2.22</v>
       </c>
       <c r="U116" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="V116" t="n">
         <v>4.7</v>
@@ -22930,10 +22930,10 @@
         <v>26</v>
       </c>
       <c r="Y116" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z116" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA116" t="n">
         <v>10.5</v>
@@ -22942,7 +22942,7 @@
         <v>55</v>
       </c>
       <c r="AC116" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD116" t="n">
         <v>12</v>
@@ -22951,16 +22951,16 @@
         <v>14.5</v>
       </c>
       <c r="AF116" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AG116" t="n">
         <v>60</v>
       </c>
       <c r="AH116" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AI116" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ116" t="n">
         <v>910</v>
@@ -22972,13 +22972,13 @@
         <v>230</v>
       </c>
       <c r="AM116" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN116" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AO116" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AP116" t="n">
         <v>21</v>
@@ -23002,41 +23002,41 @@
         <v>11</v>
       </c>
       <c r="AW116" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX116" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY116" t="n">
-        <v>9.6</v>
+        <v>48</v>
       </c>
       <c r="AZ116" t="n">
         <v>30</v>
       </c>
       <c r="BA116" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BB116" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BC116" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD116" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE116" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF116" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG116" t="n">
         <v>3.8</v>
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -23073,13 +23073,13 @@
         <v>3.8</v>
       </c>
       <c r="H117" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I117" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J117" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K117" t="n">
         <v>3.35</v>
@@ -23100,7 +23100,7 @@
         <v>1.58</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R117" t="n">
         <v>1.21</v>
@@ -23115,7 +23115,7 @@
         <v>1.84</v>
       </c>
       <c r="V117" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W117" t="n">
         <v>1.36</v>
@@ -23175,7 +23175,7 @@
         <v>40</v>
       </c>
       <c r="AP117" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ117" t="n">
         <v>6.4</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -23261,10 +23261,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G118" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H118" t="n">
         <v>8.800000000000001</v>
@@ -23276,7 +23276,7 @@
         <v>4</v>
       </c>
       <c r="K118" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L118" t="n">
         <v>1.01</v>
@@ -23294,7 +23294,7 @@
         <v>1.68</v>
       </c>
       <c r="Q118" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R118" t="n">
         <v>1.25</v>
@@ -23312,7 +23312,7 @@
         <v>1.11</v>
       </c>
       <c r="W118" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X118" t="n">
         <v>13.5</v>
@@ -23324,7 +23324,7 @@
         <v>95</v>
       </c>
       <c r="AA118" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="AB118" t="n">
         <v>7.2</v>
@@ -23420,11 +23420,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG118" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -23455,61 +23455,61 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="G119" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H119" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I119" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="J119" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="K119" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L119" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M119" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N119" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="O119" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="P119" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="R119" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S119" t="n">
-        <v>1.07</v>
+        <v>3.5</v>
       </c>
       <c r="T119" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U119" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V119" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W119" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X119" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y119" t="n">
         <v>1000</v>
@@ -23521,10 +23521,10 @@
         <v>1000</v>
       </c>
       <c r="AB119" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC119" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD119" t="n">
         <v>1000</v>
@@ -23563,62 +23563,62 @@
         <v>1000</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT119" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AU119" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AV119" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW119" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX119" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AY119" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ119" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA119" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB119" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC119" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD119" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE119" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF119" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG119" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -23846,10 +23846,10 @@
         <v>2.08</v>
       </c>
       <c r="G121" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H121" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I121" t="n">
         <v>4.6</v>
@@ -23858,7 +23858,7 @@
         <v>3.2</v>
       </c>
       <c r="K121" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L121" t="n">
         <v>1.48</v>
@@ -23873,10 +23873,10 @@
         <v>1.49</v>
       </c>
       <c r="P121" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q121" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R121" t="n">
         <v>1.17</v>
@@ -23894,7 +23894,7 @@
         <v>1.28</v>
       </c>
       <c r="W121" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X121" t="n">
         <v>1000</v>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -24037,22 +24037,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G122" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H122" t="n">
         <v>3.45</v>
       </c>
       <c r="I122" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J122" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K122" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L122" t="n">
         <v>1.01</v>
@@ -24061,16 +24061,16 @@
         <v>1.01</v>
       </c>
       <c r="N122" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O122" t="n">
         <v>1.31</v>
       </c>
       <c r="P122" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R122" t="n">
         <v>1.28</v>
@@ -24085,10 +24085,10 @@
         <v>1.01</v>
       </c>
       <c r="V122" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W122" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X122" t="n">
         <v>1000</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24231,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="G123" t="n">
         <v>2.78</v>
@@ -24255,7 +24255,7 @@
         <v>1.06</v>
       </c>
       <c r="N123" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="O123" t="n">
         <v>1.35</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G124" t="n">
         <v>2.18</v>
@@ -24440,7 +24440,7 @@
         <v>3.2</v>
       </c>
       <c r="K124" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L124" t="n">
         <v>1.48</v>
@@ -24449,7 +24449,7 @@
         <v>1.12</v>
       </c>
       <c r="N124" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O124" t="n">
         <v>1.53</v>
@@ -24488,7 +24488,7 @@
         <v>34</v>
       </c>
       <c r="AA124" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB124" t="n">
         <v>7</v>
@@ -24584,11 +24584,11 @@
         <v>6.4</v>
       </c>
       <c r="BG124" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>
@@ -24658,13 +24658,13 @@
         <v>1.68</v>
       </c>
       <c r="S125" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T125" t="n">
         <v>1.93</v>
       </c>
       <c r="U125" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V125" t="n">
         <v>1.05</v>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-04-05 02:37:13</t>
+          <t>2026-04-05 05:07:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-06.xlsx
@@ -760,7 +760,7 @@
         <v>1.32</v>
       </c>
       <c r="G2" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="H2" t="n">
         <v>7.2</v>
@@ -772,16 +772,16 @@
         <v>4.7</v>
       </c>
       <c r="K2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
@@ -796,10 +796,10 @@
         <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
         <v>1.78</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
         <v>2.32</v>
@@ -960,31 +960,31 @@
         <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
@@ -999,7 +999,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
         <v>1.75</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J5" t="n">
         <v>3.45</v>
@@ -1360,37 +1360,37 @@
         <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
         <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
         <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1402,7 +1402,7 @@
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
         <v>15</v>
@@ -1441,7 +1441,7 @@
         <v>95</v>
       </c>
       <c r="AN5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
         <v>21</v>
@@ -1456,7 +1456,7 @@
         <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT5" t="n">
         <v>11.5</v>
@@ -1471,38 +1471,38 @@
         <v>18.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
         <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE5" t="n">
         <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
         <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -1536,10 +1536,10 @@
         <v>5.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I6" t="n">
         <v>1.74</v>
@@ -1584,7 +1584,7 @@
         <v>2.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -1662,7 +1662,7 @@
         <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX6" t="n">
         <v>40</v>
@@ -1686,17 +1686,17 @@
         <v>18</v>
       </c>
       <c r="BE6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG6" t="n">
         <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H7" t="n">
         <v>3.6</v>
@@ -1742,7 +1742,7 @@
         <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,34 +1751,34 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1796,7 +1796,7 @@
         <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
         <v>16</v>
@@ -1835,7 +1835,7 @@
         <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
@@ -1844,19 +1844,19 @@
         <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX7" t="n">
         <v>12</v>
@@ -1868,29 +1868,29 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD7" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
         <v>19</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K8" t="n">
         <v>4.6</v>
@@ -1945,10 +1945,10 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="P8" t="n">
         <v>1.58</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -2121,16 +2121,16 @@
         <v>5.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="I9" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>2.92</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.37</v>
@@ -2154,7 +2154,7 @@
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,7 +2163,7 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="W9" t="n">
         <v>1.23</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
         <v>46</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AQ10" t="n">
         <v>13</v>
@@ -2429,10 +2429,10 @@
         <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
@@ -2444,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
@@ -2453,7 +2453,7 @@
         <v>3.95</v>
       </c>
       <c r="BB10" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC10" t="n">
         <v>14</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P11" t="n">
         <v>1.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I13" t="n">
         <v>2.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
@@ -2915,22 +2915,22 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
         <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
         <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.65</v>
@@ -2942,10 +2942,10 @@
         <v>1.83</v>
       </c>
       <c r="W13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
@@ -2954,7 +2954,7 @@
         <v>18.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="n">
         <v>18.5</v>
@@ -2966,7 +2966,7 @@
         <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF13" t="n">
         <v>32</v>
@@ -2978,7 +2978,7 @@
         <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
         <v>75</v>
@@ -3020,7 +3020,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX13" t="n">
         <v>18.5</v>
@@ -3044,17 +3044,17 @@
         <v>3.95</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF13" t="n">
         <v>3.85</v>
       </c>
       <c r="BG13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="G14" t="n">
-        <v>110</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>2.56</v>
       </c>
       <c r="K14" t="n">
         <v>3.85</v>
@@ -3133,10 +3133,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
         <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q18" t="n">
         <v>1.02</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         <v>1.22</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
         <v>1.55</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
         <v>15.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
         <v>13.5</v>
@@ -4990,11 +4990,11 @@
         <v>3</v>
       </c>
       <c r="BG23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.68</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H24" t="n">
         <v>2.56</v>
@@ -5046,25 +5046,25 @@
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>2.24</v>
       </c>
       <c r="O24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="T24" t="n">
         <v>1.64</v>
@@ -5085,7 +5085,7 @@
         <v>13.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
@@ -5142,7 +5142,7 @@
         <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O25" t="n">
         <v>1.18</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H26" t="n">
         <v>2.96</v>
@@ -5452,7 +5452,7 @@
         <v>1.55</v>
       </c>
       <c r="S26" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -5461,7 +5461,7 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
         <v>1.72</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>2.72</v>
       </c>
       <c r="G27" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H27" t="n">
         <v>2.44</v>
       </c>
       <c r="I27" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="J27" t="n">
         <v>3.1</v>
@@ -5658,7 +5658,7 @@
         <v>1.54</v>
       </c>
       <c r="W27" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X27" t="n">
         <v>21</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>3.05</v>
       </c>
       <c r="G28" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I28" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J28" t="n">
         <v>3.95</v>
@@ -5846,10 +5846,10 @@
         <v>1.54</v>
       </c>
       <c r="U28" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V28" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W28" t="n">
         <v>1.44</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.14</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H30" t="n">
         <v>3.2</v>
@@ -6228,7 +6228,7 @@
         <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="T30" t="n">
         <v>1.53</v>
@@ -6237,7 +6237,7 @@
         <v>2.16</v>
       </c>
       <c r="V30" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
         <v>1.63</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
         <v>2.34</v>
       </c>
       <c r="O33" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P33" t="n">
         <v>1.48</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -7162,22 +7162,22 @@
         <v>3.25</v>
       </c>
       <c r="G35" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="H35" t="n">
         <v>2.28</v>
       </c>
       <c r="I35" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="K35" t="n">
         <v>3.95</v>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M35" t="n">
         <v>1.08</v>
@@ -7207,10 +7207,10 @@
         <v>2.04</v>
       </c>
       <c r="V35" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="W35" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X35" t="n">
         <v>15.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
         <v>3.4</v>
       </c>
       <c r="I38" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>3.6</v>
@@ -7774,10 +7774,10 @@
         <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="R38" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
         <v>2.86</v>
@@ -7786,7 +7786,7 @@
         <v>1.58</v>
       </c>
       <c r="U38" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V38" t="n">
         <v>1.33</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -7968,13 +7968,13 @@
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R39" t="n">
         <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="T39" t="n">
         <v>1.68</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
         <v>3.35</v>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J40" t="n">
         <v>3.15</v>
@@ -8159,7 +8159,7 @@
         <v>1.39</v>
       </c>
       <c r="P40" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q40" t="n">
         <v>2.16</v>
@@ -8177,7 +8177,7 @@
         <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W40" t="n">
         <v>1.64</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -8347,13 +8347,13 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O41" t="n">
         <v>1.18</v>
       </c>
       <c r="P41" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q41" t="n">
         <v>1.18</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
         <v>36</v>
       </c>
       <c r="AG42" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH42" t="n">
         <v>21</v>
@@ -8628,7 +8628,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR42" t="n">
         <v>10</v>
@@ -8649,7 +8649,7 @@
         <v>18.5</v>
       </c>
       <c r="AX42" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY42" t="n">
         <v>15.5</v>
@@ -8661,26 +8661,26 @@
         <v>32</v>
       </c>
       <c r="BB42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC42" t="n">
         <v>50</v>
       </c>
       <c r="BD42" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG42" t="n">
         <v>13</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
         <v>4.1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P43" t="n">
         <v>2.1</v>
@@ -8750,7 +8750,7 @@
         <v>1.43</v>
       </c>
       <c r="S43" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
         <v>2.06</v>
@@ -8822,13 +8822,13 @@
         <v>15</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR43" t="n">
         <v>5.8</v>
       </c>
       <c r="AS43" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT43" t="n">
         <v>7</v>
@@ -8837,7 +8837,7 @@
         <v>9.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW43" t="n">
         <v>6</v>
@@ -8849,7 +8849,7 @@
         <v>9</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA43" t="n">
         <v>5.9</v>
@@ -8861,7 +8861,7 @@
         <v>14</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE43" t="n">
         <v>6</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -8938,13 +8938,13 @@
         <v>1.83</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R44" t="n">
         <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T44" t="n">
         <v>1.89</v>
@@ -9019,7 +9019,7 @@
         <v>12.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS44" t="n">
         <v>5.6</v>
@@ -9055,7 +9055,7 @@
         <v>20</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE44" t="n">
         <v>5.6</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -9108,13 +9108,13 @@
         <v>1.81</v>
       </c>
       <c r="I45" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J45" t="n">
         <v>3.8</v>
       </c>
       <c r="K45" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L45" t="n">
         <v>1.44</v>
@@ -9144,13 +9144,13 @@
         <v>1.99</v>
       </c>
       <c r="U45" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V45" t="n">
         <v>2.2</v>
       </c>
       <c r="W45" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X45" t="n">
         <v>13</v>
@@ -9159,7 +9159,7 @@
         <v>7.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA45" t="n">
         <v>18.5</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>3.8</v>
       </c>
       <c r="J47" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K47" t="n">
         <v>950</v>
@@ -9508,7 +9508,7 @@
         <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N47" t="n">
         <v>1.01</v>
@@ -9535,7 +9535,7 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W47" t="n">
         <v>1.58</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G49" t="n">
         <v>3.1</v>
@@ -9884,7 +9884,7 @@
         <v>2.5</v>
       </c>
       <c r="I49" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J49" t="n">
         <v>3.45</v>
@@ -9923,7 +9923,7 @@
         <v>2.24</v>
       </c>
       <c r="V49" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W49" t="n">
         <v>1.47</v>
@@ -9983,13 +9983,13 @@
         <v>25</v>
       </c>
       <c r="AP49" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ49" t="n">
         <v>10</v>
       </c>
       <c r="AR49" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AS49" t="n">
         <v>4.8</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -10069,37 +10069,37 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="G50" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="H50" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="I50" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="J50" t="n">
         <v>3.5</v>
       </c>
       <c r="K50" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N50" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="O50" t="n">
         <v>1.12</v>
       </c>
       <c r="P50" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q50" t="n">
         <v>1.37</v>
@@ -10117,10 +10117,10 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W50" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G51" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="H51" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I51" t="n">
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="K51" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10287,25 +10287,25 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O51" t="n">
         <v>1.07</v>
       </c>
       <c r="P51" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q51" t="n">
         <v>1.3</v>
       </c>
       <c r="R51" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S51" t="n">
         <v>1.64</v>
       </c>
       <c r="T51" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U51" t="n">
         <v>1.87</v>
@@ -10314,7 +10314,7 @@
         <v>1.06</v>
       </c>
       <c r="W51" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="X51" t="n">
         <v>65</v>
@@ -10329,7 +10329,7 @@
         <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC51" t="n">
         <v>26</v>
@@ -10344,7 +10344,7 @@
         <v>14</v>
       </c>
       <c r="AG51" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH51" t="n">
         <v>38</v>
@@ -10353,10 +10353,10 @@
         <v>150</v>
       </c>
       <c r="AJ51" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK51" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AL51" t="n">
         <v>38</v>
@@ -10365,22 +10365,22 @@
         <v>140</v>
       </c>
       <c r="AN51" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AO51" t="n">
         <v>190</v>
       </c>
       <c r="AP51" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR51" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT51" t="n">
         <v>12</v>
@@ -10389,10 +10389,10 @@
         <v>15</v>
       </c>
       <c r="AV51" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX51" t="n">
         <v>8.6</v>
@@ -10401,10 +10401,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ51" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB51" t="n">
         <v>8</v>
@@ -10413,20 +10413,20 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF51" t="n">
         <v>2.32</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -10487,7 +10487,7 @@
         <v>1.14</v>
       </c>
       <c r="P52" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q52" t="n">
         <v>1.44</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
         <v>1.52</v>
       </c>
       <c r="S53" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="T53" t="n">
         <v>1.54</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -10845,43 +10845,43 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="G54" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="H54" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="J54" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K54" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="L54" t="n">
         <v>1.27</v>
       </c>
       <c r="M54" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N54" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O54" t="n">
         <v>1.2</v>
       </c>
       <c r="P54" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q54" t="n">
         <v>1.64</v>
       </c>
       <c r="R54" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
         <v>2.38</v>
@@ -10893,10 +10893,10 @@
         <v>1.01</v>
       </c>
       <c r="V54" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="W54" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11386,7 @@
         <v>4.6</v>
       </c>
       <c r="BE56" t="n">
-        <v>4.7</v>
+        <v>42</v>
       </c>
       <c r="BF56" t="n">
         <v>20</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G57" t="n">
         <v>2.48</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
         <v>18.5</v>
       </c>
       <c r="AC59" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD59" t="n">
         <v>12.5</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
         <v>4.2</v>
       </c>
       <c r="L60" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M60" t="n">
         <v>1.06</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -12233,22 +12233,22 @@
         <v>1.18</v>
       </c>
       <c r="P61" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R61" t="n">
         <v>1.66</v>
       </c>
       <c r="S61" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T61" t="n">
         <v>1.6</v>
       </c>
       <c r="U61" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V61" t="n">
         <v>1.25</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -12421,28 +12421,28 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O62" t="n">
         <v>1.43</v>
       </c>
       <c r="P62" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R62" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S62" t="n">
         <v>3.85</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V62" t="n">
         <v>1.64</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G63" t="n">
         <v>2.1</v>
@@ -12648,22 +12648,22 @@
         <v>1000</v>
       </c>
       <c r="Y63" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z63" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA63" t="n">
         <v>90</v>
       </c>
       <c r="AB63" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC63" t="n">
         <v>11.5</v>
       </c>
       <c r="AD63" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE63" t="n">
         <v>55</v>
@@ -12681,10 +12681,10 @@
         <v>60</v>
       </c>
       <c r="AJ63" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK63" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL63" t="n">
         <v>44</v>
@@ -12699,16 +12699,16 @@
         <v>48</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="AQ63" t="n">
         <v>10.5</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.18</v>
+        <v>19</v>
       </c>
       <c r="AS63" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="AT63" t="n">
         <v>7.6</v>
@@ -12720,7 +12720,7 @@
         <v>10.5</v>
       </c>
       <c r="AW63" t="n">
-        <v>2.22</v>
+        <v>2.86</v>
       </c>
       <c r="AX63" t="n">
         <v>9.6</v>
@@ -12732,29 +12732,29 @@
         <v>11</v>
       </c>
       <c r="BA63" t="n">
-        <v>2.24</v>
+        <v>2.86</v>
       </c>
       <c r="BB63" t="n">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="BC63" t="n">
         <v>14</v>
       </c>
       <c r="BD63" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="BE63" t="n">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="BF63" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG63" t="n">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -12788,13 +12788,13 @@
         <v>1.96</v>
       </c>
       <c r="G64" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H64" t="n">
         <v>4.3</v>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>3.35</v>
@@ -12833,10 +12833,10 @@
         <v>1.72</v>
       </c>
       <c r="V64" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W64" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G66" t="n">
         <v>1.58</v>
@@ -13218,7 +13218,7 @@
         <v>1.59</v>
       </c>
       <c r="U66" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V66" t="n">
         <v>1.17</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -13397,10 +13397,10 @@
         <v>1.17</v>
       </c>
       <c r="P67" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R67" t="n">
         <v>1.64</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -13600,7 +13600,7 @@
         <v>2.06</v>
       </c>
       <c r="S68" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="T68" t="n">
         <v>1.42</v>
@@ -13609,7 +13609,7 @@
         <v>2.68</v>
       </c>
       <c r="V68" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W68" t="n">
         <v>2.26</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -13755,19 +13755,19 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="G69" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H69" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="I69" t="n">
         <v>1000</v>
       </c>
       <c r="J69" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="K69" t="n">
         <v>1000</v>
@@ -13785,25 +13785,25 @@
         <v>1.11</v>
       </c>
       <c r="P69" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q69" t="n">
         <v>1.34</v>
       </c>
       <c r="R69" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S69" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="T69" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="U69" t="n">
         <v>1.01</v>
       </c>
       <c r="V69" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W69" t="n">
         <v>3.2</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -14143,22 +14143,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="G71" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="H71" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="I71" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K71" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -14191,13 +14191,13 @@
         <v>2.62</v>
       </c>
       <c r="V71" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W71" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="X71" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y71" t="n">
         <v>19</v>
@@ -14206,7 +14206,7 @@
         <v>25</v>
       </c>
       <c r="AA71" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB71" t="n">
         <v>17.5</v>
@@ -14233,7 +14233,7 @@
         <v>32</v>
       </c>
       <c r="AJ71" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK71" t="n">
         <v>24</v>
@@ -14248,10 +14248,10 @@
         <v>12.5</v>
       </c>
       <c r="AO71" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP71" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ71" t="n">
         <v>15.5</v>
@@ -14275,7 +14275,7 @@
         <v>6.2</v>
       </c>
       <c r="AX71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY71" t="n">
         <v>10.5</v>
@@ -14287,13 +14287,13 @@
         <v>6.4</v>
       </c>
       <c r="BB71" t="n">
-        <v>27</v>
+        <v>6.6</v>
       </c>
       <c r="BC71" t="n">
         <v>18.5</v>
       </c>
       <c r="BD71" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE71" t="n">
         <v>7</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -14352,7 +14352,7 @@
         <v>4.7</v>
       </c>
       <c r="K72" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="L72" t="n">
         <v>1.18</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
         <v>1.74</v>
       </c>
       <c r="G73" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H73" t="n">
         <v>4.3</v>
@@ -14552,7 +14552,7 @@
         <v>1.28</v>
       </c>
       <c r="M73" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N73" t="n">
         <v>5.6</v>
@@ -14579,7 +14579,7 @@
         <v>2.2</v>
       </c>
       <c r="V73" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W73" t="n">
         <v>2.14</v>
@@ -14588,7 +14588,7 @@
         <v>32</v>
       </c>
       <c r="Y73" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z73" t="n">
         <v>48</v>
@@ -14639,22 +14639,22 @@
         <v>44</v>
       </c>
       <c r="AP73" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ73" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ73" t="n">
-        <v>17</v>
-      </c>
       <c r="AR73" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS73" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT73" t="n">
         <v>9.6</v>
       </c>
       <c r="AU73" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV73" t="n">
         <v>13.5</v>
@@ -14666,16 +14666,16 @@
         <v>10</v>
       </c>
       <c r="AY73" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ73" t="n">
         <v>12</v>
       </c>
       <c r="BA73" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB73" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BC73" t="n">
         <v>12</v>
@@ -14684,17 +14684,17 @@
         <v>19</v>
       </c>
       <c r="BE73" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF73" t="n">
         <v>5.6</v>
       </c>
       <c r="BG73" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -14755,7 +14755,7 @@
         <v>1.15</v>
       </c>
       <c r="P74" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q74" t="n">
         <v>1.45</v>
@@ -14764,19 +14764,19 @@
         <v>1.73</v>
       </c>
       <c r="S74" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T74" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="U74" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="V74" t="n">
         <v>1.19</v>
       </c>
       <c r="W74" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X74" t="n">
         <v>38</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -14919,16 +14919,16 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G75" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H75" t="n">
         <v>2.72</v>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>3.2</v>
@@ -14943,13 +14943,13 @@
         <v>1.07</v>
       </c>
       <c r="N75" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O75" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P75" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q75" t="n">
         <v>1.99</v>
@@ -14958,16 +14958,16 @@
         <v>1.31</v>
       </c>
       <c r="S75" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T75" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="U75" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="V75" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W75" t="n">
         <v>1.51</v>
@@ -14982,13 +14982,13 @@
         <v>24</v>
       </c>
       <c r="AA75" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB75" t="n">
         <v>13</v>
       </c>
       <c r="AC75" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD75" t="n">
         <v>15.5</v>
@@ -15003,10 +15003,10 @@
         <v>15</v>
       </c>
       <c r="AH75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI75" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ75" t="n">
         <v>55</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -15218,10 +15218,10 @@
         <v>80</v>
       </c>
       <c r="AO76" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AP76" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ76" t="n">
         <v>14.5</v>
@@ -15233,7 +15233,7 @@
         <v>11</v>
       </c>
       <c r="AT76" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU76" t="n">
         <v>14.5</v>
@@ -15245,7 +15245,7 @@
         <v>11.5</v>
       </c>
       <c r="AX76" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY76" t="n">
         <v>26</v>
@@ -15257,16 +15257,16 @@
         <v>21</v>
       </c>
       <c r="BB76" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC76" t="n">
         <v>10</v>
-      </c>
-      <c r="BC76" t="n">
-        <v>9.6</v>
       </c>
       <c r="BD76" t="n">
         <v>55</v>
       </c>
       <c r="BE76" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF76" t="n">
         <v>55</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -15307,19 +15307,19 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G77" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H77" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I77" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K77" t="n">
         <v>4.7</v>
@@ -15334,31 +15334,31 @@
         <v>5.3</v>
       </c>
       <c r="O77" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P77" t="n">
         <v>2.44</v>
       </c>
       <c r="Q77" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R77" t="n">
         <v>1.6</v>
       </c>
-      <c r="R77" t="n">
-        <v>1.58</v>
-      </c>
       <c r="S77" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T77" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="U77" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V77" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W77" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X77" t="n">
         <v>25</v>
@@ -15376,7 +15376,7 @@
         <v>12.5</v>
       </c>
       <c r="AC77" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD77" t="n">
         <v>21</v>
@@ -15385,10 +15385,10 @@
         <v>60</v>
       </c>
       <c r="AF77" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG77" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH77" t="n">
         <v>18</v>
@@ -15400,7 +15400,7 @@
         <v>970</v>
       </c>
       <c r="AK77" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL77" t="n">
         <v>29</v>
@@ -15421,56 +15421,56 @@
         <v>19</v>
       </c>
       <c r="AR77" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS77" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT77" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU77" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AV77" t="n">
         <v>14.5</v>
       </c>
       <c r="AW77" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX77" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY77" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ77" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA77" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BB77" t="n">
         <v>15.5</v>
       </c>
       <c r="BC77" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD77" t="n">
         <v>21</v>
       </c>
       <c r="BE77" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BF77" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG77" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -15501,10 +15501,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G78" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H78" t="n">
         <v>3.65</v>
@@ -15552,7 +15552,7 @@
         <v>1.27</v>
       </c>
       <c r="W78" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -15695,55 +15695,55 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G79" t="n">
         <v>2.26</v>
       </c>
       <c r="H79" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I79" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K79" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
       </c>
       <c r="M79" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N79" t="n">
         <v>6.2</v>
       </c>
       <c r="O79" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P79" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T79" t="n">
         <v>1.49</v>
       </c>
-      <c r="R79" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1.47</v>
-      </c>
       <c r="U79" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="V79" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W79" t="n">
         <v>1.79</v>
@@ -15764,10 +15764,10 @@
         <v>17.5</v>
       </c>
       <c r="AC79" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD79" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE79" t="n">
         <v>32</v>
@@ -15776,10 +15776,10 @@
         <v>19.5</v>
       </c>
       <c r="AG79" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH79" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AI79" t="n">
         <v>34</v>
@@ -15797,25 +15797,25 @@
         <v>60</v>
       </c>
       <c r="AN79" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO79" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP79" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ79" t="n">
         <v>17.5</v>
       </c>
       <c r="AR79" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AS79" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT79" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU79" t="n">
         <v>9.199999999999999</v>
@@ -15824,22 +15824,22 @@
         <v>12.5</v>
       </c>
       <c r="AW79" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AX79" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY79" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ79" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA79" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB79" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC79" t="n">
         <v>16.5</v>
@@ -15851,14 +15851,14 @@
         <v>40</v>
       </c>
       <c r="BF79" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BG79" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -16086,16 +16086,16 @@
         <v>1.43</v>
       </c>
       <c r="G81" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="H81" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="I81" t="n">
         <v>11</v>
       </c>
       <c r="J81" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K81" t="n">
         <v>5.7</v>
@@ -16134,7 +16134,7 @@
         <v>1.1</v>
       </c>
       <c r="W81" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="X81" t="n">
         <v>1000</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -16277,16 +16277,16 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G82" t="n">
         <v>3.55</v>
       </c>
       <c r="H82" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I82" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="J82" t="n">
         <v>3.7</v>
@@ -16307,13 +16307,13 @@
         <v>1.26</v>
       </c>
       <c r="P82" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q82" t="n">
         <v>1.78</v>
       </c>
       <c r="R82" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S82" t="n">
         <v>2.94</v>
@@ -16325,7 +16325,7 @@
         <v>2.34</v>
       </c>
       <c r="V82" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W82" t="n">
         <v>1.39</v>
@@ -16337,7 +16337,7 @@
         <v>12.5</v>
       </c>
       <c r="Z82" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA82" t="n">
         <v>29</v>
@@ -16346,7 +16346,7 @@
         <v>16.5</v>
       </c>
       <c r="AC82" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD82" t="n">
         <v>12</v>
@@ -16367,7 +16367,7 @@
         <v>34</v>
       </c>
       <c r="AJ82" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK82" t="n">
         <v>40</v>
@@ -16376,7 +16376,7 @@
         <v>44</v>
       </c>
       <c r="AM82" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN82" t="n">
         <v>32</v>
@@ -16394,13 +16394,13 @@
         <v>13.5</v>
       </c>
       <c r="AS82" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT82" t="n">
         <v>13</v>
       </c>
       <c r="AU82" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV82" t="n">
         <v>9.6</v>
@@ -16409,7 +16409,7 @@
         <v>18.5</v>
       </c>
       <c r="AX82" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY82" t="n">
         <v>12</v>
@@ -16418,29 +16418,29 @@
         <v>13.5</v>
       </c>
       <c r="BA82" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB82" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC82" t="n">
         <v>30</v>
       </c>
       <c r="BD82" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE82" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF82" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG82" t="n">
         <v>11.5</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
         <v>2.62</v>
       </c>
       <c r="H83" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I83" t="n">
         <v>3.4</v>
@@ -16489,7 +16489,7 @@
         <v>3.35</v>
       </c>
       <c r="L83" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M83" t="n">
         <v>1.09</v>
@@ -16513,7 +16513,7 @@
         <v>4.2</v>
       </c>
       <c r="T83" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U83" t="n">
         <v>2</v>
@@ -16540,7 +16540,7 @@
         <v>10.5</v>
       </c>
       <c r="AC83" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD83" t="n">
         <v>16.5</v>
@@ -16600,7 +16600,7 @@
         <v>12.5</v>
       </c>
       <c r="AW83" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX83" t="n">
         <v>14</v>
@@ -16624,17 +16624,17 @@
         <v>5.1</v>
       </c>
       <c r="BE83" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF83" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG83" t="n">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -16668,13 +16668,13 @@
         <v>3.1</v>
       </c>
       <c r="G84" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H84" t="n">
         <v>2.2</v>
       </c>
       <c r="I84" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="J84" t="n">
         <v>2.86</v>
@@ -16713,10 +16713,10 @@
         <v>1.84</v>
       </c>
       <c r="V84" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W84" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X84" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -16862,10 +16862,10 @@
         <v>2.12</v>
       </c>
       <c r="G85" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H85" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I85" t="n">
         <v>4.5</v>
@@ -16874,7 +16874,7 @@
         <v>2.8</v>
       </c>
       <c r="K85" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L85" t="n">
         <v>1.01</v>
@@ -16883,10 +16883,10 @@
         <v>1.01</v>
       </c>
       <c r="N85" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="O85" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="P85" t="n">
         <v>1.45</v>
@@ -16910,7 +16910,7 @@
         <v>1.28</v>
       </c>
       <c r="W85" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X85" t="n">
         <v>1000</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -17277,10 +17277,10 @@
         <v>1.33</v>
       </c>
       <c r="P87" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q87" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R87" t="n">
         <v>1.37</v>
@@ -17289,7 +17289,7 @@
         <v>3.6</v>
       </c>
       <c r="T87" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U87" t="n">
         <v>1.7</v>
@@ -17298,7 +17298,7 @@
         <v>1.09</v>
       </c>
       <c r="W87" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="X87" t="n">
         <v>15</v>
@@ -17349,7 +17349,7 @@
         <v>250</v>
       </c>
       <c r="AN87" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO87" t="n">
         <v>360</v>
@@ -17388,7 +17388,7 @@
         <v>30</v>
       </c>
       <c r="BA87" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB87" t="n">
         <v>10</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -17447,25 +17447,25 @@
         <v>2.8</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I88" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K88" t="n">
         <v>3.35</v>
       </c>
       <c r="L88" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M88" t="n">
         <v>1.1</v>
       </c>
       <c r="N88" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O88" t="n">
         <v>1.45</v>
@@ -17489,7 +17489,7 @@
         <v>1.9</v>
       </c>
       <c r="V88" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W88" t="n">
         <v>1.56</v>
@@ -17501,7 +17501,7 @@
         <v>12</v>
       </c>
       <c r="Z88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA88" t="n">
         <v>70</v>
@@ -17513,10 +17513,10 @@
         <v>8.6</v>
       </c>
       <c r="AD88" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE88" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF88" t="n">
         <v>21</v>
@@ -17546,7 +17546,7 @@
         <v>46</v>
       </c>
       <c r="AO88" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP88" t="n">
         <v>8.800000000000001</v>
@@ -17558,7 +17558,7 @@
         <v>14.5</v>
       </c>
       <c r="AS88" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT88" t="n">
         <v>7.8</v>
@@ -17582,29 +17582,29 @@
         <v>17</v>
       </c>
       <c r="BA88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC88" t="n">
         <v>4</v>
       </c>
-      <c r="BB88" t="n">
+      <c r="BD88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF88" t="n">
         <v>4</v>
       </c>
-      <c r="BC88" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD88" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE88" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF88" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BG88" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -17635,16 +17635,16 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G89" t="n">
         <v>1.38</v>
       </c>
       <c r="H89" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="I89" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="J89" t="n">
         <v>5.2</v>
@@ -17659,7 +17659,7 @@
         <v>1.03</v>
       </c>
       <c r="N89" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O89" t="n">
         <v>1.2</v>
@@ -17683,7 +17683,7 @@
         <v>1.91</v>
       </c>
       <c r="V89" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W89" t="n">
         <v>3.6</v>
@@ -17692,13 +17692,13 @@
         <v>23</v>
       </c>
       <c r="Y89" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Z89" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA89" t="n">
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="AB89" t="n">
         <v>9.800000000000001</v>
@@ -17707,10 +17707,10 @@
         <v>12.5</v>
       </c>
       <c r="AD89" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AE89" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AF89" t="n">
         <v>8.800000000000001</v>
@@ -17719,40 +17719,40 @@
         <v>10.5</v>
       </c>
       <c r="AH89" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI89" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ89" t="n">
         <v>13.5</v>
       </c>
       <c r="AK89" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL89" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM89" t="n">
         <v>160</v>
       </c>
       <c r="AN89" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AO89" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AP89" t="n">
         <v>20</v>
       </c>
       <c r="AQ89" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR89" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS89" t="n">
         <v>11</v>
-      </c>
-      <c r="AS89" t="n">
-        <v>12</v>
       </c>
       <c r="AT89" t="n">
         <v>8.4</v>
@@ -17761,10 +17761,10 @@
         <v>10.5</v>
       </c>
       <c r="AV89" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="AW89" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX89" t="n">
         <v>7.6</v>
@@ -17776,7 +17776,7 @@
         <v>21</v>
       </c>
       <c r="BA89" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB89" t="n">
         <v>9.800000000000001</v>
@@ -17785,20 +17785,20 @@
         <v>12</v>
       </c>
       <c r="BD89" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BE89" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF89" t="n">
         <v>4.5</v>
       </c>
       <c r="BG89" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -17829,10 +17829,10 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G90" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H90" t="n">
         <v>3.75</v>
@@ -17841,10 +17841,10 @@
         <v>3.9</v>
       </c>
       <c r="J90" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K90" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L90" t="n">
         <v>1.44</v>
@@ -17880,7 +17880,7 @@
         <v>1.35</v>
       </c>
       <c r="W90" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X90" t="n">
         <v>12.5</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -18023,25 +18023,25 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G91" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H91" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I91" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J91" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K91" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L91" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M91" t="n">
         <v>1.07</v>
@@ -18056,19 +18056,19 @@
         <v>1.84</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R91" t="n">
         <v>1.32</v>
       </c>
       <c r="S91" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T91" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="U91" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="V91" t="n">
         <v>2.04</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -18220,16 +18220,16 @@
         <v>3.35</v>
       </c>
       <c r="G92" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H92" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="I92" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="J92" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K92" t="n">
         <v>3.55</v>
@@ -18241,7 +18241,7 @@
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O92" t="n">
         <v>1.38</v>
@@ -18265,13 +18265,13 @@
         <v>1.01</v>
       </c>
       <c r="V92" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W92" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X92" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y92" t="n">
         <v>11</v>
@@ -18280,10 +18280,10 @@
         <v>17.5</v>
       </c>
       <c r="AA92" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB92" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC92" t="n">
         <v>8</v>
@@ -18295,10 +18295,10 @@
         <v>34</v>
       </c>
       <c r="AF92" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG92" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH92" t="n">
         <v>23</v>
@@ -18307,19 +18307,19 @@
         <v>55</v>
       </c>
       <c r="AJ92" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AK92" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL92" t="n">
         <v>75</v>
       </c>
       <c r="AM92" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN92" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AO92" t="n">
         <v>29</v>
@@ -18334,7 +18334,7 @@
         <v>12</v>
       </c>
       <c r="AS92" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT92" t="n">
         <v>10</v>
@@ -18346,7 +18346,7 @@
         <v>9.6</v>
       </c>
       <c r="AW92" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AX92" t="n">
         <v>21</v>
@@ -18358,29 +18358,29 @@
         <v>16</v>
       </c>
       <c r="BA92" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB92" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC92" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD92" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE92" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF92" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG92" t="n">
         <v>17</v>
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -18417,16 +18417,16 @@
         <v>2.48</v>
       </c>
       <c r="H93" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J93" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K93" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L93" t="n">
         <v>1.31</v>
@@ -18435,13 +18435,13 @@
         <v>1.01</v>
       </c>
       <c r="N93" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="O93" t="n">
         <v>1.29</v>
       </c>
       <c r="P93" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q93" t="n">
         <v>1.87</v>
@@ -18450,7 +18450,7 @@
         <v>1.21</v>
       </c>
       <c r="S93" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T93" t="n">
         <v>1.01</v>
@@ -18459,10 +18459,10 @@
         <v>1.01</v>
       </c>
       <c r="V93" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W93" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="X93" t="n">
         <v>1000</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -18799,10 +18799,10 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G95" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H95" t="n">
         <v>12</v>
@@ -18814,7 +18814,7 @@
         <v>5.3</v>
       </c>
       <c r="K95" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L95" t="n">
         <v>1.01</v>
@@ -18823,22 +18823,22 @@
         <v>1.02</v>
       </c>
       <c r="N95" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O95" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P95" t="n">
         <v>1.86</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R95" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S95" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="T95" t="n">
         <v>1.01</v>
@@ -18850,7 +18850,7 @@
         <v>1.01</v>
       </c>
       <c r="W95" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="X95" t="n">
         <v>1000</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -18993,16 +18993,16 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="G96" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="H96" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="I96" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="J96" t="n">
         <v>3.2</v>
@@ -19020,13 +19020,13 @@
         <v>3.3</v>
       </c>
       <c r="O96" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P96" t="n">
         <v>1.8</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R96" t="n">
         <v>1.3</v>
@@ -19041,10 +19041,10 @@
         <v>2.04</v>
       </c>
       <c r="V96" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W96" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="X96" t="n">
         <v>15</v>
@@ -19059,7 +19059,7 @@
         <v>1000</v>
       </c>
       <c r="AB96" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC96" t="n">
         <v>8.800000000000001</v>
@@ -19074,7 +19074,7 @@
         <v>1000</v>
       </c>
       <c r="AG96" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH96" t="n">
         <v>1000</v>
@@ -19104,13 +19104,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ96" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR96" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS96" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT96" t="n">
         <v>8</v>
@@ -19119,10 +19119,10 @@
         <v>6</v>
       </c>
       <c r="AV96" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW96" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX96" t="n">
         <v>13</v>
@@ -19134,29 +19134,29 @@
         <v>13.5</v>
       </c>
       <c r="BA96" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB96" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC96" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD96" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE96" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF96" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG96" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G97" t="n">
         <v>3.45</v>
@@ -19199,10 +19199,10 @@
         <v>2.4</v>
       </c>
       <c r="J97" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K97" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L97" t="n">
         <v>1.01</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
         <v>4.1</v>
       </c>
       <c r="J98" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K98" t="n">
         <v>4.3</v>
@@ -19405,28 +19405,28 @@
         <v>1.06</v>
       </c>
       <c r="N98" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O98" t="n">
         <v>1.29</v>
       </c>
       <c r="P98" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R98" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S98" t="n">
         <v>3.15</v>
       </c>
       <c r="T98" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="U98" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V98" t="n">
         <v>1.32</v>
@@ -19438,19 +19438,19 @@
         <v>18</v>
       </c>
       <c r="Y98" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z98" t="n">
         <v>29</v>
       </c>
       <c r="AA98" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB98" t="n">
         <v>12.5</v>
       </c>
       <c r="AC98" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD98" t="n">
         <v>17</v>
@@ -19483,13 +19483,13 @@
         <v>100</v>
       </c>
       <c r="AN98" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO98" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP98" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ98" t="n">
         <v>10.5</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -19963,16 +19963,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G101" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H101" t="n">
         <v>5.5</v>
       </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J101" t="n">
         <v>3.95</v>
@@ -19987,25 +19987,25 @@
         <v>1.06</v>
       </c>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O101" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P101" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R101" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S101" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T101" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U101" t="n">
         <v>2.06</v>
@@ -20044,7 +20044,7 @@
         <v>11</v>
       </c>
       <c r="AG101" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH101" t="n">
         <v>20</v>
@@ -20077,13 +20077,13 @@
         <v>17</v>
       </c>
       <c r="AR101" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS101" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT101" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU101" t="n">
         <v>8.199999999999999</v>
@@ -20092,19 +20092,19 @@
         <v>18.5</v>
       </c>
       <c r="AW101" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX101" t="n">
         <v>9.4</v>
       </c>
       <c r="AY101" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ101" t="n">
         <v>17.5</v>
       </c>
       <c r="BA101" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB101" t="n">
         <v>15.5</v>
@@ -20113,20 +20113,20 @@
         <v>16</v>
       </c>
       <c r="BD101" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE101" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF101" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG101" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -20163,10 +20163,10 @@
         <v>3.3</v>
       </c>
       <c r="H102" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I102" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J102" t="n">
         <v>3.25</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -20351,25 +20351,25 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G103" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H103" t="n">
         <v>6.2</v>
       </c>
       <c r="I103" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J103" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K103" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L103" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M103" t="n">
         <v>1.05</v>
@@ -20378,40 +20378,40 @@
         <v>4.3</v>
       </c>
       <c r="O103" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P103" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R103" t="n">
         <v>1.45</v>
       </c>
       <c r="S103" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T103" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U103" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V103" t="n">
         <v>1.17</v>
       </c>
       <c r="W103" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="X103" t="n">
         <v>20</v>
       </c>
       <c r="Y103" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z103" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA103" t="n">
         <v>200</v>
@@ -20429,13 +20429,13 @@
         <v>100</v>
       </c>
       <c r="AF103" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG103" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG103" t="n">
-        <v>11</v>
-      </c>
       <c r="AH103" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI103" t="n">
         <v>80</v>
@@ -20468,10 +20468,10 @@
         <v>40</v>
       </c>
       <c r="AS103" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT103" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU103" t="n">
         <v>8.800000000000001</v>
@@ -20480,19 +20480,19 @@
         <v>18.5</v>
       </c>
       <c r="AW103" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX103" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY103" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ103" t="n">
         <v>18.5</v>
       </c>
       <c r="BA103" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB103" t="n">
         <v>11.5</v>
@@ -20501,20 +20501,20 @@
         <v>12.5</v>
       </c>
       <c r="BD103" t="n">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BE103" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF103" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG103" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G104" t="n">
         <v>3.2</v>
@@ -20554,7 +20554,7 @@
         <v>2.52</v>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J104" t="n">
         <v>3.45</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
         <v>2.1</v>
       </c>
       <c r="G105" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H105" t="n">
         <v>4.1</v>
@@ -20754,13 +20754,13 @@
         <v>3.2</v>
       </c>
       <c r="K105" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L105" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M105" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N105" t="n">
         <v>3.35</v>
@@ -20769,13 +20769,13 @@
         <v>1.37</v>
       </c>
       <c r="P105" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R105" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S105" t="n">
         <v>3.8</v>
@@ -20790,10 +20790,10 @@
         <v>1.28</v>
       </c>
       <c r="W105" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X105" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y105" t="n">
         <v>15</v>
@@ -20808,7 +20808,7 @@
         <v>9</v>
       </c>
       <c r="AC105" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD105" t="n">
         <v>18.5</v>
@@ -20817,7 +20817,7 @@
         <v>60</v>
       </c>
       <c r="AF105" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG105" t="n">
         <v>11</v>
@@ -20853,13 +20853,13 @@
         <v>12</v>
       </c>
       <c r="AR105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS105" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT105" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU105" t="n">
         <v>6.6</v>
@@ -20868,19 +20868,19 @@
         <v>15</v>
       </c>
       <c r="AW105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX105" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY105" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ105" t="n">
         <v>15.5</v>
       </c>
       <c r="BA105" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB105" t="n">
         <v>21</v>
@@ -20889,20 +20889,20 @@
         <v>19.5</v>
       </c>
       <c r="BD105" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE105" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF105" t="n">
         <v>15</v>
       </c>
       <c r="BG105" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G108" t="n">
         <v>2.7</v>
@@ -21330,7 +21330,7 @@
         <v>2.76</v>
       </c>
       <c r="I108" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J108" t="n">
         <v>3.6</v>
@@ -21348,22 +21348,22 @@
         <v>4.3</v>
       </c>
       <c r="O108" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P108" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R108" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S108" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T108" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="U108" t="n">
         <v>2.36</v>
@@ -21378,7 +21378,7 @@
         <v>21</v>
       </c>
       <c r="Y108" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z108" t="n">
         <v>22</v>
@@ -21390,7 +21390,7 @@
         <v>13.5</v>
       </c>
       <c r="AC108" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD108" t="n">
         <v>13.5</v>
@@ -21402,7 +21402,7 @@
         <v>19.5</v>
       </c>
       <c r="AG108" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH108" t="n">
         <v>16.5</v>
@@ -21438,7 +21438,7 @@
         <v>17.5</v>
       </c>
       <c r="AS108" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT108" t="n">
         <v>11</v>
@@ -21456,35 +21456,35 @@
         <v>15.5</v>
       </c>
       <c r="AY108" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ108" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA108" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB108" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC108" t="n">
         <v>19</v>
       </c>
       <c r="BD108" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE108" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF108" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG108" t="n">
         <v>18.5</v>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -21515,25 +21515,25 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G109" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="H109" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I109" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J109" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K109" t="n">
         <v>3.05</v>
       </c>
       <c r="L109" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="M109" t="n">
         <v>1.15</v>
@@ -21548,7 +21548,7 @@
         <v>1.41</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
         <v>1.14</v>
@@ -21563,122 +21563,122 @@
         <v>1.61</v>
       </c>
       <c r="V109" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W109" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X109" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Y109" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY109" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB109" t="n">
+      <c r="AZ109" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA109" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC109" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF109" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG109" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO109" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP109" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AQ109" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AR109" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS109" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT109" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AU109" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AV109" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AW109" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AX109" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY109" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ109" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA109" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BB109" t="n">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="BC109" t="n">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="BD109" t="n">
-        <v>2.46</v>
+        <v>8.4</v>
       </c>
       <c r="BE109" t="n">
-        <v>2.46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF109" t="n">
-        <v>2.38</v>
+        <v>7.8</v>
       </c>
       <c r="BG109" t="n">
-        <v>2.46</v>
+        <v>8.4</v>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -21709,19 +21709,19 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G110" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H110" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="I110" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="J110" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K110" t="n">
         <v>4.8</v>
@@ -21733,7 +21733,7 @@
         <v>1.01</v>
       </c>
       <c r="N110" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O110" t="n">
         <v>1.12</v>
@@ -21757,10 +21757,10 @@
         <v>2.74</v>
       </c>
       <c r="V110" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W110" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X110" t="n">
         <v>42</v>
@@ -21841,7 +21841,7 @@
         <v>20</v>
       </c>
       <c r="AX110" t="n">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="AY110" t="n">
         <v>4.7</v>
@@ -21850,7 +21850,7 @@
         <v>5</v>
       </c>
       <c r="BA110" t="n">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="BB110" t="n">
         <v>6</v>
@@ -21868,11 +21868,11 @@
         <v>4</v>
       </c>
       <c r="BG110" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -22136,7 +22136,7 @@
         <v>1.42</v>
       </c>
       <c r="S112" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T112" t="n">
         <v>1.76</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -22342,7 +22342,7 @@
         <v>1.29</v>
       </c>
       <c r="W113" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X113" t="n">
         <v>16.5</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -22488,13 +22488,13 @@
         <v>2.6</v>
       </c>
       <c r="G114" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H114" t="n">
         <v>3.3</v>
       </c>
       <c r="I114" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J114" t="n">
         <v>3.1</v>
@@ -22536,7 +22536,7 @@
         <v>1.42</v>
       </c>
       <c r="W114" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X114" t="n">
         <v>9.800000000000001</v>
@@ -22620,7 +22620,7 @@
         <v>14</v>
       </c>
       <c r="AY114" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ114" t="n">
         <v>18.5</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -22742,7 +22742,7 @@
         <v>16.5</v>
       </c>
       <c r="AA115" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB115" t="n">
         <v>16</v>
@@ -22826,13 +22826,13 @@
         <v>28</v>
       </c>
       <c r="BC115" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD115" t="n">
         <v>34</v>
       </c>
       <c r="BE115" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF115" t="n">
         <v>22</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -22873,22 +22873,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="G116" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="H116" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I116" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="J116" t="n">
         <v>6.8</v>
       </c>
       <c r="K116" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L116" t="n">
         <v>1.28</v>
@@ -22897,22 +22897,22 @@
         <v>1.03</v>
       </c>
       <c r="N116" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O116" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P116" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R116" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S116" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="T116" t="n">
         <v>2.22</v>
@@ -22957,13 +22957,13 @@
         <v>60</v>
       </c>
       <c r="AH116" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI116" t="n">
         <v>46</v>
       </c>
       <c r="AJ116" t="n">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="AK116" t="n">
         <v>310</v>
@@ -22975,13 +22975,13 @@
         <v>220</v>
       </c>
       <c r="AN116" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="AO116" t="n">
         <v>4</v>
       </c>
       <c r="AP116" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ116" t="n">
         <v>8.800000000000001</v>
@@ -23011,7 +23011,7 @@
         <v>48</v>
       </c>
       <c r="AZ116" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BA116" t="n">
         <v>38</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -23067,22 +23067,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G117" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H117" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I117" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>3.05</v>
       </c>
       <c r="K117" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L117" t="n">
         <v>1.01</v>
@@ -23115,10 +23115,10 @@
         <v>1.84</v>
       </c>
       <c r="V117" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W117" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X117" t="n">
         <v>11</v>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G118" t="n">
         <v>1.54</v>
@@ -23339,7 +23339,7 @@
         <v>250</v>
       </c>
       <c r="AF118" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AG118" t="n">
         <v>13</v>
@@ -23375,10 +23375,10 @@
         <v>18.5</v>
       </c>
       <c r="AR118" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS118" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT118" t="n">
         <v>5.4</v>
@@ -23387,10 +23387,10 @@
         <v>8.6</v>
       </c>
       <c r="AV118" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AW118" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AX118" t="n">
         <v>6.8</v>
@@ -23399,10 +23399,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ118" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA118" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB118" t="n">
         <v>12</v>
@@ -23411,20 +23411,20 @@
         <v>17.5</v>
       </c>
       <c r="BD118" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE118" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF118" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG118" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -23458,7 +23458,7 @@
         <v>1.95</v>
       </c>
       <c r="G119" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="H119" t="n">
         <v>3.85</v>
@@ -23467,7 +23467,7 @@
         <v>5.9</v>
       </c>
       <c r="J119" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="K119" t="n">
         <v>3.6</v>
@@ -23476,7 +23476,7 @@
         <v>1.45</v>
       </c>
       <c r="M119" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N119" t="n">
         <v>2.44</v>
@@ -23506,7 +23506,7 @@
         <v>1.2</v>
       </c>
       <c r="W119" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="X119" t="n">
         <v>11.5</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -24040,7 +24040,7 @@
         <v>2.14</v>
       </c>
       <c r="G122" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H122" t="n">
         <v>3.45</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24231,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="G123" t="n">
         <v>2.78</v>
@@ -24240,10 +24240,10 @@
         <v>3</v>
       </c>
       <c r="I123" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J123" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="K123" t="n">
         <v>1000</v>
@@ -24279,7 +24279,7 @@
         <v>1.01</v>
       </c>
       <c r="V123" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W123" t="n">
         <v>1.56</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -24425,19 +24425,19 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G124" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H124" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I124" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J124" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K124" t="n">
         <v>3.4</v>
@@ -24473,10 +24473,10 @@
         <v>1.71</v>
       </c>
       <c r="V124" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W124" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X124" t="n">
         <v>10.5</v>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
@@ -24655,7 +24655,7 @@
         <v>1.48</v>
       </c>
       <c r="R125" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S125" t="n">
         <v>2.06</v>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-04-05 05:07:26</t>
+          <t>2026-04-05 07:37:34</t>
         </is>
       </c>
     </row>
